--- a/src/main/resources/doc/PONKIDS-테이블정의서_v2.4.xlsx
+++ b/src/main/resources/doc/PONKIDS-테이블정의서_v2.4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20403"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jjeoV/Desktop/jjeoV/2023/pioneerKids/workspace/ponkidsDev/ponkids/src/main/resources/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\git\ponkids\src\main\resources\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439846BF-2907-AC45-9C1E-3215403D21DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54983D3-087F-4EB3-9A99-8E785D5513E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="855" windowWidth="34200" windowHeight="21375" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="테이블정의서" sheetId="26" r:id="rId1"/>
@@ -22,38 +22,28 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'테이블 목록'!$D$163:$D$504</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">테이블정의서!$A$4:$X$421</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">테이블정의서!$A$4:$X$429</definedName>
+    <definedName name="baseline" localSheetId="0">'[2]2.일정추적'!#REF!</definedName>
+    <definedName name="baseline">'[2]2.일정추적'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'테이블 목록'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">테이블정의서!$B$1:$S$42</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'테이블 목록'!$1:$3</definedName>
+    <definedName name="rpt_date">'[2]1.요약'!$C$4</definedName>
+    <definedName name="T01_컬럼정보_Query" localSheetId="0">#REF!</definedName>
+    <definedName name="T01_컬럼정보_Query">#REF!</definedName>
+    <definedName name="tol">'[2]4.1공수분석_개발'!$J$6</definedName>
     <definedName name="ㄴ" localSheetId="0">#REF!</definedName>
     <definedName name="ㄴ">#REF!</definedName>
     <definedName name="버전" localSheetId="0">#REF!</definedName>
     <definedName name="버전">#REF!</definedName>
-    <definedName name="사업명">[2]표지!$B$43</definedName>
-    <definedName name="baseline" localSheetId="0">'[1]2.일정추적'!#REF!</definedName>
-    <definedName name="baseline">'[1]2.일정추적'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'테이블 목록'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">테이블정의서!$B$1:$S$42</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'테이블 목록'!$1:$3</definedName>
-    <definedName name="rpt_date">'[1]1.요약'!$C$4</definedName>
-    <definedName name="T01_컬럼정보_Query" localSheetId="0">#REF!</definedName>
-    <definedName name="T01_컬럼정보_Query">#REF!</definedName>
-    <definedName name="tol">'[1]4.1공수분석_개발'!$J$6</definedName>
+    <definedName name="사업명">[1]표지!$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4326" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4313" uniqueCount="764">
   <si>
     <t>테이블명</t>
     <phoneticPr fontId="12" type="noConversion"/>
@@ -2968,10 +2958,6 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>사용자 ID</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
     <t>TB_QESTNAR_ANSWER_DETAIL</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
@@ -3069,6 +3055,14 @@
   </si>
   <si>
     <t>컬럼삭제</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>USER_SN</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자일련번호</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -3077,16 +3071,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00_);&quot;₩&quot;&quot;₩&quot;\(&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\)"/>
-    <numFmt numFmtId="181" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="182" formatCode="&quot;₩&quot;#,##0;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0"/>
-    <numFmt numFmtId="183" formatCode="_-&quot;₩&quot;* #,##0_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="184" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0.00"/>
-    <numFmt numFmtId="185" formatCode="0_ "/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00_);&quot;₩&quot;&quot;₩&quot;\(&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\)"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="&quot;₩&quot;#,##0;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="182" formatCode="_-&quot;₩&quot;* #,##0_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="183" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0.00"/>
+    <numFmt numFmtId="184" formatCode="0_ "/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -3636,17 +3630,17 @@
   <cellStyleXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="183" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="182" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="183" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment horizontal="left"/>
@@ -3660,7 +3654,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="10" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4"/>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
@@ -3669,10 +3663,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3683,61 +3677,61 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -3936,7 +3930,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="21" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="21" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3975,7 +3969,7 @@
     <xf numFmtId="0" fontId="28" fillId="6" borderId="14" xfId="88" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="28" fillId="6" borderId="14" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="28" fillId="6" borderId="14" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="14" xfId="88" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4083,7 +4077,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="88" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="28" fillId="5" borderId="14" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="28" fillId="5" borderId="14" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="14" xfId="88" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4113,7 +4107,7 @@
     <xf numFmtId="0" fontId="28" fillId="5" borderId="18" xfId="88" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="28" fillId="5" borderId="18" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="28" fillId="5" borderId="18" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="7" borderId="3" xfId="97" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4236,7 +4230,7 @@
     <xf numFmtId="0" fontId="34" fillId="5" borderId="15" xfId="88" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="28" fillId="5" borderId="14" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="28" fillId="5" borderId="14" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="92" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4283,6 +4277,29 @@
     </xf>
   </cellXfs>
   <cellStyles count="100">
+    <cellStyle name="AeE­ [0]_PERSONAL" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="AeE­_PERSONAL" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="ALIGNMENT" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="C￥AØ_PERSONAL" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="category" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Comma [0] 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Comma [0]_MACRO1.XLM" xfId="9" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="comma zerodec" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Currency1" xfId="11" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Dollar (zero dec)" xfId="12" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Grey" xfId="13" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="HEADER" xfId="14" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Header1" xfId="15" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Header2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Hyperlink_NEGS" xfId="17" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Input [yellow]" xfId="18" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Model" xfId="19" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal - Style1" xfId="20" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normal_#26-PSS Rev and Drivers " xfId="33" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Percent [2]" xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Percent 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="subhead" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
     <cellStyle name="백분율 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
     <cellStyle name="백분율 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
     <cellStyle name="쉼표 [0] 10" xfId="34" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
@@ -4360,29 +4377,6 @@
     <cellStyle name="표준 8" xfId="86" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
     <cellStyle name="표준 9" xfId="87" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
     <cellStyle name="하이퍼링크" xfId="93" builtinId="8"/>
-    <cellStyle name="AeE­ [0]_PERSONAL" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="AeE­_PERSONAL" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="ALIGNMENT" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="C￥AØ_PERSONAL" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="category" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Comma [0] 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Comma [0]_MACRO1.XLM" xfId="9" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="comma zerodec" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Currency1" xfId="11" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Dollar (zero dec)" xfId="12" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Grey" xfId="13" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="HEADER" xfId="14" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Header1" xfId="15" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Header2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Hyperlink_NEGS" xfId="17" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Input [yellow]" xfId="18" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Model" xfId="19" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Normal - Style1" xfId="20" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Normal 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Normal_#26-PSS Rev and Drivers " xfId="33" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Percent [2]" xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Percent 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="subhead" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4403,42 +4397,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="1.요약"/>
-      <sheetName val="2.일정추적"/>
-      <sheetName val="3.규모추적"/>
-      <sheetName val="4.1공수분석_개발"/>
-      <sheetName val="4.2공수추적_관리"/>
-      <sheetName val="5.1결함분석_현황"/>
-      <sheetName val="5.2결함분석_제거"/>
-      <sheetName val="6.Risks"/>
-      <sheetName val="7.실시내용 &amp; Issues"/>
-      <sheetName val="8.Lessons"/>
-      <sheetName val="99.1공수"/>
-      <sheetName val="99.2결함"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="표지"/>
@@ -4469,6 +4428,23 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="2.일정추적"/>
+      <sheetName val="1.요약"/>
+      <sheetName val="4.1공수분석_개발"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4799,43 +4775,43 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AG480"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" style="89" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" style="89" customWidth="1"/>
     <col min="2" max="2" width="9" style="89" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="89" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.6640625" style="93" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="93" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.6640625" style="94" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="93" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" style="93" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="89" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.1640625" style="89" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.5" style="89" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.44140625" style="93" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.77734375" style="93" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" style="89" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" style="89" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.33203125" style="89" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" style="89" customWidth="1"/>
-    <col min="14" max="15" width="18.5" style="89" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="93" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.83203125" style="94" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.83203125" style="89" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.77734375" style="89" customWidth="1"/>
+    <col min="14" max="15" width="18.44140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.77734375" style="93" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.77734375" style="94" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.77734375" style="89" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="24.33203125" style="93" customWidth="1"/>
     <col min="20" max="20" width="29.6640625" style="131" customWidth="1"/>
-    <col min="21" max="21" width="23.5" style="131" customWidth="1"/>
-    <col min="22" max="22" width="17.5" style="93" customWidth="1"/>
-    <col min="23" max="23" width="8.5" style="89" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.44140625" style="131" customWidth="1"/>
+    <col min="22" max="22" width="17.44140625" style="93" customWidth="1"/>
+    <col min="23" max="23" width="8.44140625" style="89" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.33203125" style="131" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="25" style="131" customWidth="1"/>
-    <col min="26" max="26" width="40.83203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="40.77734375" style="131" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="36" style="131" customWidth="1"/>
     <col min="28" max="28" width="29.6640625" style="131" customWidth="1"/>
-    <col min="29" max="29" width="36.1640625" style="131" customWidth="1"/>
+    <col min="29" max="29" width="36.109375" style="131" customWidth="1"/>
     <col min="30" max="30" width="80.6640625" style="131" bestFit="1" customWidth="1"/>
     <col min="31" max="32" width="80.6640625" style="131" customWidth="1"/>
-    <col min="33" max="33" width="86.5" style="131" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="8.83203125" style="131"/>
+    <col min="33" max="33" width="86.44140625" style="131" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="8.77734375" style="131"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1" thickBot="1">
+    <row r="1" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A1" s="29" t="s">
         <v>54</v>
       </c>
@@ -4891,7 +4867,7 @@
       <c r="V2" s="42"/>
       <c r="W2" s="40"/>
     </row>
-    <row r="3" spans="1:33" s="41" customFormat="1" ht="25" customHeight="1" thickBot="1">
+    <row r="3" spans="1:33" s="41" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
       <c r="A3" s="134"/>
       <c r="B3" s="135"/>
       <c r="C3" s="135"/>
@@ -4917,7 +4893,7 @@
       <c r="W3" s="72"/>
       <c r="X3" s="72"/>
     </row>
-    <row r="4" spans="1:33" s="41" customFormat="1" ht="32">
+    <row r="4" spans="1:33" s="41" customFormat="1">
       <c r="A4" s="80" t="s">
         <v>6</v>
       </c>
@@ -5000,22 +4976,22 @@
         <v>569</v>
       </c>
       <c r="AC4" s="41" t="s">
+        <v>757</v>
+      </c>
+      <c r="AD4" s="41" t="s">
         <v>758</v>
       </c>
-      <c r="AD4" s="41" t="s">
-        <v>759</v>
-      </c>
       <c r="AE4" s="41" t="s">
+        <v>760</v>
+      </c>
+      <c r="AF4" s="41" t="s">
         <v>761</v>
-      </c>
-      <c r="AF4" s="41" t="s">
-        <v>762</v>
       </c>
       <c r="AG4" s="41" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="5" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="55">
         <v>1</v>
       </c>
@@ -5104,7 +5080,7 @@
         <v>COMMENT ON COLUMN TB_USER.USER_SN IS '사용자 일련번호' ;</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="6" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="55">
         <v>2</v>
       </c>
@@ -5132,9 +5108,7 @@
       <c r="I6" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="75">
-        <v>2</v>
-      </c>
+      <c r="J6" s="75"/>
       <c r="K6" s="75"/>
       <c r="L6" s="75"/>
       <c r="M6" s="75"/>
@@ -5144,7 +5118,7 @@
         <v>555</v>
       </c>
       <c r="Q6" s="126" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="R6" s="75"/>
       <c r="S6" s="110" t="s">
@@ -5163,7 +5137,7 @@
       </c>
       <c r="Z6" s="50" t="str">
         <f>G6&amp;" "&amp;P6&amp;Q6&amp;IF(ISBLANK(J6),""," PRIMARY KEY")&amp;IF(AND(ISBLANK(J6),I6="Y")," NOT NULL","")&amp;","</f>
-        <v>USER_ID VARCHAR(500) PRIMARY KEY,</v>
+        <v>USER_ID VARCHAR(50) NOT NULL,</v>
       </c>
       <c r="AA6" s="50" t="str">
         <f t="shared" ref="AA6:AA66" si="1">IF(ISBLANK(K6),"","ALTER TABLE " &amp; D6 &amp; " ADD CONSTRAINT " &amp; D6 &amp; "_FKEY" &amp; K6 &amp;  " FOREIGN KEY(" &amp;G6 &amp; ") REFERENCES " &amp; L6 &amp; "(" &amp; M6 &amp; ") "&amp;N6&amp;" "&amp;O6&amp;";")</f>
@@ -5179,11 +5153,11 @@
       </c>
       <c r="AD6" s="50" t="str">
         <f t="shared" ref="AD6:AD69" si="4">"ALTER TABLE "&amp;$D6&amp;" ALTER COLUMN "&amp;$G6&amp;" TYPE "&amp;$P6&amp;IF(ISBLANK(Q6),"",Q6)&amp;";"</f>
-        <v>ALTER TABLE TB_USER ALTER COLUMN USER_ID TYPE VARCHAR(500);</v>
+        <v>ALTER TABLE TB_USER ALTER COLUMN USER_ID TYPE VARCHAR(50);</v>
       </c>
       <c r="AE6" s="50" t="str">
         <f t="shared" ref="AE6:AE69" si="5">"ALTER TABLE "&amp;$D6&amp;" ADD COLUMN "&amp;$G6&amp;" "&amp;$P6&amp;IF(ISBLANK(Q6),"",$Q6)&amp;IF(ISBLANK($I6),""," NOT NULL")&amp;IF(ISBLANK($R6),""," DEFAULT "&amp;$R6)&amp;";"</f>
-        <v>ALTER TABLE TB_USER ADD COLUMN USER_ID VARCHAR(500) NOT NULL;</v>
+        <v>ALTER TABLE TB_USER ADD COLUMN USER_ID VARCHAR(50) NOT NULL;</v>
       </c>
       <c r="AF6" s="50" t="str">
         <f t="shared" ref="AF6:AF69" si="6">"ALTER TABLE "&amp;$D6&amp;" DROP COLUMN "&amp;$G6&amp;";"</f>
@@ -5194,7 +5168,7 @@
         <v>COMMENT ON COLUMN TB_USER.USER_ID IS '사용자 ID' ;</v>
       </c>
     </row>
-    <row r="7" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="7" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="55">
         <v>3</v>
       </c>
@@ -5214,10 +5188,10 @@
         <v>3</v>
       </c>
       <c r="G7" s="101" t="s">
+        <v>751</v>
+      </c>
+      <c r="H7" s="101" t="s">
         <v>752</v>
-      </c>
-      <c r="H7" s="101" t="s">
-        <v>753</v>
       </c>
       <c r="I7" s="75" t="s">
         <v>72</v>
@@ -5236,12 +5210,12 @@
       </c>
       <c r="R7" s="84"/>
       <c r="S7" s="53" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="T7" s="115"/>
       <c r="U7" s="115"/>
       <c r="V7" s="123" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="W7" s="48"/>
       <c r="X7" s="49"/>
@@ -5282,7 +5256,7 @@
         <v>COMMENT ON COLUMN TB_USER.PASSWORD IS '비밀번호' ;</v>
       </c>
     </row>
-    <row r="8" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="8" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="55">
         <v>4</v>
       </c>
@@ -5368,7 +5342,7 @@
         <v>COMMENT ON COLUMN TB_USER.USER_NM IS '사용자 이름' ;</v>
       </c>
     </row>
-    <row r="9" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="9" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="55">
         <v>5</v>
       </c>
@@ -5388,7 +5362,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="101" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H9" s="101" t="s">
         <v>73</v>
@@ -5456,7 +5430,7 @@
         <v>COMMENT ON COLUMN TB_USER.GENDER IS '사용자의 성별. 남자 혹은 여자' ;</v>
       </c>
     </row>
-    <row r="10" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="10" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="55">
         <v>6</v>
       </c>
@@ -5501,7 +5475,7 @@
       <c r="T10" s="115"/>
       <c r="U10" s="115"/>
       <c r="V10" s="123" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="W10" s="48"/>
       <c r="X10" s="49"/>
@@ -5542,7 +5516,7 @@
         <v>COMMENT ON COLUMN TB_USER.BRDT_DATE IS '사용자 생년월일' ;</v>
       </c>
     </row>
-    <row r="11" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="11" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="55">
         <v>7</v>
       </c>
@@ -5628,7 +5602,7 @@
         <v>COMMENT ON COLUMN TB_USER.TEL_NO IS '사용자 연락처' ;</v>
       </c>
     </row>
-    <row r="12" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="12" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="55">
         <v>8</v>
       </c>
@@ -5712,7 +5686,7 @@
         <v>COMMENT ON COLUMN TB_USER.RESIDE_AREA IS '사용자 거주지역' ;</v>
       </c>
     </row>
-    <row r="13" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="13" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="55">
         <v>9</v>
       </c>
@@ -5796,7 +5770,7 @@
         <v>COMMENT ON COLUMN TB_USER.ZIP IS '우편번호' ;</v>
       </c>
     </row>
-    <row r="14" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="14" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="55">
         <v>10</v>
       </c>
@@ -5880,7 +5854,7 @@
         <v>COMMENT ON COLUMN TB_USER.RDNM_ADR IS '도로명 주소' ;</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="15" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="55">
         <v>11</v>
       </c>
@@ -5964,7 +5938,7 @@
         <v>COMMENT ON COLUMN TB_USER.DETAIL_ADR IS '상세 주소' ;</v>
       </c>
     </row>
-    <row r="16" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="16" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="55">
         <v>12</v>
       </c>
@@ -6056,7 +6030,7 @@
         <v>COMMENT ON COLUMN TB_USER.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="17" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="17" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="55">
         <v>13</v>
       </c>
@@ -6144,7 +6118,7 @@
         <v>COMMENT ON COLUMN TB_USER.MNGR_YN IS '관리자 여부' ;</v>
       </c>
     </row>
-    <row r="18" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="18" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="55">
         <v>14</v>
       </c>
@@ -6230,7 +6204,7 @@
         <v>COMMENT ON COLUMN TB_USER.MNGR_CONFM_YN IS '관리자 승인 여부' ;</v>
       </c>
     </row>
-    <row r="19" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="19" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="55">
         <v>15</v>
       </c>
@@ -6316,7 +6290,7 @@
         <v>COMMENT ON COLUMN TB_USER.CONFMER_ID IS '승인자 ID' ;</v>
       </c>
     </row>
-    <row r="20" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="20" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="55">
         <v>16</v>
       </c>
@@ -6400,7 +6374,7 @@
         <v>COMMENT ON COLUMN TB_USER.CONFMER_IP IS '승인자 IP' ;</v>
       </c>
     </row>
-    <row r="21" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="21" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="55">
         <v>17</v>
       </c>
@@ -6433,7 +6407,7 @@
       <c r="N21" s="61"/>
       <c r="O21" s="61"/>
       <c r="P21" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q21" s="126"/>
       <c r="R21" s="82"/>
@@ -6482,7 +6456,7 @@
         <v>COMMENT ON COLUMN TB_USER.CONFM_DT IS '승인 일시' ;</v>
       </c>
     </row>
-    <row r="22" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="22" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="55">
         <v>18</v>
       </c>
@@ -6566,7 +6540,7 @@
         <v>COMMENT ON COLUMN TB_USER.CNTN_SNS IS '연계 SNS' ;</v>
       </c>
     </row>
-    <row r="23" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="23" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="55">
         <v>19</v>
       </c>
@@ -6599,7 +6573,7 @@
       <c r="N23" s="52"/>
       <c r="O23" s="52"/>
       <c r="P23" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q23" s="126"/>
       <c r="R23" s="85"/>
@@ -6648,7 +6622,7 @@
         <v>COMMENT ON COLUMN TB_USER.LAST_LOGIN_DT IS '마지막 로그인한 일시' ;</v>
       </c>
     </row>
-    <row r="24" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="24" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="55">
         <v>20</v>
       </c>
@@ -6734,7 +6708,7 @@
         <v>COMMENT ON COLUMN TB_USER.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="25" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="25" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="55">
         <v>21</v>
       </c>
@@ -6769,7 +6743,7 @@
       <c r="N25" s="52"/>
       <c r="O25" s="52"/>
       <c r="P25" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q25" s="126"/>
       <c r="R25" s="85"/>
@@ -6818,7 +6792,7 @@
         <v>COMMENT ON COLUMN TB_USER.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="26" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="26" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="55">
         <v>22</v>
       </c>
@@ -6904,7 +6878,7 @@
         <v>COMMENT ON COLUMN TB_USER.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="27" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="27" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="55">
         <v>23</v>
       </c>
@@ -6988,7 +6962,7 @@
         <v>COMMENT ON COLUMN TB_USER.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="28" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="28" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="55">
         <v>24</v>
       </c>
@@ -7021,7 +6995,7 @@
       <c r="N28" s="61"/>
       <c r="O28" s="61"/>
       <c r="P28" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q28" s="126"/>
       <c r="R28" s="82"/>
@@ -7070,7 +7044,7 @@
         <v>COMMENT ON COLUMN TB_USER.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="29" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="29" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="55">
         <v>25</v>
       </c>
@@ -7158,7 +7132,7 @@
         <v>COMMENT ON COLUMN TB_USER.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="30" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="30" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="55">
         <v>26</v>
       </c>
@@ -7247,7 +7221,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.CHLDRN_SN IS '자녀 일련번호' ;</v>
       </c>
     </row>
-    <row r="31" spans="1:33" s="50" customFormat="1" ht="20" customHeight="1">
+    <row r="31" spans="1:33" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="55">
         <v>27</v>
       </c>
@@ -7267,10 +7241,10 @@
         <v>2</v>
       </c>
       <c r="G31" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="H31" s="100" t="s">
-        <v>527</v>
+        <v>763</v>
       </c>
       <c r="I31" s="75" t="s">
         <v>72</v>
@@ -7283,7 +7257,7 @@
         <v>9</v>
       </c>
       <c r="M31" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="N31" s="100" t="s">
         <v>574</v>
@@ -7292,20 +7266,16 @@
         <v>576</v>
       </c>
       <c r="P31" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q31" s="126" t="s">
-        <v>560</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q31" s="126"/>
       <c r="R31" s="86"/>
       <c r="S31" s="112" t="s">
-        <v>528</v>
+        <v>109</v>
       </c>
       <c r="T31" s="115"/>
       <c r="U31" s="115"/>
-      <c r="V31" s="123" t="s">
-        <v>529</v>
-      </c>
+      <c r="V31" s="123"/>
       <c r="W31" s="68"/>
       <c r="X31" s="70"/>
       <c r="Y31" s="129" t="str">
@@ -7314,11 +7284,11 @@
       </c>
       <c r="Z31" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>USER_ID VARCHAR(50) NOT NULL,</v>
+        <v>USER_SN INTEGER NOT NULL,</v>
       </c>
       <c r="AA31" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>ALTER TABLE TB_USER_CHLDRN ADD CONSTRAINT TB_USER_CHLDRN_FKEY1 FOREIGN KEY(USER_ID) REFERENCES TB_USER(USER_ID) ON UPDATE CASCADE ON DELETE CASCADE;</v>
+        <v>ALTER TABLE TB_USER_CHLDRN ADD CONSTRAINT TB_USER_CHLDRN_FKEY1 FOREIGN KEY(USER_SN) REFERENCES TB_USER(USER_SN) ON UPDATE CASCADE ON DELETE CASCADE;</v>
       </c>
       <c r="AB31" s="50" t="str">
         <f t="shared" si="2"/>
@@ -7330,22 +7300,22 @@
       </c>
       <c r="AD31" s="50" t="str">
         <f t="shared" si="4"/>
-        <v>ALTER TABLE TB_USER_CHLDRN ALTER COLUMN USER_ID TYPE VARCHAR(50);</v>
+        <v>ALTER TABLE TB_USER_CHLDRN ALTER COLUMN USER_SN TYPE INTEGER;</v>
       </c>
       <c r="AE31" s="50" t="str">
         <f t="shared" si="5"/>
-        <v>ALTER TABLE TB_USER_CHLDRN ADD COLUMN USER_ID VARCHAR(50) NOT NULL;</v>
+        <v>ALTER TABLE TB_USER_CHLDRN ADD COLUMN USER_SN INTEGER NOT NULL;</v>
       </c>
       <c r="AF31" s="50" t="str">
         <f t="shared" si="6"/>
-        <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN USER_ID;</v>
+        <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN USER_SN;</v>
       </c>
       <c r="AG31" s="50" t="str">
         <f t="shared" si="7"/>
-        <v>COMMENT ON COLUMN TB_USER_CHLDRN.USER_ID IS '사용자 ID' ;</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+        <v>COMMENT ON COLUMN TB_USER_CHLDRN.USER_SN IS '사용자 일련번호' ;</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="55">
         <v>28</v>
       </c>
@@ -7431,7 +7401,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.USER_CHLDRN_SEQ IS '해당 사용자의 몇번째 자녀인지 구분하는 값' ;</v>
       </c>
     </row>
-    <row r="33" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="33" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="55">
         <v>29</v>
       </c>
@@ -7517,7 +7487,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.CHLDRN_NM IS '자녀 이름' ;</v>
       </c>
     </row>
-    <row r="34" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="34" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="55">
         <v>30</v>
       </c>
@@ -7537,7 +7507,7 @@
         <v>5</v>
       </c>
       <c r="G34" s="104" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H34" s="104" t="s">
         <v>123</v>
@@ -7603,7 +7573,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.CHLDRN_GENDER IS '자녀 성별' ;</v>
       </c>
     </row>
-    <row r="35" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="35" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A35" s="55">
         <v>31</v>
       </c>
@@ -7648,7 +7618,7 @@
       <c r="T35" s="115"/>
       <c r="U35" s="115"/>
       <c r="V35" s="123" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="W35" s="48"/>
       <c r="X35" s="49"/>
@@ -7689,7 +7659,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.CHLDRN_BRDT_DATE IS '자녀 생년월일' ;</v>
       </c>
     </row>
-    <row r="36" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="36" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="55">
         <v>32</v>
       </c>
@@ -7773,7 +7743,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.CHLDRN_EMAIL IS '자녀 이메일' ;</v>
       </c>
     </row>
-    <row r="37" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="37" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="55">
         <v>33</v>
       </c>
@@ -7857,7 +7827,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.CHLDRN_TEL_NO IS '자녀 연락처' ;</v>
       </c>
     </row>
-    <row r="38" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="38" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="55">
         <v>34</v>
       </c>
@@ -7949,7 +7919,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="39" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="39" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A39" s="55">
         <v>35</v>
       </c>
@@ -8037,7 +8007,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="40" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="40" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="55">
         <v>36</v>
       </c>
@@ -8123,7 +8093,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="41" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="41" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A41" s="55">
         <v>37</v>
       </c>
@@ -8158,7 +8128,7 @@
       <c r="N41" s="52"/>
       <c r="O41" s="52"/>
       <c r="P41" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q41" s="126"/>
       <c r="R41" s="85"/>
@@ -8207,7 +8177,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="42" spans="1:33" s="41" customFormat="1" ht="20" customHeight="1">
+    <row r="42" spans="1:33" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A42" s="55">
         <v>38</v>
       </c>
@@ -8293,7 +8263,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="20" customHeight="1">
+    <row r="43" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A43" s="55">
         <v>39</v>
       </c>
@@ -8377,7 +8347,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="20" customHeight="1">
+    <row r="44" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A44" s="55">
         <v>40</v>
       </c>
@@ -8410,7 +8380,7 @@
       <c r="N44" s="61"/>
       <c r="O44" s="61"/>
       <c r="P44" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q44" s="126"/>
       <c r="R44" s="82"/>
@@ -8459,7 +8429,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="20" customHeight="1">
+    <row r="45" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A45" s="55">
         <v>41</v>
       </c>
@@ -8547,7 +8517,7 @@
         <v>COMMENT ON COLUMN TB_USER_CHLDRN.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="20" customHeight="1">
+    <row r="46" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A46" s="55">
         <v>42</v>
       </c>
@@ -8636,7 +8606,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.ROLE_SN IS '권한 일련번호' ;</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="20" customHeight="1">
+    <row r="47" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A47" s="55">
         <v>43</v>
       </c>
@@ -8722,7 +8692,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.ROLE_NM IS '권한 이름' ;</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="20" customHeight="1">
+    <row r="48" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A48" s="55">
         <v>44</v>
       </c>
@@ -8806,7 +8776,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.ROLE_DC IS '권한 설명' ;</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="20" customHeight="1">
+    <row r="49" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A49" s="55">
         <v>45</v>
       </c>
@@ -8894,7 +8864,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="20" customHeight="1">
+    <row r="50" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A50" s="55">
         <v>46</v>
       </c>
@@ -8980,7 +8950,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="20" customHeight="1">
+    <row r="51" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A51" s="55">
         <v>47</v>
       </c>
@@ -9015,7 +8985,7 @@
       <c r="N51" s="52"/>
       <c r="O51" s="52"/>
       <c r="P51" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q51" s="126"/>
       <c r="R51" s="85"/>
@@ -9064,7 +9034,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="20" customHeight="1">
+    <row r="52" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A52" s="55">
         <v>48</v>
       </c>
@@ -9150,7 +9120,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="20" customHeight="1">
+    <row r="53" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A53" s="55">
         <v>49</v>
       </c>
@@ -9234,7 +9204,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="20" customHeight="1">
+    <row r="54" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="55">
         <v>50</v>
       </c>
@@ -9267,7 +9237,7 @@
       <c r="N54" s="61"/>
       <c r="O54" s="61"/>
       <c r="P54" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q54" s="126"/>
       <c r="R54" s="82"/>
@@ -9316,7 +9286,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="20" customHeight="1">
+    <row r="55" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="55">
         <v>51</v>
       </c>
@@ -9404,7 +9374,7 @@
         <v>COMMENT ON COLUMN TB_ROLE.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="20" customHeight="1">
+    <row r="56" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A56" s="55">
         <v>52</v>
       </c>
@@ -9493,7 +9463,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.USER_ROLE_SN IS '사용자 권한 일련번호' ;</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="20" customHeight="1">
+    <row r="57" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A57" s="55">
         <v>53</v>
       </c>
@@ -9512,11 +9482,11 @@
       <c r="F57" s="97">
         <v>2</v>
       </c>
-      <c r="G57" s="106" t="s">
-        <v>526</v>
-      </c>
-      <c r="H57" s="106" t="s">
-        <v>527</v>
+      <c r="G57" s="100" t="s">
+        <v>762</v>
+      </c>
+      <c r="H57" s="100" t="s">
+        <v>763</v>
       </c>
       <c r="I57" s="75" t="s">
         <v>72</v>
@@ -9529,7 +9499,7 @@
         <v>9</v>
       </c>
       <c r="M57" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="N57" s="100" t="s">
         <v>574</v>
@@ -9538,20 +9508,16 @@
         <v>576</v>
       </c>
       <c r="P57" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q57" s="126" t="s">
-        <v>560</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q57" s="126"/>
       <c r="R57" s="86"/>
       <c r="S57" s="112" t="s">
-        <v>528</v>
+        <v>109</v>
       </c>
       <c r="T57" s="130"/>
       <c r="U57" s="130"/>
-      <c r="V57" s="123" t="s">
-        <v>529</v>
-      </c>
+      <c r="V57" s="123"/>
       <c r="W57" s="90"/>
       <c r="X57" s="130"/>
       <c r="Y57" s="129" t="str">
@@ -9560,11 +9526,11 @@
       </c>
       <c r="Z57" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>USER_ID VARCHAR(50) NOT NULL,</v>
+        <v>USER_SN INTEGER NOT NULL,</v>
       </c>
       <c r="AA57" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>ALTER TABLE TB_USER_ROLE ADD CONSTRAINT TB_USER_ROLE_FKEY1 FOREIGN KEY(USER_ID) REFERENCES TB_USER(USER_ID) ON UPDATE CASCADE ON DELETE CASCADE;</v>
+        <v>ALTER TABLE TB_USER_ROLE ADD CONSTRAINT TB_USER_ROLE_FKEY1 FOREIGN KEY(USER_SN) REFERENCES TB_USER(USER_SN) ON UPDATE CASCADE ON DELETE CASCADE;</v>
       </c>
       <c r="AB57" s="50" t="str">
         <f t="shared" si="2"/>
@@ -9576,22 +9542,22 @@
       </c>
       <c r="AD57" s="50" t="str">
         <f t="shared" si="4"/>
-        <v>ALTER TABLE TB_USER_ROLE ALTER COLUMN USER_ID TYPE VARCHAR(50);</v>
+        <v>ALTER TABLE TB_USER_ROLE ALTER COLUMN USER_SN TYPE INTEGER;</v>
       </c>
       <c r="AE57" s="50" t="str">
         <f t="shared" si="5"/>
-        <v>ALTER TABLE TB_USER_ROLE ADD COLUMN USER_ID VARCHAR(50) NOT NULL;</v>
+        <v>ALTER TABLE TB_USER_ROLE ADD COLUMN USER_SN INTEGER NOT NULL;</v>
       </c>
       <c r="AF57" s="50" t="str">
         <f t="shared" si="6"/>
-        <v>ALTER TABLE TB_USER_ROLE DROP COLUMN USER_ID;</v>
+        <v>ALTER TABLE TB_USER_ROLE DROP COLUMN USER_SN;</v>
       </c>
       <c r="AG57" s="50" t="str">
         <f t="shared" si="7"/>
-        <v>COMMENT ON COLUMN TB_USER_ROLE.USER_ID IS '사용자 ID' ;</v>
-      </c>
-    </row>
-    <row r="58" spans="1:33" ht="20" customHeight="1">
+        <v>COMMENT ON COLUMN TB_USER_ROLE.USER_SN IS '사용자 일련번호' ;</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A58" s="55">
         <v>54</v>
       </c>
@@ -9685,7 +9651,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.ROLE_SN IS '권한 일련번호' ;</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="20" customHeight="1">
+    <row r="59" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A59" s="55">
         <v>55</v>
       </c>
@@ -9773,7 +9739,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="20" customHeight="1">
+    <row r="60" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A60" s="55">
         <v>56</v>
       </c>
@@ -9859,7 +9825,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="20" customHeight="1">
+    <row r="61" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A61" s="55">
         <v>57</v>
       </c>
@@ -9894,7 +9860,7 @@
       <c r="N61" s="52"/>
       <c r="O61" s="52"/>
       <c r="P61" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q61" s="126"/>
       <c r="R61" s="85"/>
@@ -9943,7 +9909,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="20" customHeight="1">
+    <row r="62" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A62" s="55">
         <v>58</v>
       </c>
@@ -10029,7 +9995,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="20" customHeight="1">
+    <row r="63" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A63" s="55">
         <v>59</v>
       </c>
@@ -10113,7 +10079,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="20" customHeight="1">
+    <row r="64" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A64" s="55">
         <v>60</v>
       </c>
@@ -10146,7 +10112,7 @@
       <c r="N64" s="61"/>
       <c r="O64" s="61"/>
       <c r="P64" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q64" s="126"/>
       <c r="R64" s="82"/>
@@ -10195,7 +10161,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="20" customHeight="1">
+    <row r="65" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A65" s="55">
         <v>61</v>
       </c>
@@ -10283,7 +10249,7 @@
         <v>COMMENT ON COLUMN TB_USER_ROLE.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="20" customHeight="1">
+    <row r="66" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A66" s="55">
         <v>62</v>
       </c>
@@ -10372,7 +10338,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_SN IS '클래스 일련번호' ;</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="20" customHeight="1">
+    <row r="67" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A67" s="55">
         <v>63</v>
       </c>
@@ -10458,7 +10424,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CTGRY_CD IS '클래스 카테고리 코드' ;</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="20" customHeight="1">
+    <row r="68" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A68" s="55">
         <v>64</v>
       </c>
@@ -10544,7 +10510,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CRSE_CD IS '클래스 커리큘럼 코드' ;</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="20" customHeight="1">
+    <row r="69" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A69" s="55">
         <v>65</v>
       </c>
@@ -10630,7 +10596,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_SJ IS '클래스 제목' ;</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="20" customHeight="1">
+    <row r="70" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A70" s="55">
         <v>66</v>
       </c>
@@ -10714,7 +10680,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_SUMRY IS '클래스 요약' ;</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="20" customHeight="1">
+    <row r="71" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A71" s="55">
         <v>67</v>
       </c>
@@ -10798,7 +10764,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_DC IS '클래스 설명' ;</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="20" customHeight="1">
+    <row r="72" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A72" s="55">
         <v>68</v>
       </c>
@@ -10882,7 +10848,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_AMT IS '클래스 금액' ;</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="20" customHeight="1">
+    <row r="73" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A73" s="55">
         <v>69</v>
       </c>
@@ -10968,7 +10934,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_DSCNT_BFE_AMT IS '클래스 할인 전 금액' ;</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="20" customHeight="1">
+    <row r="74" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="55">
         <v>70</v>
       </c>
@@ -11054,7 +11020,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_PD_SET_YN IS '클래스 운영기간 설정할지 여부' ;</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="20" customHeight="1">
+    <row r="75" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A75" s="55">
         <v>71</v>
       </c>
@@ -11090,7 +11056,7 @@
         <v>106</v>
       </c>
       <c r="Q75" s="126" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="R75" s="45"/>
       <c r="S75" s="106" t="s">
@@ -11138,7 +11104,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_BEGIN_DT IS '클래스 운영 시작 일시' ;</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="20" customHeight="1">
+    <row r="76" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A76" s="55">
         <v>72</v>
       </c>
@@ -11174,7 +11140,7 @@
         <v>106</v>
       </c>
       <c r="Q76" s="126" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="R76" s="45"/>
       <c r="S76" s="106" t="s">
@@ -11222,7 +11188,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_END_DT IS '클래스 운영 종료 일시' ;</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="20" customHeight="1">
+    <row r="77" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A77" s="55">
         <v>73</v>
       </c>
@@ -11314,7 +11280,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.THUMB_ATCH_FILE_SN IS '썸네일 첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="20" customHeight="1">
+    <row r="78" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A78" s="55">
         <v>74</v>
       </c>
@@ -11406,7 +11372,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="20" customHeight="1">
+    <row r="79" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A79" s="55">
         <v>75</v>
       </c>
@@ -11494,7 +11460,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.CLASS_EXPSR_YN IS '클래스 화면 표시 여부' ;</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="20" customHeight="1">
+    <row r="80" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A80" s="55">
         <v>76</v>
       </c>
@@ -11582,7 +11548,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="20" customHeight="1">
+    <row r="81" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A81" s="55">
         <v>77</v>
       </c>
@@ -11668,7 +11634,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="20" customHeight="1">
+    <row r="82" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A82" s="55">
         <v>78</v>
       </c>
@@ -11703,7 +11669,7 @@
       <c r="N82" s="52"/>
       <c r="O82" s="52"/>
       <c r="P82" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q82" s="126"/>
       <c r="R82" s="85"/>
@@ -11752,7 +11718,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="20" customHeight="1">
+    <row r="83" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A83" s="55">
         <v>79</v>
       </c>
@@ -11838,7 +11804,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="20" customHeight="1">
+    <row r="84" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A84" s="55">
         <v>80</v>
       </c>
@@ -11922,7 +11888,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="20" customHeight="1">
+    <row r="85" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A85" s="55">
         <v>81</v>
       </c>
@@ -11955,7 +11921,7 @@
       <c r="N85" s="61"/>
       <c r="O85" s="61"/>
       <c r="P85" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q85" s="126"/>
       <c r="R85" s="82"/>
@@ -12004,7 +11970,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="20" customHeight="1">
+    <row r="86" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A86" s="55">
         <v>82</v>
       </c>
@@ -12092,7 +12058,7 @@
         <v>COMMENT ON COLUMN TB_CLASS.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="20" customHeight="1">
+    <row r="87" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A87" s="55">
         <v>83</v>
       </c>
@@ -12181,7 +12147,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.CLASS_DETAIL_SN IS '클래스 상세 일련번호' ;</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="20" customHeight="1">
+    <row r="88" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A88" s="55">
         <v>84</v>
       </c>
@@ -12275,7 +12241,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.CLASS_SN IS '클래스 일련번호' ;</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="20" customHeight="1">
+    <row r="89" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="55">
         <v>85</v>
       </c>
@@ -12364,7 +12330,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.CLASS_DETAIL_SEQ IS '클래스 상세 순번' ;</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="20" customHeight="1">
+    <row r="90" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="55">
         <v>86</v>
       </c>
@@ -12454,7 +12420,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.CLASS_DETAIL_ITEM_TY_CD IS '클래스 상세 항목 유형 코드' ;</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="20" customHeight="1">
+    <row r="91" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="55">
         <v>87</v>
       </c>
@@ -12538,7 +12504,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.CLASS_DETAIL_ITEM_CN IS '클래스 상세 항목' ;</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="20" customHeight="1">
+    <row r="92" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="55">
         <v>88</v>
       </c>
@@ -12626,7 +12592,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.CLASS_DETAIL_ESSNTL_YN IS '클래스 상세 필수 여부' ;</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="20" customHeight="1">
+    <row r="93" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="55">
         <v>89</v>
       </c>
@@ -12714,7 +12680,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="20" customHeight="1">
+    <row r="94" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A94" s="55">
         <v>90</v>
       </c>
@@ -12800,7 +12766,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="20" customHeight="1">
+    <row r="95" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A95" s="55">
         <v>91</v>
       </c>
@@ -12835,7 +12801,7 @@
       <c r="N95" s="52"/>
       <c r="O95" s="52"/>
       <c r="P95" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q95" s="126"/>
       <c r="R95" s="85"/>
@@ -12884,7 +12850,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="20" customHeight="1">
+    <row r="96" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A96" s="55">
         <v>92</v>
       </c>
@@ -12970,7 +12936,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="20" customHeight="1">
+    <row r="97" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A97" s="55">
         <v>93</v>
       </c>
@@ -13054,7 +13020,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="20" customHeight="1">
+    <row r="98" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A98" s="55">
         <v>94</v>
       </c>
@@ -13087,7 +13053,7 @@
       <c r="N98" s="61"/>
       <c r="O98" s="61"/>
       <c r="P98" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q98" s="126"/>
       <c r="R98" s="82"/>
@@ -13136,7 +13102,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="20" customHeight="1">
+    <row r="99" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A99" s="55">
         <v>95</v>
       </c>
@@ -13224,7 +13190,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="20" customHeight="1">
+    <row r="100" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A100" s="55">
         <v>96</v>
       </c>
@@ -13315,7 +13281,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.CLASS_DETAIL_OPTN_SN IS '클래스 상세 옵션 일련번호' ;</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="20" customHeight="1">
+    <row r="101" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A101" s="55">
         <v>97</v>
       </c>
@@ -13409,7 +13375,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.CLASS_DETAIL_SN IS '클래스 상세 일련번호' ;</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="20" customHeight="1">
+    <row r="102" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A102" s="55">
         <v>98</v>
       </c>
@@ -13496,7 +13462,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.CLASS_DETAIL_OPTN_SEQ IS '클래스 상세 옵션 순번' ;</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="20" customHeight="1">
+    <row r="103" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A103" s="55">
         <v>99</v>
       </c>
@@ -13580,7 +13546,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.CLASS_DETAIL_OPTN_CN IS '클래스 상세 옵션 내용' ;</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="20" customHeight="1">
+    <row r="104" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A104" s="55">
         <v>100</v>
       </c>
@@ -13668,7 +13634,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="20" customHeight="1">
+    <row r="105" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A105" s="55">
         <v>101</v>
       </c>
@@ -13754,7 +13720,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="20" customHeight="1">
+    <row r="106" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A106" s="55">
         <v>102</v>
       </c>
@@ -13789,7 +13755,7 @@
       <c r="N106" s="52"/>
       <c r="O106" s="52"/>
       <c r="P106" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q106" s="126"/>
       <c r="R106" s="85"/>
@@ -13838,7 +13804,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="20" customHeight="1">
+    <row r="107" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A107" s="55">
         <v>103</v>
       </c>
@@ -13924,7 +13890,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="20" customHeight="1">
+    <row r="108" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A108" s="55">
         <v>104</v>
       </c>
@@ -14008,7 +13974,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="20" customHeight="1">
+    <row r="109" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A109" s="55">
         <v>105</v>
       </c>
@@ -14041,7 +14007,7 @@
       <c r="N109" s="61"/>
       <c r="O109" s="61"/>
       <c r="P109" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q109" s="126"/>
       <c r="R109" s="82"/>
@@ -14090,7 +14056,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="20" customHeight="1">
+    <row r="110" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A110" s="55">
         <v>106</v>
       </c>
@@ -14178,7 +14144,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_OPTN.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="20" customHeight="1">
+    <row r="111" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A111" s="55">
         <v>107</v>
       </c>
@@ -14267,7 +14233,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.CLASS_DETAIL_REQST_SN IS '클래스 상세 신청 일련번호' ;</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="20" customHeight="1">
+    <row r="112" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A112" s="55">
         <v>108</v>
       </c>
@@ -14361,7 +14327,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.CLASS_DETAIL_SN IS '클래스 상세 일련번호' ;</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="20" customHeight="1">
+    <row r="113" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A113" s="55">
         <v>109</v>
       </c>
@@ -14455,7 +14421,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.LCTRE_REQST_SN IS '수업 신청 일련번호' ;</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="20" customHeight="1">
+    <row r="114" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A114" s="55">
         <v>110</v>
       </c>
@@ -14539,7 +14505,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.CLASS_DETAIL_ANSWER IS '클래스 상세 답변' ;</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="20" customHeight="1">
+    <row r="115" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A115" s="55">
         <v>111</v>
       </c>
@@ -14627,7 +14593,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="20" customHeight="1">
+    <row r="116" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A116" s="55">
         <v>112</v>
       </c>
@@ -14713,7 +14679,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="20" customHeight="1">
+    <row r="117" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A117" s="55">
         <v>113</v>
       </c>
@@ -14748,7 +14714,7 @@
       <c r="N117" s="52"/>
       <c r="O117" s="52"/>
       <c r="P117" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q117" s="126"/>
       <c r="R117" s="85"/>
@@ -14797,7 +14763,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="20" customHeight="1">
+    <row r="118" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A118" s="55">
         <v>114</v>
       </c>
@@ -14883,7 +14849,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="20" customHeight="1">
+    <row r="119" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A119" s="55">
         <v>115</v>
       </c>
@@ -14967,7 +14933,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="20" customHeight="1">
+    <row r="120" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A120" s="55">
         <v>116</v>
       </c>
@@ -15000,7 +14966,7 @@
       <c r="N120" s="61"/>
       <c r="O120" s="61"/>
       <c r="P120" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q120" s="126"/>
       <c r="R120" s="82"/>
@@ -15049,7 +15015,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="20" customHeight="1">
+    <row r="121" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A121" s="55">
         <v>117</v>
       </c>
@@ -15137,7 +15103,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_DETAIL_REQST.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="20" customHeight="1">
+    <row r="122" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A122" s="55">
         <v>118</v>
       </c>
@@ -15226,7 +15192,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.CLASS_WEEK_SN IS '클래스 요일 일련번호' ;</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="20" customHeight="1">
+    <row r="123" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A123" s="55">
         <v>119</v>
       </c>
@@ -15320,7 +15286,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.CLASS_SN IS '클래스 일련번호' ;</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="20" customHeight="1">
+    <row r="124" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A124" s="55">
         <v>120</v>
       </c>
@@ -15406,7 +15372,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.CLASS_DAY_CD IS '클래스 요일 코드' ;</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="20" customHeight="1">
+    <row r="125" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A125" s="55">
         <v>121</v>
       </c>
@@ -15494,7 +15460,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="20" customHeight="1">
+    <row r="126" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A126" s="55">
         <v>122</v>
       </c>
@@ -15580,7 +15546,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="20" customHeight="1">
+    <row r="127" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A127" s="55">
         <v>123</v>
       </c>
@@ -15615,7 +15581,7 @@
       <c r="N127" s="52"/>
       <c r="O127" s="52"/>
       <c r="P127" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q127" s="126"/>
       <c r="R127" s="85"/>
@@ -15664,7 +15630,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="20" customHeight="1">
+    <row r="128" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A128" s="55">
         <v>124</v>
       </c>
@@ -15750,7 +15716,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="20" customHeight="1">
+    <row r="129" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A129" s="55">
         <v>125</v>
       </c>
@@ -15834,7 +15800,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="20" customHeight="1">
+    <row r="130" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A130" s="55">
         <v>126</v>
       </c>
@@ -15867,7 +15833,7 @@
       <c r="N130" s="61"/>
       <c r="O130" s="61"/>
       <c r="P130" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q130" s="126"/>
       <c r="R130" s="82"/>
@@ -15916,7 +15882,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="20" customHeight="1">
+    <row r="131" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A131" s="55">
         <v>127</v>
       </c>
@@ -16004,7 +15970,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_WEEK.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="20" customHeight="1">
+    <row r="132" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A132" s="55">
         <v>128</v>
       </c>
@@ -16093,7 +16059,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.CLASS_LIKE_SN IS '클래스 관심 일련번호' ;</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="20" customHeight="1">
+    <row r="133" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A133" s="55">
         <v>129</v>
       </c>
@@ -16187,7 +16153,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.CLASS_SN IS '클래스 일련번호' ;</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="20" customHeight="1">
+    <row r="134" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A134" s="55">
         <v>130</v>
       </c>
@@ -16207,10 +16173,10 @@
         <v>3</v>
       </c>
       <c r="G134" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="H134" s="100" t="s">
-        <v>527</v>
+        <v>763</v>
       </c>
       <c r="I134" s="75" t="s">
         <v>72</v>
@@ -16223,7 +16189,7 @@
         <v>9</v>
       </c>
       <c r="M134" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="N134" s="100" t="s">
         <v>574</v>
@@ -16232,20 +16198,16 @@
         <v>576</v>
       </c>
       <c r="P134" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q134" s="126" t="s">
-        <v>560</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q134" s="126"/>
       <c r="R134" s="75"/>
-      <c r="S134" s="110" t="s">
-        <v>528</v>
+      <c r="S134" s="112" t="s">
+        <v>109</v>
       </c>
       <c r="T134" s="83"/>
       <c r="U134" s="83"/>
-      <c r="V134" s="123" t="s">
-        <v>529</v>
-      </c>
+      <c r="V134" s="123"/>
       <c r="W134" s="45"/>
       <c r="X134" s="83"/>
       <c r="Y134" s="129" t="str">
@@ -16254,11 +16216,11 @@
       </c>
       <c r="Z134" s="50" t="str">
         <f t="shared" si="32"/>
-        <v>USER_ID VARCHAR(50) NOT NULL,</v>
+        <v>USER_SN INTEGER NOT NULL,</v>
       </c>
       <c r="AA134" s="50" t="str">
         <f t="shared" si="29"/>
-        <v>ALTER TABLE TB_CLASS_LIKE ADD CONSTRAINT TB_CLASS_LIKE_FKEY2 FOREIGN KEY(USER_ID) REFERENCES TB_USER(USER_ID) ON UPDATE CASCADE ON DELETE CASCADE;</v>
+        <v>ALTER TABLE TB_CLASS_LIKE ADD CONSTRAINT TB_CLASS_LIKE_FKEY2 FOREIGN KEY(USER_SN) REFERENCES TB_USER(USER_SN) ON UPDATE CASCADE ON DELETE CASCADE;</v>
       </c>
       <c r="AB134" s="50" t="str">
         <f t="shared" si="30"/>
@@ -16270,22 +16232,22 @@
       </c>
       <c r="AD134" s="50" t="str">
         <f t="shared" ref="AD134:AD197" si="34">"ALTER TABLE "&amp;$D134&amp;" ALTER COLUMN "&amp;$G134&amp;" TYPE "&amp;$P134&amp;IF(ISBLANK(Q134),"",Q134)&amp;";"</f>
-        <v>ALTER TABLE TB_CLASS_LIKE ALTER COLUMN USER_ID TYPE VARCHAR(50);</v>
+        <v>ALTER TABLE TB_CLASS_LIKE ALTER COLUMN USER_SN TYPE INTEGER;</v>
       </c>
       <c r="AE134" s="50" t="str">
         <f t="shared" ref="AE134:AE197" si="35">"ALTER TABLE "&amp;$D134&amp;" ADD COLUMN "&amp;$G134&amp;" "&amp;$P134&amp;IF(ISBLANK(Q134),"",$Q134)&amp;IF(ISBLANK($I134),""," NOT NULL")&amp;IF(ISBLANK($R134),""," DEFAULT "&amp;$R134)&amp;";"</f>
-        <v>ALTER TABLE TB_CLASS_LIKE ADD COLUMN USER_ID VARCHAR(50) NOT NULL;</v>
+        <v>ALTER TABLE TB_CLASS_LIKE ADD COLUMN USER_SN INTEGER NOT NULL;</v>
       </c>
       <c r="AF134" s="50" t="str">
         <f t="shared" ref="AF134:AF197" si="36">"ALTER TABLE "&amp;$D134&amp;" DROP COLUMN "&amp;$G134&amp;";"</f>
-        <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN USER_ID;</v>
+        <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN USER_SN;</v>
       </c>
       <c r="AG134" s="50" t="str">
         <f t="shared" si="31"/>
-        <v>COMMENT ON COLUMN TB_CLASS_LIKE.USER_ID IS '사용자 ID' ;</v>
-      </c>
-    </row>
-    <row r="135" spans="1:33" ht="20" customHeight="1">
+        <v>COMMENT ON COLUMN TB_CLASS_LIKE.USER_SN IS '사용자 일련번호' ;</v>
+      </c>
+    </row>
+    <row r="135" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A135" s="55">
         <v>131</v>
       </c>
@@ -16373,7 +16335,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="20" customHeight="1">
+    <row r="136" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A136" s="55">
         <v>132</v>
       </c>
@@ -16459,7 +16421,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="20" customHeight="1">
+    <row r="137" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A137" s="55">
         <v>133</v>
       </c>
@@ -16494,7 +16456,7 @@
       <c r="N137" s="52"/>
       <c r="O137" s="52"/>
       <c r="P137" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q137" s="126"/>
       <c r="R137" s="85"/>
@@ -16543,7 +16505,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="20" customHeight="1">
+    <row r="138" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A138" s="55">
         <v>134</v>
       </c>
@@ -16629,7 +16591,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="20" customHeight="1">
+    <row r="139" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A139" s="55">
         <v>135</v>
       </c>
@@ -16713,7 +16675,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="20" customHeight="1">
+    <row r="140" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A140" s="55">
         <v>136</v>
       </c>
@@ -16746,7 +16708,7 @@
       <c r="N140" s="61"/>
       <c r="O140" s="61"/>
       <c r="P140" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q140" s="126"/>
       <c r="R140" s="82"/>
@@ -16795,7 +16757,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="20" customHeight="1">
+    <row r="141" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A141" s="55">
         <v>137</v>
       </c>
@@ -16883,7 +16845,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_LIKE.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="20" customHeight="1">
+    <row r="142" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A142" s="55">
         <v>138</v>
       </c>
@@ -16972,7 +16934,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.CLASS_REVIEW_SN IS '클래스 후기 일련번호' ;</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="20" customHeight="1">
+    <row r="143" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A143" s="55">
         <v>139</v>
       </c>
@@ -17066,7 +17028,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.CLASS_SN IS '클래스 일련번호' ;</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="20" customHeight="1">
+    <row r="144" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A144" s="55">
         <v>140</v>
       </c>
@@ -17085,11 +17047,11 @@
       <c r="F144" s="97">
         <v>3</v>
       </c>
-      <c r="G144" s="106" t="s">
-        <v>526</v>
-      </c>
-      <c r="H144" s="106" t="s">
-        <v>527</v>
+      <c r="G144" s="100" t="s">
+        <v>762</v>
+      </c>
+      <c r="H144" s="100" t="s">
+        <v>763</v>
       </c>
       <c r="I144" s="45" t="s">
         <v>198</v>
@@ -17102,7 +17064,7 @@
         <v>9</v>
       </c>
       <c r="M144" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="N144" s="100" t="s">
         <v>574</v>
@@ -17111,20 +17073,16 @@
         <v>576</v>
       </c>
       <c r="P144" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q144" s="126" t="s">
-        <v>560</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q144" s="126"/>
       <c r="R144" s="45"/>
-      <c r="S144" s="106" t="s">
-        <v>528</v>
+      <c r="S144" s="112" t="s">
+        <v>109</v>
       </c>
       <c r="T144" s="83"/>
       <c r="U144" s="83"/>
-      <c r="V144" s="123" t="s">
-        <v>529</v>
-      </c>
+      <c r="V144" s="123"/>
       <c r="W144" s="45"/>
       <c r="X144" s="83"/>
       <c r="Y144" s="129" t="str">
@@ -17133,11 +17091,11 @@
       </c>
       <c r="Z144" s="50" t="str">
         <f t="shared" si="32"/>
-        <v>USER_ID VARCHAR(50) NOT NULL,</v>
+        <v>USER_SN INTEGER NOT NULL,</v>
       </c>
       <c r="AA144" s="50" t="str">
         <f t="shared" si="29"/>
-        <v>ALTER TABLE TB_CLASS_REVIEW ADD CONSTRAINT TB_CLASS_REVIEW_FKEY2 FOREIGN KEY(USER_ID) REFERENCES TB_USER(USER_ID) ON UPDATE CASCADE ON DELETE CASCADE;</v>
+        <v>ALTER TABLE TB_CLASS_REVIEW ADD CONSTRAINT TB_CLASS_REVIEW_FKEY2 FOREIGN KEY(USER_SN) REFERENCES TB_USER(USER_SN) ON UPDATE CASCADE ON DELETE CASCADE;</v>
       </c>
       <c r="AB144" s="50" t="str">
         <f t="shared" si="30"/>
@@ -17149,22 +17107,22 @@
       </c>
       <c r="AD144" s="50" t="str">
         <f t="shared" si="34"/>
-        <v>ALTER TABLE TB_CLASS_REVIEW ALTER COLUMN USER_ID TYPE VARCHAR(50);</v>
+        <v>ALTER TABLE TB_CLASS_REVIEW ALTER COLUMN USER_SN TYPE INTEGER;</v>
       </c>
       <c r="AE144" s="50" t="str">
         <f t="shared" si="35"/>
-        <v>ALTER TABLE TB_CLASS_REVIEW ADD COLUMN USER_ID VARCHAR(50) NOT NULL;</v>
+        <v>ALTER TABLE TB_CLASS_REVIEW ADD COLUMN USER_SN INTEGER NOT NULL;</v>
       </c>
       <c r="AF144" s="50" t="str">
         <f t="shared" si="36"/>
-        <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN USER_ID;</v>
+        <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN USER_SN;</v>
       </c>
       <c r="AG144" s="50" t="str">
         <f t="shared" si="31"/>
-        <v>COMMENT ON COLUMN TB_CLASS_REVIEW.USER_ID IS '사용자 ID' ;</v>
-      </c>
-    </row>
-    <row r="145" spans="1:33" ht="20" customHeight="1">
+        <v>COMMENT ON COLUMN TB_CLASS_REVIEW.USER_SN IS '사용자 일련번호' ;</v>
+      </c>
+    </row>
+    <row r="145" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A145" s="55">
         <v>141</v>
       </c>
@@ -17250,7 +17208,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.STEP IS '계층' ;</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="20" customHeight="1">
+    <row r="146" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A146" s="55">
         <v>142</v>
       </c>
@@ -17337,7 +17295,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.PARNTS_REVIEW_SN IS '부모 후기 일련번호' ;</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="20" customHeight="1">
+    <row r="147" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A147" s="55">
         <v>143</v>
       </c>
@@ -17423,7 +17381,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.REVIEW_CN IS '후기 내용' ;</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="20" customHeight="1">
+    <row r="148" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A148" s="55">
         <v>144</v>
       </c>
@@ -17509,7 +17467,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.REVIEW_GRADE IS '후기 등급(별점)' ;</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="20" customHeight="1">
+    <row r="149" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A149" s="55">
         <v>145</v>
       </c>
@@ -17601,7 +17559,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="20" customHeight="1">
+    <row r="150" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A150" s="55">
         <v>146</v>
       </c>
@@ -17689,7 +17647,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="20" customHeight="1">
+    <row r="151" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A151" s="55">
         <v>147</v>
       </c>
@@ -17775,7 +17733,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="20" customHeight="1">
+    <row r="152" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A152" s="55">
         <v>148</v>
       </c>
@@ -17810,7 +17768,7 @@
       <c r="N152" s="52"/>
       <c r="O152" s="52"/>
       <c r="P152" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q152" s="126"/>
       <c r="R152" s="85"/>
@@ -17859,7 +17817,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="20" customHeight="1">
+    <row r="153" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A153" s="55">
         <v>149</v>
       </c>
@@ -17945,7 +17903,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="20" customHeight="1">
+    <row r="154" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A154" s="55">
         <v>150</v>
       </c>
@@ -18029,7 +17987,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="20" customHeight="1">
+    <row r="155" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A155" s="55">
         <v>151</v>
       </c>
@@ -18062,7 +18020,7 @@
       <c r="N155" s="61"/>
       <c r="O155" s="61"/>
       <c r="P155" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q155" s="126"/>
       <c r="R155" s="82"/>
@@ -18111,7 +18069,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="20" customHeight="1">
+    <row r="156" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A156" s="55">
         <v>152</v>
       </c>
@@ -18199,7 +18157,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_REVIEW.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="20" customHeight="1">
+    <row r="157" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A157" s="55">
         <v>153</v>
       </c>
@@ -18288,7 +18246,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.CLASS_INQRY_SN IS '클래스 문의 일련번호' ;</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="20" customHeight="1">
+    <row r="158" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A158" s="55">
         <v>154</v>
       </c>
@@ -18382,7 +18340,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.CLASS_SN IS '클래스 일련번호' ;</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="20" customHeight="1">
+    <row r="159" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A159" s="55">
         <v>155</v>
       </c>
@@ -18468,7 +18426,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.STEP IS '계층' ;</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="20" customHeight="1">
+    <row r="160" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A160" s="55">
         <v>156</v>
       </c>
@@ -18553,7 +18511,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.PARNTS_INQRY_SN IS '부모 문의 일련번호' ;</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="20" customHeight="1">
+    <row r="161" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A161" s="55">
         <v>157</v>
       </c>
@@ -18572,11 +18530,11 @@
       <c r="F161" s="97">
         <v>5</v>
       </c>
-      <c r="G161" s="102" t="s">
-        <v>526</v>
-      </c>
-      <c r="H161" s="102" t="s">
-        <v>527</v>
+      <c r="G161" s="100" t="s">
+        <v>762</v>
+      </c>
+      <c r="H161" s="100" t="s">
+        <v>763</v>
       </c>
       <c r="I161" s="75" t="s">
         <v>72</v>
@@ -18589,7 +18547,7 @@
         <v>9</v>
       </c>
       <c r="M161" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="N161" s="100" t="s">
         <v>574</v>
@@ -18598,20 +18556,16 @@
         <v>576</v>
       </c>
       <c r="P161" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q161" s="126" t="s">
-        <v>560</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q161" s="126"/>
       <c r="R161" s="86"/>
       <c r="S161" s="112" t="s">
-        <v>528</v>
+        <v>109</v>
       </c>
       <c r="T161" s="83"/>
       <c r="U161" s="83"/>
-      <c r="V161" s="123" t="s">
-        <v>529</v>
-      </c>
+      <c r="V161" s="123"/>
       <c r="W161" s="45"/>
       <c r="X161" s="83"/>
       <c r="Y161" s="129" t="str">
@@ -18620,11 +18574,11 @@
       </c>
       <c r="Z161" s="50" t="str">
         <f t="shared" si="32"/>
-        <v>USER_ID VARCHAR(50) NOT NULL,</v>
+        <v>USER_SN INTEGER NOT NULL,</v>
       </c>
       <c r="AA161" s="50" t="str">
         <f t="shared" si="29"/>
-        <v>ALTER TABLE TB_CLASS_INQRY ADD CONSTRAINT TB_CLASS_INQRY_FKEY2 FOREIGN KEY(USER_ID) REFERENCES TB_USER(USER_ID) ON UPDATE CASCADE ON DELETE CASCADE;</v>
+        <v>ALTER TABLE TB_CLASS_INQRY ADD CONSTRAINT TB_CLASS_INQRY_FKEY2 FOREIGN KEY(USER_SN) REFERENCES TB_USER(USER_SN) ON UPDATE CASCADE ON DELETE CASCADE;</v>
       </c>
       <c r="AB161" s="50" t="str">
         <f t="shared" si="30"/>
@@ -18636,22 +18590,22 @@
       </c>
       <c r="AD161" s="50" t="str">
         <f t="shared" si="34"/>
-        <v>ALTER TABLE TB_CLASS_INQRY ALTER COLUMN USER_ID TYPE VARCHAR(50);</v>
+        <v>ALTER TABLE TB_CLASS_INQRY ALTER COLUMN USER_SN TYPE INTEGER;</v>
       </c>
       <c r="AE161" s="50" t="str">
         <f t="shared" si="35"/>
-        <v>ALTER TABLE TB_CLASS_INQRY ADD COLUMN USER_ID VARCHAR(50) NOT NULL;</v>
+        <v>ALTER TABLE TB_CLASS_INQRY ADD COLUMN USER_SN INTEGER NOT NULL;</v>
       </c>
       <c r="AF161" s="50" t="str">
         <f t="shared" si="36"/>
-        <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN USER_ID;</v>
+        <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN USER_SN;</v>
       </c>
       <c r="AG161" s="50" t="str">
         <f t="shared" si="31"/>
-        <v>COMMENT ON COLUMN TB_CLASS_INQRY.USER_ID IS '사용자 ID' ;</v>
-      </c>
-    </row>
-    <row r="162" spans="1:33" ht="20" customHeight="1">
+        <v>COMMENT ON COLUMN TB_CLASS_INQRY.USER_SN IS '사용자 일련번호' ;</v>
+      </c>
+    </row>
+    <row r="162" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A162" s="55">
         <v>158</v>
       </c>
@@ -18737,7 +18691,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.INQRY_SJ IS '문의 제목' ;</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="20" customHeight="1">
+    <row r="163" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A163" s="55">
         <v>159</v>
       </c>
@@ -18821,7 +18775,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.INQRY_CN IS '문의 내용' ;</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="20" customHeight="1">
+    <row r="164" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A164" s="55">
         <v>160</v>
       </c>
@@ -18907,7 +18861,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.OPEN_YN IS '공개 여부' ;</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="20" customHeight="1">
+    <row r="165" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A165" s="55">
         <v>161</v>
       </c>
@@ -18995,7 +18949,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="20" customHeight="1">
+    <row r="166" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A166" s="55">
         <v>162</v>
       </c>
@@ -19081,7 +19035,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="20" customHeight="1">
+    <row r="167" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A167" s="55">
         <v>163</v>
       </c>
@@ -19116,7 +19070,7 @@
       <c r="N167" s="52"/>
       <c r="O167" s="52"/>
       <c r="P167" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q167" s="126"/>
       <c r="R167" s="85"/>
@@ -19165,7 +19119,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="20" customHeight="1">
+    <row r="168" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A168" s="55">
         <v>164</v>
       </c>
@@ -19251,7 +19205,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="20" customHeight="1">
+    <row r="169" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A169" s="55">
         <v>165</v>
       </c>
@@ -19335,7 +19289,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="20" customHeight="1">
+    <row r="170" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A170" s="55">
         <v>166</v>
       </c>
@@ -19368,7 +19322,7 @@
       <c r="N170" s="61"/>
       <c r="O170" s="61"/>
       <c r="P170" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q170" s="126"/>
       <c r="R170" s="82"/>
@@ -19417,7 +19371,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="20" customHeight="1">
+    <row r="171" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A171" s="55">
         <v>167</v>
       </c>
@@ -19505,7 +19459,7 @@
         <v>COMMENT ON COLUMN TB_CLASS_INQRY.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="20" customHeight="1">
+    <row r="172" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A172" s="55">
         <v>168</v>
       </c>
@@ -19594,7 +19548,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.LCTRE_SN IS '수업 일련번호' ;</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="20" customHeight="1">
+    <row r="173" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A173" s="55">
         <v>169</v>
       </c>
@@ -19688,7 +19642,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.CLASS_SN IS '클래스 일련번호' ;</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="20" customHeight="1">
+    <row r="174" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A174" s="55">
         <v>170</v>
       </c>
@@ -19782,7 +19736,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.CLASS_WEEK_SN IS '클래스 요일 일련번호' ;</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="20" customHeight="1">
+    <row r="175" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A175" s="55">
         <v>171</v>
       </c>
@@ -19871,7 +19825,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.LCTRE_SEQ IS '수업 순번' ;</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="20" customHeight="1">
+    <row r="176" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A176" s="55">
         <v>172</v>
       </c>
@@ -19955,7 +19909,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.LCTRE_SJ IS '수업 제목' ;</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="20" customHeight="1">
+    <row r="177" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A177" s="55">
         <v>173</v>
       </c>
@@ -20039,7 +19993,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.LCTRE_DC IS '수업 설명' ;</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="20" customHeight="1">
+    <row r="178" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A178" s="55">
         <v>174</v>
       </c>
@@ -20123,7 +20077,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.LCTRE_APPLCNT_GUIDANCE IS '수업 신청자 안내' ;</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="20" customHeight="1">
+    <row r="179" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A179" s="55">
         <v>175</v>
       </c>
@@ -20209,7 +20163,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.RCRIT_NMPR_SET_YN IS '모집 인원 설정 여부' ;</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="20" customHeight="1">
+    <row r="180" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A180" s="55">
         <v>176</v>
       </c>
@@ -20293,7 +20247,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.RCRIT_NMPR_CO IS '모집 인원 수' ;</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="20" customHeight="1">
+    <row r="181" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A181" s="55">
         <v>177</v>
       </c>
@@ -20379,7 +20333,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.PREPAR_RCRIT_NMPR_SET_YN IS '예비 모집 인원 설정 여부' ;</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="20" customHeight="1">
+    <row r="182" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A182" s="55">
         <v>178</v>
       </c>
@@ -20463,7 +20417,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.PREPAR_RCRIT_NMPR_CO IS '예비 모집 인원 수' ;</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="20" customHeight="1">
+    <row r="183" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A183" s="55">
         <v>179</v>
       </c>
@@ -20551,7 +20505,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="20" customHeight="1">
+    <row r="184" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A184" s="55">
         <v>180</v>
       </c>
@@ -20637,7 +20591,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="20" customHeight="1">
+    <row r="185" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A185" s="55">
         <v>181</v>
       </c>
@@ -20672,7 +20626,7 @@
       <c r="N185" s="52"/>
       <c r="O185" s="52"/>
       <c r="P185" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q185" s="127"/>
       <c r="R185" s="85"/>
@@ -20721,7 +20675,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="20" customHeight="1">
+    <row r="186" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A186" s="55">
         <v>182</v>
       </c>
@@ -20807,7 +20761,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="20" customHeight="1">
+    <row r="187" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A187" s="55">
         <v>183</v>
       </c>
@@ -20891,7 +20845,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="20" customHeight="1">
+    <row r="188" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A188" s="55">
         <v>184</v>
       </c>
@@ -20924,7 +20878,7 @@
       <c r="N188" s="61"/>
       <c r="O188" s="61"/>
       <c r="P188" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q188" s="127"/>
       <c r="R188" s="82"/>
@@ -20973,7 +20927,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="20" customHeight="1">
+    <row r="189" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A189" s="55">
         <v>185</v>
       </c>
@@ -21061,7 +21015,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="20" customHeight="1">
+    <row r="190" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A190" s="55">
         <v>186</v>
       </c>
@@ -21150,7 +21104,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.LCTRE_REQST_SN IS '수업 신청 일련번호' ;</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="20" customHeight="1">
+    <row r="191" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A191" s="55">
         <v>187</v>
       </c>
@@ -21244,7 +21198,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.LCTRE_SN IS '수업 일련번호' ;</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="20" customHeight="1">
+    <row r="192" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A192" s="55">
         <v>188</v>
       </c>
@@ -21263,11 +21217,11 @@
       <c r="F192" s="97">
         <v>3</v>
       </c>
-      <c r="G192" s="106" t="s">
-        <v>526</v>
-      </c>
-      <c r="H192" s="106" t="s">
-        <v>527</v>
+      <c r="G192" s="100" t="s">
+        <v>762</v>
+      </c>
+      <c r="H192" s="100" t="s">
+        <v>763</v>
       </c>
       <c r="I192" s="75" t="s">
         <v>198</v>
@@ -21280,7 +21234,7 @@
         <v>9</v>
       </c>
       <c r="M192" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="N192" s="100" t="s">
         <v>574</v>
@@ -21289,20 +21243,16 @@
         <v>576</v>
       </c>
       <c r="P192" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q192" s="126" t="s">
-        <v>560</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q192" s="126"/>
       <c r="R192" s="45"/>
-      <c r="S192" s="106" t="s">
-        <v>528</v>
+      <c r="S192" s="112" t="s">
+        <v>109</v>
       </c>
       <c r="T192" s="83"/>
       <c r="U192" s="83"/>
-      <c r="V192" s="123" t="s">
-        <v>529</v>
-      </c>
+      <c r="V192" s="123"/>
       <c r="W192" s="45"/>
       <c r="X192" s="83"/>
       <c r="Y192" s="129" t="str">
@@ -21311,11 +21261,11 @@
       </c>
       <c r="Z192" s="50" t="str">
         <f t="shared" si="32"/>
-        <v>USER_ID VARCHAR(50) NOT NULL,</v>
+        <v>USER_SN INTEGER NOT NULL,</v>
       </c>
       <c r="AA192" s="50" t="str">
         <f t="shared" si="29"/>
-        <v>ALTER TABLE TB_LCTRE_REQST ADD CONSTRAINT TB_LCTRE_REQST_FKEY2 FOREIGN KEY(USER_ID) REFERENCES TB_USER(USER_ID) ON UPDATE CASCADE ON DELETE CASCADE;</v>
+        <v>ALTER TABLE TB_LCTRE_REQST ADD CONSTRAINT TB_LCTRE_REQST_FKEY2 FOREIGN KEY(USER_SN) REFERENCES TB_USER(USER_SN) ON UPDATE CASCADE ON DELETE CASCADE;</v>
       </c>
       <c r="AB192" s="50" t="str">
         <f t="shared" si="30"/>
@@ -21327,22 +21277,22 @@
       </c>
       <c r="AD192" s="50" t="str">
         <f t="shared" si="34"/>
-        <v>ALTER TABLE TB_LCTRE_REQST ALTER COLUMN USER_ID TYPE VARCHAR(50);</v>
+        <v>ALTER TABLE TB_LCTRE_REQST ALTER COLUMN USER_SN TYPE INTEGER;</v>
       </c>
       <c r="AE192" s="50" t="str">
         <f t="shared" si="35"/>
-        <v>ALTER TABLE TB_LCTRE_REQST ADD COLUMN USER_ID VARCHAR(50) NOT NULL;</v>
+        <v>ALTER TABLE TB_LCTRE_REQST ADD COLUMN USER_SN INTEGER NOT NULL;</v>
       </c>
       <c r="AF192" s="50" t="str">
         <f t="shared" si="36"/>
-        <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN USER_ID;</v>
+        <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN USER_SN;</v>
       </c>
       <c r="AG192" s="50" t="str">
         <f t="shared" si="31"/>
-        <v>COMMENT ON COLUMN TB_LCTRE_REQST.USER_ID IS '사용자 ID' ;</v>
-      </c>
-    </row>
-    <row r="193" spans="1:33" ht="20" customHeight="1">
+        <v>COMMENT ON COLUMN TB_LCTRE_REQST.USER_SN IS '사용자 일련번호' ;</v>
+      </c>
+    </row>
+    <row r="193" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A193" s="55">
         <v>189</v>
       </c>
@@ -21434,7 +21384,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.CHLDRN_SN IS '자녀 일련번호' ;</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="20" customHeight="1">
+    <row r="194" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A194" s="55">
         <v>190</v>
       </c>
@@ -21522,7 +21472,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="20" customHeight="1">
+    <row r="195" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A195" s="55">
         <v>191</v>
       </c>
@@ -21608,7 +21558,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="20" customHeight="1">
+    <row r="196" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A196" s="55">
         <v>192</v>
       </c>
@@ -21643,7 +21593,7 @@
       <c r="N196" s="52"/>
       <c r="O196" s="52"/>
       <c r="P196" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q196" s="126"/>
       <c r="R196" s="85"/>
@@ -21692,7 +21642,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="20" customHeight="1">
+    <row r="197" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A197" s="55">
         <v>193</v>
       </c>
@@ -21778,7 +21728,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="20" customHeight="1">
+    <row r="198" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A198" s="55">
         <v>194</v>
       </c>
@@ -21862,7 +21812,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="20" customHeight="1">
+    <row r="199" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A199" s="55">
         <v>195</v>
       </c>
@@ -21895,7 +21845,7 @@
       <c r="N199" s="61"/>
       <c r="O199" s="61"/>
       <c r="P199" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q199" s="126"/>
       <c r="R199" s="82"/>
@@ -21944,7 +21894,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="20" customHeight="1">
+    <row r="200" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A200" s="55">
         <v>196</v>
       </c>
@@ -22032,7 +21982,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="20" customHeight="1">
+    <row r="201" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A201" s="55">
         <v>197</v>
       </c>
@@ -22121,7 +22071,7 @@
         <v>COMMENT ON COLUMN TB_BBS.BBS_SN IS '게시판 일련번호' ;</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="20" customHeight="1">
+    <row r="202" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A202" s="55">
         <v>198</v>
       </c>
@@ -22209,7 +22159,7 @@
         <v>COMMENT ON COLUMN TB_BBS.BBS_SE_CD IS '게시판 구분 코드' ;</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="20" customHeight="1">
+    <row r="203" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A203" s="55">
         <v>199</v>
       </c>
@@ -22263,7 +22213,7 @@
         <v>TB_BBS</v>
       </c>
       <c r="Z203" s="50" t="str">
-        <f t="shared" ref="Z203:Z331" si="60">G203&amp;" "&amp;P203&amp;Q203&amp;IF(ISBLANK(J203),""," PRIMARY KEY")&amp;IF(AND(ISBLANK(J203),I203="Y")," NOT NULL","")&amp;","</f>
+        <f t="shared" ref="Z203:Z318" si="60">G203&amp;" "&amp;P203&amp;Q203&amp;IF(ISBLANK(J203),""," PRIMARY KEY")&amp;IF(AND(ISBLANK(J203),I203="Y")," NOT NULL","")&amp;","</f>
         <v>BBS_NM VARCHAR(255) NOT NULL,</v>
       </c>
       <c r="AA203" s="50" t="str">
@@ -22295,7 +22245,7 @@
         <v>COMMENT ON COLUMN TB_BBS.BBS_NM IS '게시판 이름' ;</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="20" customHeight="1">
+    <row r="204" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A204" s="55">
         <v>200</v>
       </c>
@@ -22377,7 +22327,7 @@
         <v>COMMENT ON COLUMN TB_BBS.BBS_GDCC IS '게시판 안내 문구' ;</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="20" customHeight="1">
+    <row r="205" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A205" s="55">
         <v>201</v>
       </c>
@@ -22461,7 +22411,7 @@
         <v>COMMENT ON COLUMN TB_BBS.BBS_DC IS '게시판 설명' ;</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="20" customHeight="1">
+    <row r="206" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A206" s="55">
         <v>202</v>
       </c>
@@ -22545,7 +22495,7 @@
         <v>COMMENT ON COLUMN TB_BBS.ANSWER_SET_YN IS '댓글 설정 여부' ;</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="20" customHeight="1">
+    <row r="207" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A207" s="55">
         <v>228</v>
       </c>
@@ -22592,7 +22542,7 @@
       <c r="T207" s="83"/>
       <c r="U207" s="83"/>
       <c r="V207" s="106" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="W207" s="45"/>
       <c r="X207" s="83"/>
@@ -22633,7 +22583,7 @@
         <v>COMMENT ON COLUMN TB_BBS.OPEN_YN IS '공개 여부' ;</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="20" customHeight="1">
+    <row r="208" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A208" s="55">
         <v>203</v>
       </c>
@@ -22719,7 +22669,7 @@
         <v>COMMENT ON COLUMN TB_BBS.USE_YN IS '사용 여부' ;</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="20" customHeight="1">
+    <row r="209" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A209" s="55">
         <v>204</v>
       </c>
@@ -22807,7 +22757,7 @@
         <v>COMMENT ON COLUMN TB_BBS.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="20" customHeight="1">
+    <row r="210" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A210" s="55">
         <v>205</v>
       </c>
@@ -22893,7 +22843,7 @@
         <v>COMMENT ON COLUMN TB_BBS.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="20" customHeight="1">
+    <row r="211" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A211" s="55">
         <v>206</v>
       </c>
@@ -22928,7 +22878,7 @@
       <c r="N211" s="52"/>
       <c r="O211" s="52"/>
       <c r="P211" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q211" s="126"/>
       <c r="R211" s="85"/>
@@ -22977,7 +22927,7 @@
         <v>COMMENT ON COLUMN TB_BBS.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="20" customHeight="1">
+    <row r="212" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A212" s="55">
         <v>207</v>
       </c>
@@ -23063,7 +23013,7 @@
         <v>COMMENT ON COLUMN TB_BBS.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="20" customHeight="1">
+    <row r="213" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A213" s="55">
         <v>208</v>
       </c>
@@ -23147,7 +23097,7 @@
         <v>COMMENT ON COLUMN TB_BBS.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="20" customHeight="1">
+    <row r="214" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A214" s="55">
         <v>209</v>
       </c>
@@ -23180,7 +23130,7 @@
       <c r="N214" s="61"/>
       <c r="O214" s="61"/>
       <c r="P214" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q214" s="126"/>
       <c r="R214" s="82"/>
@@ -23229,7 +23179,7 @@
         <v>COMMENT ON COLUMN TB_BBS.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="20" customHeight="1">
+    <row r="215" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A215" s="55">
         <v>210</v>
       </c>
@@ -23317,7 +23267,7 @@
         <v>COMMENT ON COLUMN TB_BBS.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="20" customHeight="1">
+    <row r="216" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A216" s="55">
         <v>221</v>
       </c>
@@ -23406,7 +23356,7 @@
         <v>COMMENT ON COLUMN TB_NTT.NTT_SN IS '게시물 일련번호' ;</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="20" customHeight="1">
+    <row r="217" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A217" s="55">
         <v>222</v>
       </c>
@@ -23500,7 +23450,7 @@
         <v>COMMENT ON COLUMN TB_NTT.BBS_SN IS '게시판 일련번호' ;</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="20" customHeight="1">
+    <row r="218" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A218" s="55">
         <v>223</v>
       </c>
@@ -23589,7 +23539,7 @@
         <v>COMMENT ON COLUMN TB_NTT.NTT_SEQ IS '게시물 순번' ;</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="20" customHeight="1">
+    <row r="219" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A219" s="55">
         <v>224</v>
       </c>
@@ -23673,7 +23623,7 @@
         <v>COMMENT ON COLUMN TB_NTT.NTT_NM IS '게시물 이름' ;</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="20" customHeight="1">
+    <row r="220" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A220" s="55">
         <v>73</v>
       </c>
@@ -23765,7 +23715,7 @@
         <v>COMMENT ON COLUMN TB_NTT.THUMB_ATCH_FILE_SN IS '썸네일 첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="20" customHeight="1">
+    <row r="221" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A221" s="55">
         <v>225</v>
       </c>
@@ -23847,7 +23797,7 @@
         <v>COMMENT ON COLUMN TB_NTT.NTT_CN IS '게시물 내용' ;</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="20" customHeight="1">
+    <row r="222" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A222" s="55">
         <v>226</v>
       </c>
@@ -23939,7 +23889,7 @@
         <v>COMMENT ON COLUMN TB_NTT.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="20" customHeight="1">
+    <row r="223" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A223" s="55">
         <v>227</v>
       </c>
@@ -24021,7 +23971,7 @@
         <v>COMMENT ON COLUMN TB_NTT.NTT_RDCNT IS '게시물 조회수' ;</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="20" customHeight="1">
+    <row r="224" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A224" s="55">
         <v>228</v>
       </c>
@@ -24107,7 +24057,7 @@
         <v>COMMENT ON COLUMN TB_NTT.OPEN_YN IS '공개 여부' ;</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="20" customHeight="1">
+    <row r="225" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A225" s="55">
         <v>229</v>
       </c>
@@ -24191,7 +24141,7 @@
         <v>COMMENT ON COLUMN TB_NTT.NOTICE_SET_YN IS '공지 설정 여부' ;</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="20" customHeight="1">
+    <row r="226" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A226" s="55">
         <v>230</v>
       </c>
@@ -24278,7 +24228,7 @@
         <v>COMMENT ON COLUMN TB_NTT.NOTICE_SEQ IS '공지 순번' ;</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="20" customHeight="1">
+    <row r="227" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A227" s="55">
         <v>231</v>
       </c>
@@ -24366,7 +24316,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="20" customHeight="1">
+    <row r="228" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A228" s="55">
         <v>232</v>
       </c>
@@ -24452,7 +24402,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="20" customHeight="1">
+    <row r="229" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A229" s="55">
         <v>233</v>
       </c>
@@ -24487,7 +24437,7 @@
       <c r="N229" s="52"/>
       <c r="O229" s="52"/>
       <c r="P229" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q229" s="126"/>
       <c r="R229" s="85"/>
@@ -24536,7 +24486,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="20" customHeight="1">
+    <row r="230" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A230" s="55">
         <v>234</v>
       </c>
@@ -24622,7 +24572,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="20" customHeight="1">
+    <row r="231" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A231" s="55">
         <v>235</v>
       </c>
@@ -24706,7 +24656,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="20" customHeight="1">
+    <row r="232" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A232" s="55">
         <v>236</v>
       </c>
@@ -24739,7 +24689,7 @@
       <c r="N232" s="61"/>
       <c r="O232" s="61"/>
       <c r="P232" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q232" s="126"/>
       <c r="R232" s="82"/>
@@ -24788,7 +24738,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="20" customHeight="1">
+    <row r="233" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A233" s="55">
         <v>237</v>
       </c>
@@ -24876,7 +24826,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="20" customHeight="1">
+    <row r="234" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A234" s="55">
         <v>238</v>
       </c>
@@ -24965,7 +24915,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.NTT_ANSWER_SN IS '게시물 댓글 일련번호' ;</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="20" customHeight="1">
+    <row r="235" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A235" s="55">
         <v>239</v>
       </c>
@@ -25059,7 +25009,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.NTT_SN IS '게시물 일련번호' ;</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="20" customHeight="1">
+    <row r="236" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A236" s="55">
         <v>240</v>
       </c>
@@ -25145,7 +25095,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.STEP IS '계층' ;</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="20" customHeight="1">
+    <row r="237" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A237" s="55">
         <v>241</v>
       </c>
@@ -25232,7 +25182,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.PARNTS_ANSWER_SN IS '부모 댓글 일련번호' ;</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="20" customHeight="1">
+    <row r="238" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A238" s="55">
         <v>242</v>
       </c>
@@ -25321,7 +25271,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.NTT_ANSWER_SEQ IS '게시물 댓글 순번' ;</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="20" customHeight="1">
+    <row r="239" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A239" s="55">
         <v>243</v>
       </c>
@@ -25405,7 +25355,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.NTT_ANSWER_CN IS '게시물 댓글 내용' ;</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="20" customHeight="1">
+    <row r="240" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A240" s="55">
         <v>244</v>
       </c>
@@ -25491,7 +25441,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.OPEN_YN IS '공개 여부' ;</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="20" customHeight="1">
+    <row r="241" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A241" s="55">
         <v>245</v>
       </c>
@@ -25579,7 +25529,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="20" customHeight="1">
+    <row r="242" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A242" s="55">
         <v>246</v>
       </c>
@@ -25665,7 +25615,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="20" customHeight="1">
+    <row r="243" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A243" s="55">
         <v>247</v>
       </c>
@@ -25700,7 +25650,7 @@
       <c r="N243" s="52"/>
       <c r="O243" s="52"/>
       <c r="P243" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q243" s="126"/>
       <c r="R243" s="85"/>
@@ -25749,7 +25699,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="20" customHeight="1">
+    <row r="244" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A244" s="55">
         <v>248</v>
       </c>
@@ -25835,7 +25785,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="20" customHeight="1">
+    <row r="245" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A245" s="55">
         <v>249</v>
       </c>
@@ -25919,7 +25869,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="20" customHeight="1">
+    <row r="246" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A246" s="55">
         <v>250</v>
       </c>
@@ -25952,7 +25902,7 @@
       <c r="N246" s="61"/>
       <c r="O246" s="61"/>
       <c r="P246" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q246" s="126"/>
       <c r="R246" s="82"/>
@@ -26001,7 +25951,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="20" customHeight="1">
+    <row r="247" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A247" s="55">
         <v>251</v>
       </c>
@@ -26089,7 +26039,7 @@
         <v>COMMENT ON COLUMN TB_NTT_ANSWER.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="20" customHeight="1">
+    <row r="248" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A248" s="55">
         <v>252</v>
       </c>
@@ -26178,7 +26128,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.POPUP_SN IS '팝업 일련번호' ;</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="20" customHeight="1">
+    <row r="249" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A249" s="55">
         <v>253</v>
       </c>
@@ -26262,7 +26212,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.POPUP_SJ IS '팝업 제목' ;</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="20" customHeight="1">
+    <row r="250" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A250" s="55">
         <v>254</v>
       </c>
@@ -26346,7 +26296,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.POPUP_CN IS '팝업 내용' ;</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="20" customHeight="1">
+    <row r="251" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A251" s="55">
         <v>255</v>
       </c>
@@ -26432,7 +26382,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.USE_YN IS '사용 여부' ;</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="20" customHeight="1">
+    <row r="252" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A252" s="55">
         <v>256</v>
       </c>
@@ -26470,7 +26420,7 @@
         <v>106</v>
       </c>
       <c r="Q252" s="126" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="R252" s="90"/>
       <c r="S252" s="109" t="s">
@@ -26518,7 +26468,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.POPUP_BEGIN_DT IS '팝업 시작 일시' ;</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="20" customHeight="1">
+    <row r="253" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A253" s="55">
         <v>257</v>
       </c>
@@ -26556,7 +26506,7 @@
         <v>106</v>
       </c>
       <c r="Q253" s="126" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="R253" s="90"/>
       <c r="S253" s="109" t="s">
@@ -26604,7 +26554,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.POPUP_END_DT IS '팝업 종료 일시' ;</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="20" customHeight="1">
+    <row r="254" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A254" s="55">
         <v>258</v>
       </c>
@@ -26698,7 +26648,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="20" customHeight="1">
+    <row r="255" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A255" s="55">
         <v>259</v>
       </c>
@@ -26782,7 +26732,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.MOVE_URL IS '클릭시 이동 URL' ;</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="20" customHeight="1">
+    <row r="256" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A256" s="55">
         <v>260</v>
       </c>
@@ -26870,7 +26820,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="20" customHeight="1">
+    <row r="257" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A257" s="55">
         <v>261</v>
       </c>
@@ -26956,7 +26906,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="20" customHeight="1">
+    <row r="258" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A258" s="55">
         <v>262</v>
       </c>
@@ -26991,7 +26941,7 @@
       <c r="N258" s="52"/>
       <c r="O258" s="52"/>
       <c r="P258" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q258" s="126"/>
       <c r="R258" s="85"/>
@@ -27040,7 +26990,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="20" customHeight="1">
+    <row r="259" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A259" s="55">
         <v>263</v>
       </c>
@@ -27126,7 +27076,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="20" customHeight="1">
+    <row r="260" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A260" s="55">
         <v>264</v>
       </c>
@@ -27210,7 +27160,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="20" customHeight="1">
+    <row r="261" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A261" s="55">
         <v>265</v>
       </c>
@@ -27243,7 +27193,7 @@
       <c r="N261" s="61"/>
       <c r="O261" s="61"/>
       <c r="P261" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q261" s="126"/>
       <c r="R261" s="82"/>
@@ -27292,7 +27242,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="20" customHeight="1">
+    <row r="262" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A262" s="55">
         <v>266</v>
       </c>
@@ -27380,7 +27330,7 @@
         <v>COMMENT ON COLUMN TB_POPUP.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="20" customHeight="1">
+    <row r="263" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A263" s="55">
         <v>267</v>
       </c>
@@ -27469,7 +27419,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.QESTNAR_GROUP_SN IS '설문조사 그룹 일련번호' ;</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="20" customHeight="1">
+    <row r="264" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A264" s="55">
         <v>268</v>
       </c>
@@ -27555,7 +27505,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.QESTNAR_GROUP_CD IS '설문조사 그룹 코드' ;</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="20" customHeight="1">
+    <row r="265" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A265" s="55">
         <v>269</v>
       </c>
@@ -27639,7 +27589,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.QESTNAR_GROUP_NM IS '설문조사 그룹 이름' ;</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="20" customHeight="1">
+    <row r="266" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A266" s="55">
         <v>270</v>
       </c>
@@ -27723,7 +27673,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.QESTNAR_GROUP_DC IS '설문조사 그룹 설명' ;</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="20" customHeight="1">
+    <row r="267" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A267" s="55">
         <v>271</v>
       </c>
@@ -27811,7 +27761,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.PRIVCY_YN IS '프라이버시 여부' ;</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="20" customHeight="1">
+    <row r="268" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A268" s="55">
         <v>272</v>
       </c>
@@ -27897,7 +27847,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.USE_YN IS '사용 여부' ;</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="20" customHeight="1">
+    <row r="269" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A269" s="55">
         <v>273</v>
       </c>
@@ -27985,7 +27935,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="20" customHeight="1">
+    <row r="270" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A270" s="55">
         <v>274</v>
       </c>
@@ -28071,7 +28021,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="20" customHeight="1">
+    <row r="271" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A271" s="55">
         <v>275</v>
       </c>
@@ -28106,7 +28056,7 @@
       <c r="N271" s="52"/>
       <c r="O271" s="52"/>
       <c r="P271" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q271" s="126"/>
       <c r="R271" s="85"/>
@@ -28155,7 +28105,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="20" customHeight="1">
+    <row r="272" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A272" s="55">
         <v>276</v>
       </c>
@@ -28241,7 +28191,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="20" customHeight="1">
+    <row r="273" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A273" s="55">
         <v>277</v>
       </c>
@@ -28325,7 +28275,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="20" customHeight="1">
+    <row r="274" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A274" s="55">
         <v>278</v>
       </c>
@@ -28358,7 +28308,7 @@
       <c r="N274" s="61"/>
       <c r="O274" s="61"/>
       <c r="P274" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q274" s="126"/>
       <c r="R274" s="82"/>
@@ -28407,7 +28357,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="20" customHeight="1">
+    <row r="275" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A275" s="55">
         <v>279</v>
       </c>
@@ -28495,7 +28445,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_GROUP.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="20" customHeight="1">
+    <row r="276" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A276" s="55">
         <v>280</v>
       </c>
@@ -28537,7 +28487,7 @@
       <c r="Q276" s="126"/>
       <c r="R276" s="87"/>
       <c r="S276" s="102" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T276" s="132" t="str">
         <f>"SEQ_"&amp;D276&amp;"_SN"</f>
@@ -28584,7 +28534,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.QESTNAR_QESTN_SN IS '설문조사 질문 일련번호' ;</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="20" customHeight="1">
+    <row r="277" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A277" s="55">
         <v>281</v>
       </c>
@@ -28678,7 +28628,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.QESTNAR_GROUP_SN IS '설문조사 그룹 일련번호' ;</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="20" customHeight="1">
+    <row r="278" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A278" s="55">
         <v>282</v>
       </c>
@@ -28767,7 +28717,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.QESTNAR_QESTN_SEQ IS '설문조사 질문 순번' ;</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="20" customHeight="1">
+    <row r="279" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A279" s="55">
         <v>283</v>
       </c>
@@ -28857,7 +28807,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.QESTNAR_QESTN_ITEM_TY_CD IS '설문조사 질문 항목 유형 코드' ;</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="20" customHeight="1">
+    <row r="280" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A280" s="55">
         <v>284</v>
       </c>
@@ -28941,7 +28891,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.QESTNAR_QESTN_ITEM_CN IS '설문조사 질문 항목' ;</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="20" customHeight="1">
+    <row r="281" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A281" s="55">
         <v>285</v>
       </c>
@@ -29029,7 +28979,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.QESTNAR_QESTN_ESSNTL_YN IS '설문조사 질문 필수 여부' ;</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="20" customHeight="1">
+    <row r="282" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A282" s="55">
         <v>286</v>
       </c>
@@ -29117,7 +29067,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="20" customHeight="1">
+    <row r="283" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A283" s="55">
         <v>287</v>
       </c>
@@ -29203,7 +29153,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="20" customHeight="1">
+    <row r="284" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A284" s="55">
         <v>288</v>
       </c>
@@ -29238,7 +29188,7 @@
       <c r="N284" s="52"/>
       <c r="O284" s="52"/>
       <c r="P284" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q284" s="126"/>
       <c r="R284" s="85"/>
@@ -29287,7 +29237,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="20" customHeight="1">
+    <row r="285" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A285" s="55">
         <v>289</v>
       </c>
@@ -29373,7 +29323,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="20" customHeight="1">
+    <row r="286" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A286" s="55">
         <v>290</v>
       </c>
@@ -29457,7 +29407,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="20" customHeight="1">
+    <row r="287" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A287" s="55">
         <v>291</v>
       </c>
@@ -29490,7 +29440,7 @@
       <c r="N287" s="61"/>
       <c r="O287" s="61"/>
       <c r="P287" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q287" s="126"/>
       <c r="R287" s="82"/>
@@ -29539,7 +29489,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="20" customHeight="1">
+    <row r="288" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A288" s="55">
         <v>292</v>
       </c>
@@ -29627,7 +29577,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="20" customHeight="1">
+    <row r="289" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A289" s="55">
         <v>293</v>
       </c>
@@ -29718,7 +29668,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.QESTNAR_QESTN_DETAIL_SN IS '설문조사 질문 상세 일련번호' ;</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="20" customHeight="1">
+    <row r="290" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A290" s="55">
         <v>294</v>
       </c>
@@ -29812,7 +29762,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.QESTNAR_QESTN_SN IS '설문조사 질문 일련번호' ;</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="20" customHeight="1">
+    <row r="291" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A291" s="55">
         <v>295</v>
       </c>
@@ -29899,7 +29849,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.QESTNAR_QESTN_DETAIL_SEQ IS '설문조사 질문 상세 순번' ;</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="20" customHeight="1">
+    <row r="292" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A292" s="55">
         <v>296</v>
       </c>
@@ -29983,7 +29933,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.QESTNAR_QESTN_DETAIL_CN IS '설문조사 질문 상세 내용' ;</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="20" customHeight="1">
+    <row r="293" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A293" s="55">
         <v>297</v>
       </c>
@@ -30071,7 +30021,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="20" customHeight="1">
+    <row r="294" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A294" s="55">
         <v>298</v>
       </c>
@@ -30157,7 +30107,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="20" customHeight="1">
+    <row r="295" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A295" s="55">
         <v>299</v>
       </c>
@@ -30192,7 +30142,7 @@
       <c r="N295" s="52"/>
       <c r="O295" s="52"/>
       <c r="P295" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q295" s="126"/>
       <c r="R295" s="85"/>
@@ -30241,7 +30191,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="20" customHeight="1">
+    <row r="296" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A296" s="55">
         <v>300</v>
       </c>
@@ -30327,7 +30277,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="20" customHeight="1">
+    <row r="297" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A297" s="55">
         <v>301</v>
       </c>
@@ -30411,7 +30361,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="20" customHeight="1">
+    <row r="298" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A298" s="55">
         <v>302</v>
       </c>
@@ -30444,7 +30394,7 @@
       <c r="N298" s="61"/>
       <c r="O298" s="61"/>
       <c r="P298" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q298" s="126"/>
       <c r="R298" s="82"/>
@@ -30493,7 +30443,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="20" customHeight="1">
+    <row r="299" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A299" s="55">
         <v>303</v>
       </c>
@@ -30581,7 +30531,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_QESTN_DETAIL.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="20" customHeight="1">
+    <row r="300" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A300" s="55">
         <v>304</v>
       </c>
@@ -30670,7 +30620,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.QESTNAR_ANSWER_SN IS '설문조사 답변 일련번호' ;</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="20" customHeight="1">
+    <row r="301" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A301" s="55">
         <v>305</v>
       </c>
@@ -30764,7 +30714,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.QESTNAR_GROUP_SN IS '설문조사 그룹 일련번호' ;</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="20" customHeight="1">
+    <row r="302" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A302" s="55">
         <v>306</v>
       </c>
@@ -30784,10 +30734,10 @@
         <v>3</v>
       </c>
       <c r="G302" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="H302" s="100" t="s">
-        <v>527</v>
+        <v>763</v>
       </c>
       <c r="I302" s="75" t="s">
         <v>72</v>
@@ -30800,7 +30750,7 @@
         <v>9</v>
       </c>
       <c r="M302" s="100" t="s">
-        <v>526</v>
+        <v>762</v>
       </c>
       <c r="N302" s="100" t="s">
         <v>574</v>
@@ -30809,14 +30759,12 @@
         <v>576</v>
       </c>
       <c r="P302" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q302" s="126" t="s">
-        <v>563</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q302" s="126"/>
       <c r="R302" s="87"/>
       <c r="S302" s="112" t="s">
-        <v>737</v>
+        <v>109</v>
       </c>
       <c r="T302" s="130"/>
       <c r="U302" s="130"/>
@@ -30829,11 +30777,11 @@
       </c>
       <c r="Z302" s="50" t="str">
         <f t="shared" si="60"/>
-        <v>USER_ID VARCHAR(500) NOT NULL,</v>
+        <v>USER_SN INTEGER NOT NULL,</v>
       </c>
       <c r="AA302" s="50" t="str">
         <f t="shared" si="57"/>
-        <v>ALTER TABLE TB_QESTNAR_ANSWER ADD CONSTRAINT TB_QESTNAR_ANSWER_FKEY2 FOREIGN KEY(USER_ID) REFERENCES TB_USER(USER_ID) ON UPDATE CASCADE ON DELETE CASCADE;</v>
+        <v>ALTER TABLE TB_QESTNAR_ANSWER ADD CONSTRAINT TB_QESTNAR_ANSWER_FKEY2 FOREIGN KEY(USER_SN) REFERENCES TB_USER(USER_SN) ON UPDATE CASCADE ON DELETE CASCADE;</v>
       </c>
       <c r="AB302" s="50" t="str">
         <f t="shared" si="58"/>
@@ -30845,22 +30793,22 @@
       </c>
       <c r="AD302" s="50" t="str">
         <f t="shared" si="70"/>
-        <v>ALTER TABLE TB_QESTNAR_ANSWER ALTER COLUMN USER_ID TYPE VARCHAR(500);</v>
+        <v>ALTER TABLE TB_QESTNAR_ANSWER ALTER COLUMN USER_SN TYPE INTEGER;</v>
       </c>
       <c r="AE302" s="50" t="str">
         <f t="shared" si="71"/>
-        <v>ALTER TABLE TB_QESTNAR_ANSWER ADD COLUMN USER_ID VARCHAR(500) NOT NULL;</v>
+        <v>ALTER TABLE TB_QESTNAR_ANSWER ADD COLUMN USER_SN INTEGER NOT NULL;</v>
       </c>
       <c r="AF302" s="50" t="str">
         <f t="shared" si="72"/>
-        <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN USER_ID;</v>
+        <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN USER_SN;</v>
       </c>
       <c r="AG302" s="50" t="str">
         <f t="shared" si="78"/>
-        <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.USER_ID IS '사용자 ID' ;</v>
-      </c>
-    </row>
-    <row r="303" spans="1:33" ht="20" customHeight="1">
+        <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.USER_SN IS '사용자 일련번호' ;</v>
+      </c>
+    </row>
+    <row r="303" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A303" s="55">
         <v>307</v>
       </c>
@@ -30948,7 +30896,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="20" customHeight="1">
+    <row r="304" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A304" s="55">
         <v>308</v>
       </c>
@@ -31034,7 +30982,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="305" spans="1:33" ht="20" customHeight="1">
+    <row r="305" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A305" s="55">
         <v>309</v>
       </c>
@@ -31069,7 +31017,7 @@
       <c r="N305" s="52"/>
       <c r="O305" s="52"/>
       <c r="P305" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q305" s="126"/>
       <c r="R305" s="85"/>
@@ -31118,7 +31066,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="306" spans="1:33" ht="20" customHeight="1">
+    <row r="306" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A306" s="55">
         <v>310</v>
       </c>
@@ -31204,7 +31152,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="307" spans="1:33" ht="20" customHeight="1">
+    <row r="307" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A307" s="55">
         <v>311</v>
       </c>
@@ -31288,7 +31236,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="308" spans="1:33" ht="20" customHeight="1">
+    <row r="308" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A308" s="55">
         <v>312</v>
       </c>
@@ -31321,7 +31269,7 @@
       <c r="N308" s="61"/>
       <c r="O308" s="61"/>
       <c r="P308" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q308" s="126"/>
       <c r="R308" s="82"/>
@@ -31370,7 +31318,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="309" spans="1:33" ht="20" customHeight="1">
+    <row r="309" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A309" s="55">
         <v>313</v>
       </c>
@@ -31458,7 +31406,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="310" spans="1:33" ht="20" customHeight="1">
+    <row r="310" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A310" s="55">
         <v>314</v>
       </c>
@@ -31469,19 +31417,19 @@
         <v>677</v>
       </c>
       <c r="D310" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E310" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E310" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F310" s="92">
         <v>1</v>
       </c>
       <c r="G310" s="102" t="s">
+        <v>739</v>
+      </c>
+      <c r="H310" s="102" t="s">
         <v>740</v>
-      </c>
-      <c r="H310" s="102" t="s">
-        <v>741</v>
       </c>
       <c r="I310" s="75" t="s">
         <v>716</v>
@@ -31500,7 +31448,7 @@
       <c r="Q310" s="126"/>
       <c r="R310" s="87"/>
       <c r="S310" s="102" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="T310" s="132" t="str">
         <f>"SEQ_"&amp;D310&amp;"_SN"</f>
@@ -31547,7 +31495,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.QESTNAR_ANSWER_DETAIL_SN IS '설문조사 답변 상세 일련번호' ;</v>
       </c>
     </row>
-    <row r="311" spans="1:33" ht="20" customHeight="1">
+    <row r="311" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A311" s="55">
         <v>315</v>
       </c>
@@ -31558,10 +31506,10 @@
         <v>677</v>
       </c>
       <c r="D311" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E311" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E311" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F311" s="92">
         <v>2</v>
@@ -31641,7 +31589,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.QESTNAR_ANSWER_SN IS '설문조사 답변 일련번호' ;</v>
       </c>
     </row>
-    <row r="312" spans="1:33" ht="20" customHeight="1">
+    <row r="312" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A312" s="55">
         <v>316</v>
       </c>
@@ -31652,10 +31600,10 @@
         <v>677</v>
       </c>
       <c r="D312" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E312" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E312" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F312" s="92">
         <v>3</v>
@@ -31691,7 +31639,7 @@
       <c r="Q312" s="126"/>
       <c r="R312" s="87"/>
       <c r="S312" s="102" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T312" s="130"/>
       <c r="U312" s="130"/>
@@ -31735,7 +31683,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.QESTNAR_QESTN_SN IS '설문조사 질문 일련번호' ;</v>
       </c>
     </row>
-    <row r="313" spans="1:33" ht="20" customHeight="1">
+    <row r="313" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A313" s="55">
         <v>317</v>
       </c>
@@ -31746,19 +31694,19 @@
         <v>677</v>
       </c>
       <c r="D313" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E313" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E313" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F313" s="92">
         <v>4</v>
       </c>
       <c r="G313" s="102" t="s">
+        <v>741</v>
+      </c>
+      <c r="H313" s="102" t="s">
         <v>742</v>
-      </c>
-      <c r="H313" s="102" t="s">
-        <v>743</v>
       </c>
       <c r="I313" s="75"/>
       <c r="J313" s="69"/>
@@ -31775,11 +31723,11 @@
       </c>
       <c r="R313" s="87"/>
       <c r="S313" s="102" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="T313" s="130"/>
       <c r="U313" s="130" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="V313" s="109"/>
       <c r="W313" s="90"/>
@@ -31821,7 +31769,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.QESTNAR_ANSWER IS '설문조사 답변' ;</v>
       </c>
     </row>
-    <row r="314" spans="1:33" ht="20" customHeight="1">
+    <row r="314" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A314" s="55">
         <v>318</v>
       </c>
@@ -31832,10 +31780,10 @@
         <v>677</v>
       </c>
       <c r="D314" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E314" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E314" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F314" s="92">
         <v>5</v>
@@ -31873,7 +31821,7 @@
       </c>
       <c r="T314" s="130"/>
       <c r="U314" s="130" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="V314" s="109"/>
       <c r="W314" s="90"/>
@@ -31915,7 +31863,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.QESTNAR_QESTN_DETAIL_SN IS '설문조사 질문 상세 일련번호' ;</v>
       </c>
     </row>
-    <row r="315" spans="1:33" ht="20" customHeight="1">
+    <row r="315" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A315" s="55">
         <v>319</v>
       </c>
@@ -31926,10 +31874,10 @@
         <v>677</v>
       </c>
       <c r="D315" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E315" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E315" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F315" s="92">
         <v>6</v>
@@ -31967,7 +31915,7 @@
       </c>
       <c r="T315" s="130"/>
       <c r="U315" s="130" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="V315" s="109" t="s">
         <v>603</v>
@@ -32011,7 +31959,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="316" spans="1:33" ht="20" customHeight="1">
+    <row r="316" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A316" s="55">
         <v>320</v>
       </c>
@@ -32022,10 +31970,10 @@
         <v>677</v>
       </c>
       <c r="D316" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E316" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E316" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F316" s="92">
         <v>7</v>
@@ -32099,7 +32047,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="317" spans="1:33" ht="20" customHeight="1">
+    <row r="317" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A317" s="55">
         <v>321</v>
       </c>
@@ -32110,10 +32058,10 @@
         <v>677</v>
       </c>
       <c r="D317" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E317" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E317" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F317" s="92">
         <v>8</v>
@@ -32185,7 +32133,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="318" spans="1:33" ht="20" customHeight="1">
+    <row r="318" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A318" s="55">
         <v>322</v>
       </c>
@@ -32196,10 +32144,10 @@
         <v>677</v>
       </c>
       <c r="D318" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E318" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E318" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F318" s="92">
         <v>9</v>
@@ -32220,7 +32168,7 @@
       <c r="N318" s="52"/>
       <c r="O318" s="52"/>
       <c r="P318" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q318" s="126"/>
       <c r="R318" s="85"/>
@@ -32269,7 +32217,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="319" spans="1:33" ht="20" customHeight="1">
+    <row r="319" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A319" s="55">
         <v>323</v>
       </c>
@@ -32280,10 +32228,10 @@
         <v>677</v>
       </c>
       <c r="D319" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E319" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E319" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F319" s="92">
         <v>10</v>
@@ -32355,7 +32303,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="320" spans="1:33" ht="20" customHeight="1">
+    <row r="320" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A320" s="55">
         <v>324</v>
       </c>
@@ -32366,10 +32314,10 @@
         <v>677</v>
       </c>
       <c r="D320" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E320" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E320" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F320" s="92">
         <v>11</v>
@@ -32439,7 +32387,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="321" spans="1:33" ht="20" customHeight="1">
+    <row r="321" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A321" s="55">
         <v>325</v>
       </c>
@@ -32450,10 +32398,10 @@
         <v>677</v>
       </c>
       <c r="D321" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E321" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E321" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F321" s="92">
         <v>12</v>
@@ -32472,7 +32420,7 @@
       <c r="N321" s="61"/>
       <c r="O321" s="61"/>
       <c r="P321" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q321" s="126"/>
       <c r="R321" s="82"/>
@@ -32521,7 +32469,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="322" spans="1:33" ht="20" customHeight="1">
+    <row r="322" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A322" s="55">
         <v>326</v>
       </c>
@@ -32532,10 +32480,10 @@
         <v>677</v>
       </c>
       <c r="D322" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="E322" s="10" t="s">
         <v>738</v>
-      </c>
-      <c r="E322" s="10" t="s">
-        <v>739</v>
       </c>
       <c r="F322" s="92">
         <v>13</v>
@@ -32609,7 +32557,7 @@
         <v>COMMENT ON COLUMN TB_QESTNAR_ANSWER_DETAIL.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="323" spans="1:33" ht="20" customHeight="1">
+    <row r="323" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A323" s="55">
         <v>327</v>
       </c>
@@ -32698,7 +32646,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="324" spans="1:33" ht="20" customHeight="1">
+    <row r="324" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A324" s="55">
         <v>328</v>
       </c>
@@ -32733,7 +32681,7 @@
       <c r="N324" s="90"/>
       <c r="O324" s="90"/>
       <c r="P324" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q324" s="126"/>
       <c r="R324" s="85"/>
@@ -32782,7 +32730,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="325" spans="1:33" ht="20" customHeight="1">
+    <row r="325" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A325" s="55">
         <v>329</v>
       </c>
@@ -32870,7 +32818,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="326" spans="1:33" ht="20" customHeight="1">
+    <row r="326" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A326" s="55">
         <v>330</v>
       </c>
@@ -32966,7 +32914,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE_DETAIL.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="327" spans="1:33" ht="20" customHeight="1">
+    <row r="327" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A327" s="55">
         <v>331</v>
       </c>
@@ -33057,7 +33005,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE_DETAIL.FILE_SEQ IS '파일 순번' ;</v>
       </c>
     </row>
-    <row r="328" spans="1:33" ht="20" customHeight="1">
+    <row r="328" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A328" s="55">
         <v>332</v>
       </c>
@@ -33143,7 +33091,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE_DETAIL.FILE_STRE_PATH IS '파일 저장 경로' ;</v>
       </c>
     </row>
-    <row r="329" spans="1:33" ht="20" customHeight="1">
+    <row r="329" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A329" s="55">
         <v>333</v>
       </c>
@@ -33229,7 +33177,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE_DETAIL.STRE_FILE_NM IS '저장 파일 이름' ;</v>
       </c>
     </row>
-    <row r="330" spans="1:33" ht="20" customHeight="1">
+    <row r="330" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A330" s="55">
         <v>334</v>
       </c>
@@ -33315,7 +33263,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE_DETAIL.ORIGNL_FILE_NM IS '원 파일 이름' ;</v>
       </c>
     </row>
-    <row r="331" spans="1:33" ht="20" customHeight="1">
+    <row r="331" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A331" s="55">
         <v>335</v>
       </c>
@@ -33401,7 +33349,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE_DETAIL.FILE_EXTSN IS '파일 확장자' ;</v>
       </c>
     </row>
-    <row r="332" spans="1:33" ht="20" customHeight="1">
+    <row r="332" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A332" s="55">
         <v>336</v>
       </c>
@@ -33483,7 +33431,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE_DETAIL.FILE_CN IS '파일 내용' ;</v>
       </c>
     </row>
-    <row r="333" spans="1:33" ht="20" customHeight="1">
+    <row r="333" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A333" s="55">
         <v>337</v>
       </c>
@@ -33569,7 +33517,7 @@
         <v>COMMENT ON COLUMN TB_ATCH_FILE_DETAIL.FILE_SIZE IS '파일 크기' ;</v>
       </c>
     </row>
-    <row r="334" spans="1:33" ht="20" customHeight="1">
+    <row r="334" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A334" s="55">
         <v>338</v>
       </c>
@@ -33658,7 +33606,7 @@
         <v>COMMENT ON COLUMN TB_MENU.MENU_SN IS '메뉴 일련번호' ;</v>
       </c>
     </row>
-    <row r="335" spans="1:33" ht="20" customHeight="1">
+    <row r="335" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A335" s="55">
         <v>339</v>
       </c>
@@ -33743,7 +33691,7 @@
         <v>COMMENT ON COLUMN TB_MENU.UPPER_MENU_SN IS '상위 메뉴 일련번호' ;</v>
       </c>
     </row>
-    <row r="336" spans="1:33" ht="20" customHeight="1">
+    <row r="336" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A336" s="55">
         <v>340</v>
       </c>
@@ -33831,7 +33779,7 @@
         <v>COMMENT ON COLUMN TB_MENU.MENU_NM IS '메뉴 이름' ;</v>
       </c>
     </row>
-    <row r="337" spans="1:33" ht="20" customHeight="1">
+    <row r="337" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A337" s="55">
         <v>341</v>
       </c>
@@ -33917,7 +33865,7 @@
         <v>COMMENT ON COLUMN TB_MENU.MENU_CD IS '메뉴 코드' ;</v>
       </c>
     </row>
-    <row r="338" spans="1:33" ht="20" customHeight="1">
+    <row r="338" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A338" s="55">
         <v>342</v>
       </c>
@@ -34001,7 +33949,7 @@
         <v>COMMENT ON COLUMN TB_MENU.MENU_URL IS '메뉴 URL' ;</v>
       </c>
     </row>
-    <row r="339" spans="1:33" ht="20" customHeight="1">
+    <row r="339" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A339" s="55">
         <v>343</v>
       </c>
@@ -34089,7 +34037,7 @@
         <v>COMMENT ON COLUMN TB_MENU.PARNTS_MENU_YN IS '부모 메뉴 여부' ;</v>
       </c>
     </row>
-    <row r="340" spans="1:33" ht="20" customHeight="1">
+    <row r="340" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A340" s="55">
         <v>344</v>
       </c>
@@ -34178,7 +34126,7 @@
         <v>COMMENT ON COLUMN TB_MENU.MENU_SEQ IS '메뉴 순번' ;</v>
       </c>
     </row>
-    <row r="341" spans="1:33" ht="20" customHeight="1">
+    <row r="341" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A341" s="55">
         <v>345</v>
       </c>
@@ -34262,7 +34210,7 @@
         <v>COMMENT ON COLUMN TB_MENU.MENU_DC_SET_YN IS '메뉴 설명 설정 여부' ;</v>
       </c>
     </row>
-    <row r="342" spans="1:33" ht="20" customHeight="1">
+    <row r="342" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A342" s="55">
         <v>346</v>
       </c>
@@ -34348,7 +34296,7 @@
         <v>COMMENT ON COLUMN TB_MENU.MENU_DC IS '메뉴 설명' ;</v>
       </c>
     </row>
-    <row r="343" spans="1:33" ht="20" customHeight="1">
+    <row r="343" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A343" s="55">
         <v>347</v>
       </c>
@@ -34432,7 +34380,7 @@
         <v>COMMENT ON COLUMN TB_MENU.MENU_DETAIL_DC IS '메뉴 상세 설명' ;</v>
       </c>
     </row>
-    <row r="344" spans="1:33" ht="20" customHeight="1">
+    <row r="344" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A344" s="55">
         <v>348</v>
       </c>
@@ -34526,7 +34474,7 @@
         <v>COMMENT ON COLUMN TB_MENU.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="345" spans="1:33" ht="20" customHeight="1">
+    <row r="345" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A345" s="55">
         <v>349</v>
       </c>
@@ -34612,7 +34560,7 @@
         <v>COMMENT ON COLUMN TB_MENU.USE_YN IS '사용 여부' ;</v>
       </c>
     </row>
-    <row r="346" spans="1:33" ht="20" customHeight="1">
+    <row r="346" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A346" s="55">
         <v>350</v>
       </c>
@@ -34700,7 +34648,7 @@
         <v>COMMENT ON COLUMN TB_MENU.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="347" spans="1:33" ht="20" customHeight="1">
+    <row r="347" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A347" s="55">
         <v>351</v>
       </c>
@@ -34786,7 +34734,7 @@
         <v>COMMENT ON COLUMN TB_MENU.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="348" spans="1:33" ht="20" customHeight="1">
+    <row r="348" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A348" s="55">
         <v>352</v>
       </c>
@@ -34821,7 +34769,7 @@
       <c r="N348" s="52"/>
       <c r="O348" s="52"/>
       <c r="P348" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q348" s="127"/>
       <c r="R348" s="85"/>
@@ -34870,7 +34818,7 @@
         <v>COMMENT ON COLUMN TB_MENU.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="349" spans="1:33" ht="20" customHeight="1">
+    <row r="349" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A349" s="55">
         <v>353</v>
       </c>
@@ -34956,7 +34904,7 @@
         <v>COMMENT ON COLUMN TB_MENU.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="350" spans="1:33" ht="20" customHeight="1">
+    <row r="350" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A350" s="55">
         <v>354</v>
       </c>
@@ -35040,7 +34988,7 @@
         <v>COMMENT ON COLUMN TB_MENU.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="351" spans="1:33" ht="20" customHeight="1">
+    <row r="351" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A351" s="55">
         <v>355</v>
       </c>
@@ -35073,7 +35021,7 @@
       <c r="N351" s="61"/>
       <c r="O351" s="61"/>
       <c r="P351" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q351" s="127"/>
       <c r="R351" s="82"/>
@@ -35122,7 +35070,7 @@
         <v>COMMENT ON COLUMN TB_MENU.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="352" spans="1:33" ht="20" customHeight="1">
+    <row r="352" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A352" s="55">
         <v>356</v>
       </c>
@@ -35210,7 +35158,7 @@
         <v>COMMENT ON COLUMN TB_MENU.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="353" spans="1:33" ht="20" customHeight="1">
+    <row r="353" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A353" s="55">
         <v>357</v>
       </c>
@@ -35299,7 +35247,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.MENU_ROLE_SN IS '메뉴 권한 일련번호' ;</v>
       </c>
     </row>
-    <row r="354" spans="1:33" ht="20" customHeight="1">
+    <row r="354" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A354" s="55">
         <v>358</v>
       </c>
@@ -35393,7 +35341,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.MENU_SN IS '메뉴 일련번호' ;</v>
       </c>
     </row>
-    <row r="355" spans="1:33" ht="20" customHeight="1">
+    <row r="355" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A355" s="55">
         <v>359</v>
       </c>
@@ -35487,7 +35435,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.ROLE_SN IS '권한 일련번호' ;</v>
       </c>
     </row>
-    <row r="356" spans="1:33" ht="20" customHeight="1">
+    <row r="356" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A356" s="55">
         <v>360</v>
       </c>
@@ -35575,7 +35523,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="357" spans="1:33" ht="20" customHeight="1">
+    <row r="357" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A357" s="55">
         <v>361</v>
       </c>
@@ -35661,7 +35609,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="358" spans="1:33" ht="20" customHeight="1">
+    <row r="358" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A358" s="55">
         <v>362</v>
       </c>
@@ -35696,7 +35644,7 @@
       <c r="N358" s="52"/>
       <c r="O358" s="52"/>
       <c r="P358" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q358" s="127"/>
       <c r="R358" s="85"/>
@@ -35745,7 +35693,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="359" spans="1:33" ht="20" customHeight="1">
+    <row r="359" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A359" s="55">
         <v>363</v>
       </c>
@@ -35831,7 +35779,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="360" spans="1:33" ht="20" customHeight="1">
+    <row r="360" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A360" s="55">
         <v>364</v>
       </c>
@@ -35915,7 +35863,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="361" spans="1:33" ht="20" customHeight="1">
+    <row r="361" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A361" s="55">
         <v>365</v>
       </c>
@@ -35948,7 +35896,7 @@
       <c r="N361" s="61"/>
       <c r="O361" s="61"/>
       <c r="P361" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q361" s="127"/>
       <c r="R361" s="82"/>
@@ -35997,7 +35945,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="362" spans="1:33" ht="20" customHeight="1">
+    <row r="362" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A362" s="55">
         <v>366</v>
       </c>
@@ -36085,7 +36033,7 @@
         <v>COMMENT ON COLUMN TB_MENU_ROLE.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="363" spans="1:33" ht="20" customHeight="1">
+    <row r="363" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A363" s="55">
         <v>367</v>
       </c>
@@ -36174,7 +36122,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CD_SN IS '코드 일련번호' ;</v>
       </c>
     </row>
-    <row r="364" spans="1:33" ht="20" customHeight="1">
+    <row r="364" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A364" s="55">
         <v>368</v>
       </c>
@@ -36260,7 +36208,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CD_NM IS '코드 이름' ;</v>
       </c>
     </row>
-    <row r="365" spans="1:33" ht="20" customHeight="1">
+    <row r="365" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A365" s="55">
         <v>369</v>
       </c>
@@ -36342,7 +36290,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CD_DC IS '코드 설명' ;</v>
       </c>
     </row>
-    <row r="366" spans="1:33" ht="20" customHeight="1">
+    <row r="366" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A366" s="55">
         <v>370</v>
       </c>
@@ -36426,7 +36374,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CD_DETAIL_VAL1_DC IS '코드 상세 값 1 설명' ;</v>
       </c>
     </row>
-    <row r="367" spans="1:33" ht="20" customHeight="1">
+    <row r="367" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A367" s="55">
         <v>371</v>
       </c>
@@ -36510,7 +36458,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CD_DETAIL_VAL2_DC IS '코드 상세 값 2 설명' ;</v>
       </c>
     </row>
-    <row r="368" spans="1:33" ht="20" customHeight="1">
+    <row r="368" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A368" s="55">
         <v>372</v>
       </c>
@@ -36594,7 +36542,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CD_DETAIL_VAL3_DC IS '코드 상세 값 3 설명' ;</v>
       </c>
     </row>
-    <row r="369" spans="1:33" ht="20" customHeight="1">
+    <row r="369" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A369" s="55">
         <v>373</v>
       </c>
@@ -36678,7 +36626,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CD_DETAIL_VAL4_DC IS '코드 상세 값 4 설명' ;</v>
       </c>
     </row>
-    <row r="370" spans="1:33" ht="20" customHeight="1">
+    <row r="370" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A370" s="55">
         <v>374</v>
       </c>
@@ -36762,7 +36710,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CD_DETAIL_VAL5_DC IS '코드 상세 값 5 설명' ;</v>
       </c>
     </row>
-    <row r="371" spans="1:33" ht="20" customHeight="1">
+    <row r="371" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A371" s="55">
         <v>375</v>
       </c>
@@ -36848,7 +36796,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.USE_YN IS '사용 여부' ;</v>
       </c>
     </row>
-    <row r="372" spans="1:33" ht="20" customHeight="1">
+    <row r="372" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A372" s="55">
         <v>376</v>
       </c>
@@ -36936,7 +36884,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.SYS_ESSNTL_CMMN_YN IS '시스템 필수 코드 여부' ;</v>
       </c>
     </row>
-    <row r="373" spans="1:33" ht="20" customHeight="1">
+    <row r="373" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A373" s="55">
         <v>377</v>
       </c>
@@ -37022,7 +36970,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.CL_CD IS '분류 코드' ;</v>
       </c>
     </row>
-    <row r="374" spans="1:33" ht="20" customHeight="1">
+    <row r="374" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A374" s="55">
         <v>378</v>
       </c>
@@ -37104,7 +37052,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.REMARK IS '비고' ;</v>
       </c>
     </row>
-    <row r="375" spans="1:33" ht="20" customHeight="1">
+    <row r="375" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A375" s="55">
         <v>379</v>
       </c>
@@ -37192,7 +37140,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="376" spans="1:33" ht="20" customHeight="1">
+    <row r="376" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A376" s="55">
         <v>380</v>
       </c>
@@ -37278,7 +37226,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="377" spans="1:33" ht="20" customHeight="1">
+    <row r="377" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A377" s="55">
         <v>381</v>
       </c>
@@ -37313,7 +37261,7 @@
       <c r="N377" s="52"/>
       <c r="O377" s="52"/>
       <c r="P377" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q377" s="127"/>
       <c r="R377" s="85"/>
@@ -37362,7 +37310,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="378" spans="1:33" ht="20" customHeight="1">
+    <row r="378" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A378" s="55">
         <v>382</v>
       </c>
@@ -37448,7 +37396,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="379" spans="1:33" ht="20" customHeight="1">
+    <row r="379" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A379" s="55">
         <v>383</v>
       </c>
@@ -37532,7 +37480,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="380" spans="1:33" ht="20" customHeight="1">
+    <row r="380" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A380" s="55">
         <v>384</v>
       </c>
@@ -37565,7 +37513,7 @@
       <c r="N380" s="61"/>
       <c r="O380" s="61"/>
       <c r="P380" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q380" s="127"/>
       <c r="R380" s="82"/>
@@ -37614,7 +37562,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="381" spans="1:33" ht="20" customHeight="1">
+    <row r="381" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A381" s="55">
         <v>385</v>
       </c>
@@ -37702,7 +37650,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="382" spans="1:33" ht="20" customHeight="1">
+    <row r="382" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A382" s="55">
         <v>386</v>
       </c>
@@ -37791,7 +37739,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_SN IS '코드 상세 일련번호' ;</v>
       </c>
     </row>
-    <row r="383" spans="1:33" ht="20" customHeight="1">
+    <row r="383" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A383" s="55">
         <v>387</v>
       </c>
@@ -37885,7 +37833,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_SN IS '코드 일련번호' ;</v>
       </c>
     </row>
-    <row r="384" spans="1:33" ht="20" customHeight="1">
+    <row r="384" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A384" s="55">
         <v>388</v>
       </c>
@@ -37972,7 +37920,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_SEQ IS '코드 상세 순번' ;</v>
       </c>
     </row>
-    <row r="385" spans="1:33" ht="20" customHeight="1">
+    <row r="385" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A385" s="55">
         <v>389</v>
       </c>
@@ -38058,7 +38006,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_NM IS '코드 상세 이름' ;</v>
       </c>
     </row>
-    <row r="386" spans="1:33" ht="20" customHeight="1">
+    <row r="386" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A386" s="55">
         <v>390</v>
       </c>
@@ -38140,7 +38088,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_DC IS '코드 상세 설명' ;</v>
       </c>
     </row>
-    <row r="387" spans="1:33" ht="20" customHeight="1">
+    <row r="387" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A387" s="55">
         <v>391</v>
       </c>
@@ -38226,7 +38174,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_VAL1 IS '코드 상세값 1' ;</v>
       </c>
     </row>
-    <row r="388" spans="1:33" ht="20" customHeight="1">
+    <row r="388" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A388" s="55">
         <v>392</v>
       </c>
@@ -38312,7 +38260,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_VAL2 IS '코드 상세값 2' ;</v>
       </c>
     </row>
-    <row r="389" spans="1:33" ht="20" customHeight="1">
+    <row r="389" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A389" s="55">
         <v>393</v>
       </c>
@@ -38398,7 +38346,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_VAL3 IS '코드 상세값 3' ;</v>
       </c>
     </row>
-    <row r="390" spans="1:33" ht="20" customHeight="1">
+    <row r="390" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A390" s="55">
         <v>394</v>
       </c>
@@ -38484,7 +38432,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_VAL4 IS '코드 상세값 4' ;</v>
       </c>
     </row>
-    <row r="391" spans="1:33" ht="20" customHeight="1">
+    <row r="391" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A391" s="55">
         <v>395</v>
       </c>
@@ -38570,7 +38518,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.CD_DETAIL_VAL5 IS '코드 상세값 5' ;</v>
       </c>
     </row>
-    <row r="392" spans="1:33" ht="20" customHeight="1">
+    <row r="392" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A392" s="55">
         <v>396</v>
       </c>
@@ -38652,7 +38600,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.REMARK IS '비고' ;</v>
       </c>
     </row>
-    <row r="393" spans="1:33" ht="20" customHeight="1">
+    <row r="393" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A393" s="55">
         <v>397</v>
       </c>
@@ -38738,7 +38686,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.USE_YN IS '사용 여부' ;</v>
       </c>
     </row>
-    <row r="394" spans="1:33" ht="20" customHeight="1">
+    <row r="394" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A394" s="55">
         <v>398</v>
       </c>
@@ -38826,7 +38774,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="395" spans="1:33" ht="20" customHeight="1">
+    <row r="395" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A395" s="55">
         <v>399</v>
       </c>
@@ -38912,7 +38860,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="396" spans="1:33" ht="20" customHeight="1">
+    <row r="396" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A396" s="55">
         <v>400</v>
       </c>
@@ -38947,7 +38895,7 @@
       <c r="N396" s="52"/>
       <c r="O396" s="52"/>
       <c r="P396" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q396" s="127"/>
       <c r="R396" s="85"/>
@@ -38996,7 +38944,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="397" spans="1:33" ht="20" customHeight="1">
+    <row r="397" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A397" s="55">
         <v>401</v>
       </c>
@@ -39082,7 +39030,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="398" spans="1:33" ht="20" customHeight="1">
+    <row r="398" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A398" s="55">
         <v>402</v>
       </c>
@@ -39166,7 +39114,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="399" spans="1:33" ht="20" customHeight="1">
+    <row r="399" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A399" s="55">
         <v>403</v>
       </c>
@@ -39199,7 +39147,7 @@
       <c r="N399" s="61"/>
       <c r="O399" s="61"/>
       <c r="P399" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q399" s="127"/>
       <c r="R399" s="82"/>
@@ -39248,7 +39196,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="400" spans="1:33" ht="20" customHeight="1">
+    <row r="400" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A400" s="55">
         <v>404</v>
       </c>
@@ -39336,7 +39284,7 @@
         <v>COMMENT ON COLUMN TB_CMMN_CD_DETAIL.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="401" spans="1:33" ht="20" customHeight="1">
+    <row r="401" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A401" s="55">
         <v>405</v>
       </c>
@@ -39425,7 +39373,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_SN IS '배너 일련번호' ;</v>
       </c>
     </row>
-    <row r="402" spans="1:33" ht="20" customHeight="1">
+    <row r="402" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A402" s="55">
         <v>406</v>
       </c>
@@ -39513,7 +39461,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_CL_CD IS '배너 분류 코드' ;</v>
       </c>
     </row>
-    <row r="403" spans="1:33" ht="20" customHeight="1">
+    <row r="403" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A403" s="55">
         <v>407</v>
       </c>
@@ -39599,7 +39547,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_CL_DETAIL_CD IS '배너 분류 상세 코드' ;</v>
       </c>
     </row>
-    <row r="404" spans="1:33" ht="20" customHeight="1">
+    <row r="404" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A404" s="55">
         <v>408</v>
       </c>
@@ -39688,7 +39636,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_EXPSR_ORDR IS '배너 노출 순서' ;</v>
       </c>
     </row>
-    <row r="405" spans="1:33" ht="20" customHeight="1">
+    <row r="405" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A405" s="55">
         <v>409</v>
       </c>
@@ -39772,7 +39720,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_NM IS '배너 이름' ;</v>
       </c>
     </row>
-    <row r="406" spans="1:33" ht="20" customHeight="1">
+    <row r="406" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A406" s="55">
         <v>410</v>
       </c>
@@ -39854,7 +39802,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_DC IS '배너 설명' ;</v>
       </c>
     </row>
-    <row r="407" spans="1:33" ht="20" customHeight="1">
+    <row r="407" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A407" s="55">
         <v>411</v>
       </c>
@@ -39946,7 +39894,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
-    <row r="408" spans="1:33" ht="20" customHeight="1">
+    <row r="408" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A408" s="55">
         <v>412</v>
       </c>
@@ -40030,7 +39978,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.URL IS '클릭시 이동 URL' ;</v>
       </c>
     </row>
-    <row r="409" spans="1:33" ht="20" customHeight="1">
+    <row r="409" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A409" s="55">
         <v>413</v>
       </c>
@@ -40118,7 +40066,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.CLASS_MAPNG_YN IS '클래스 매핑 여부' ;</v>
       </c>
     </row>
-    <row r="410" spans="1:33" ht="20" customHeight="1">
+    <row r="410" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A410" s="55">
         <v>414</v>
       </c>
@@ -40210,7 +40158,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.CLASS_SN IS '클래스 일련번호' ;</v>
       </c>
     </row>
-    <row r="411" spans="1:33" ht="20" customHeight="1">
+    <row r="411" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A411" s="55">
         <v>415</v>
       </c>
@@ -40296,7 +40244,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.USE_YN IS '사용 여부' ;</v>
       </c>
     </row>
-    <row r="412" spans="1:33" ht="20" customHeight="1">
+    <row r="412" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A412" s="55">
         <v>416</v>
       </c>
@@ -40382,7 +40330,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_PD_SET_YN IS '배너 기간 설정 여부' ;</v>
       </c>
     </row>
-    <row r="413" spans="1:33" ht="20" customHeight="1">
+    <row r="413" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A413" s="55">
         <v>417</v>
       </c>
@@ -40418,7 +40366,7 @@
         <v>106</v>
       </c>
       <c r="Q413" s="127" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="R413" s="90"/>
       <c r="S413" s="109" t="s">
@@ -40466,7 +40414,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_BEGIN_DT IS '배너 시작 일시' ;</v>
       </c>
     </row>
-    <row r="414" spans="1:33" ht="20" customHeight="1">
+    <row r="414" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A414" s="55">
         <v>418</v>
       </c>
@@ -40502,7 +40450,7 @@
         <v>106</v>
       </c>
       <c r="Q414" s="127" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="R414" s="90"/>
       <c r="S414" s="109" t="s">
@@ -40550,7 +40498,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.BANNER_END_DT IS '배너 종료 일시' ;</v>
       </c>
     </row>
-    <row r="415" spans="1:33" ht="20" customHeight="1">
+    <row r="415" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A415" s="55">
         <v>419</v>
       </c>
@@ -40636,7 +40584,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.REGISTER_ID IS '등록자 ID' ;</v>
       </c>
     </row>
-    <row r="416" spans="1:33" ht="20" customHeight="1">
+    <row r="416" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A416" s="55">
         <v>420</v>
       </c>
@@ -40722,7 +40670,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.REGISTER_IP IS '등록자 IP' ;</v>
       </c>
     </row>
-    <row r="417" spans="1:33" ht="20" customHeight="1">
+    <row r="417" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A417" s="55">
         <v>421</v>
       </c>
@@ -40757,7 +40705,7 @@
       <c r="N417" s="52"/>
       <c r="O417" s="52"/>
       <c r="P417" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q417" s="127"/>
       <c r="R417" s="85"/>
@@ -40806,7 +40754,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.REG_DT IS '등록 일시' ;</v>
       </c>
     </row>
-    <row r="418" spans="1:33" ht="20" customHeight="1">
+    <row r="418" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A418" s="55">
         <v>422</v>
       </c>
@@ -40890,7 +40838,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.UPDUSR_ID IS '수정자 ID' ;</v>
       </c>
     </row>
-    <row r="419" spans="1:33" ht="20" customHeight="1">
+    <row r="419" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A419" s="55">
         <v>423</v>
       </c>
@@ -40974,7 +40922,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.UPDUSR_IP IS '수정자 IP' ;</v>
       </c>
     </row>
-    <row r="420" spans="1:33" ht="20" customHeight="1">
+    <row r="420" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A420" s="55">
         <v>424</v>
       </c>
@@ -41007,7 +40955,7 @@
       <c r="N420" s="61"/>
       <c r="O420" s="61"/>
       <c r="P420" s="51" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q420" s="127"/>
       <c r="R420" s="82"/>
@@ -41056,7 +41004,7 @@
         <v>COMMENT ON COLUMN TB_BANNER.UPDT_DT IS '수정 일시' ;</v>
       </c>
     </row>
-    <row r="421" spans="1:33" ht="20" customHeight="1">
+    <row r="421" spans="1:33" ht="20.100000000000001" customHeight="1">
       <c r="A421" s="55">
         <v>425</v>
       </c>
@@ -41540,8 +41488,8 @@
       <c r="H480" s="93"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:X421" xr:uid="{85B6E963-2664-4494-AE6E-E89C8C9EB8F2}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A21:X420">
+  <autoFilter ref="A4:X429" xr:uid="{85B6E963-2664-4494-AE6E-E89C8C9EB8F2}">
+    <sortState ref="A21:X420">
       <sortCondition ref="A4:A421"/>
     </sortState>
   </autoFilter>
@@ -41561,646 +41509,646 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="7" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="7" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="28.83203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="28.77734375" style="6" customWidth="1"/>
     <col min="6" max="6" width="39.6640625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="35.5" style="5" customWidth="1"/>
-    <col min="8" max="253" width="8.83203125" style="5"/>
-    <col min="254" max="254" width="8.83203125" style="5" customWidth="1"/>
-    <col min="255" max="255" width="10.5" style="5" customWidth="1"/>
-    <col min="256" max="256" width="22.1640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" style="5" customWidth="1"/>
+    <col min="8" max="253" width="8.77734375" style="5"/>
+    <col min="254" max="254" width="8.77734375" style="5" customWidth="1"/>
+    <col min="255" max="255" width="10.44140625" style="5" customWidth="1"/>
+    <col min="256" max="256" width="22.109375" style="5" customWidth="1"/>
     <col min="257" max="257" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="7.5" style="5" customWidth="1"/>
-    <col min="259" max="259" width="6.83203125" style="5" customWidth="1"/>
-    <col min="260" max="260" width="7.5" style="5" customWidth="1"/>
-    <col min="261" max="261" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="7.44140625" style="5" customWidth="1"/>
+    <col min="259" max="259" width="6.77734375" style="5" customWidth="1"/>
+    <col min="260" max="260" width="7.44140625" style="5" customWidth="1"/>
+    <col min="261" max="261" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="262" max="262" width="19.33203125" style="5" customWidth="1"/>
-    <col min="263" max="509" width="8.83203125" style="5"/>
-    <col min="510" max="510" width="8.83203125" style="5" customWidth="1"/>
-    <col min="511" max="511" width="10.5" style="5" customWidth="1"/>
-    <col min="512" max="512" width="22.1640625" style="5" customWidth="1"/>
+    <col min="263" max="509" width="8.77734375" style="5"/>
+    <col min="510" max="510" width="8.77734375" style="5" customWidth="1"/>
+    <col min="511" max="511" width="10.44140625" style="5" customWidth="1"/>
+    <col min="512" max="512" width="22.109375" style="5" customWidth="1"/>
     <col min="513" max="513" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="514" max="514" width="7.5" style="5" customWidth="1"/>
-    <col min="515" max="515" width="6.83203125" style="5" customWidth="1"/>
-    <col min="516" max="516" width="7.5" style="5" customWidth="1"/>
-    <col min="517" max="517" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="7.44140625" style="5" customWidth="1"/>
+    <col min="515" max="515" width="6.77734375" style="5" customWidth="1"/>
+    <col min="516" max="516" width="7.44140625" style="5" customWidth="1"/>
+    <col min="517" max="517" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="518" max="518" width="19.33203125" style="5" customWidth="1"/>
-    <col min="519" max="765" width="8.83203125" style="5"/>
-    <col min="766" max="766" width="8.83203125" style="5" customWidth="1"/>
-    <col min="767" max="767" width="10.5" style="5" customWidth="1"/>
-    <col min="768" max="768" width="22.1640625" style="5" customWidth="1"/>
+    <col min="519" max="765" width="8.77734375" style="5"/>
+    <col min="766" max="766" width="8.77734375" style="5" customWidth="1"/>
+    <col min="767" max="767" width="10.44140625" style="5" customWidth="1"/>
+    <col min="768" max="768" width="22.109375" style="5" customWidth="1"/>
     <col min="769" max="769" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="770" max="770" width="7.5" style="5" customWidth="1"/>
-    <col min="771" max="771" width="6.83203125" style="5" customWidth="1"/>
-    <col min="772" max="772" width="7.5" style="5" customWidth="1"/>
-    <col min="773" max="773" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="770" max="770" width="7.44140625" style="5" customWidth="1"/>
+    <col min="771" max="771" width="6.77734375" style="5" customWidth="1"/>
+    <col min="772" max="772" width="7.44140625" style="5" customWidth="1"/>
+    <col min="773" max="773" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="774" max="774" width="19.33203125" style="5" customWidth="1"/>
-    <col min="775" max="1021" width="8.83203125" style="5"/>
-    <col min="1022" max="1022" width="8.83203125" style="5" customWidth="1"/>
-    <col min="1023" max="1023" width="10.5" style="5" customWidth="1"/>
-    <col min="1024" max="1024" width="22.1640625" style="5" customWidth="1"/>
+    <col min="775" max="1021" width="8.77734375" style="5"/>
+    <col min="1022" max="1022" width="8.77734375" style="5" customWidth="1"/>
+    <col min="1023" max="1023" width="10.44140625" style="5" customWidth="1"/>
+    <col min="1024" max="1024" width="22.109375" style="5" customWidth="1"/>
     <col min="1025" max="1025" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="1026" max="1026" width="7.5" style="5" customWidth="1"/>
-    <col min="1027" max="1027" width="6.83203125" style="5" customWidth="1"/>
-    <col min="1028" max="1028" width="7.5" style="5" customWidth="1"/>
-    <col min="1029" max="1029" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1026" max="1026" width="7.44140625" style="5" customWidth="1"/>
+    <col min="1027" max="1027" width="6.77734375" style="5" customWidth="1"/>
+    <col min="1028" max="1028" width="7.44140625" style="5" customWidth="1"/>
+    <col min="1029" max="1029" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="1030" max="1030" width="19.33203125" style="5" customWidth="1"/>
-    <col min="1031" max="1277" width="8.83203125" style="5"/>
-    <col min="1278" max="1278" width="8.83203125" style="5" customWidth="1"/>
-    <col min="1279" max="1279" width="10.5" style="5" customWidth="1"/>
-    <col min="1280" max="1280" width="22.1640625" style="5" customWidth="1"/>
+    <col min="1031" max="1277" width="8.77734375" style="5"/>
+    <col min="1278" max="1278" width="8.77734375" style="5" customWidth="1"/>
+    <col min="1279" max="1279" width="10.44140625" style="5" customWidth="1"/>
+    <col min="1280" max="1280" width="22.109375" style="5" customWidth="1"/>
     <col min="1281" max="1281" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="1282" max="1282" width="7.5" style="5" customWidth="1"/>
-    <col min="1283" max="1283" width="6.83203125" style="5" customWidth="1"/>
-    <col min="1284" max="1284" width="7.5" style="5" customWidth="1"/>
-    <col min="1285" max="1285" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1282" max="1282" width="7.44140625" style="5" customWidth="1"/>
+    <col min="1283" max="1283" width="6.77734375" style="5" customWidth="1"/>
+    <col min="1284" max="1284" width="7.44140625" style="5" customWidth="1"/>
+    <col min="1285" max="1285" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="1286" max="1286" width="19.33203125" style="5" customWidth="1"/>
-    <col min="1287" max="1533" width="8.83203125" style="5"/>
-    <col min="1534" max="1534" width="8.83203125" style="5" customWidth="1"/>
-    <col min="1535" max="1535" width="10.5" style="5" customWidth="1"/>
-    <col min="1536" max="1536" width="22.1640625" style="5" customWidth="1"/>
+    <col min="1287" max="1533" width="8.77734375" style="5"/>
+    <col min="1534" max="1534" width="8.77734375" style="5" customWidth="1"/>
+    <col min="1535" max="1535" width="10.44140625" style="5" customWidth="1"/>
+    <col min="1536" max="1536" width="22.109375" style="5" customWidth="1"/>
     <col min="1537" max="1537" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="1538" max="1538" width="7.5" style="5" customWidth="1"/>
-    <col min="1539" max="1539" width="6.83203125" style="5" customWidth="1"/>
-    <col min="1540" max="1540" width="7.5" style="5" customWidth="1"/>
-    <col min="1541" max="1541" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1538" max="1538" width="7.44140625" style="5" customWidth="1"/>
+    <col min="1539" max="1539" width="6.77734375" style="5" customWidth="1"/>
+    <col min="1540" max="1540" width="7.44140625" style="5" customWidth="1"/>
+    <col min="1541" max="1541" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="1542" max="1542" width="19.33203125" style="5" customWidth="1"/>
-    <col min="1543" max="1789" width="8.83203125" style="5"/>
-    <col min="1790" max="1790" width="8.83203125" style="5" customWidth="1"/>
-    <col min="1791" max="1791" width="10.5" style="5" customWidth="1"/>
-    <col min="1792" max="1792" width="22.1640625" style="5" customWidth="1"/>
+    <col min="1543" max="1789" width="8.77734375" style="5"/>
+    <col min="1790" max="1790" width="8.77734375" style="5" customWidth="1"/>
+    <col min="1791" max="1791" width="10.44140625" style="5" customWidth="1"/>
+    <col min="1792" max="1792" width="22.109375" style="5" customWidth="1"/>
     <col min="1793" max="1793" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="1794" max="1794" width="7.5" style="5" customWidth="1"/>
-    <col min="1795" max="1795" width="6.83203125" style="5" customWidth="1"/>
-    <col min="1796" max="1796" width="7.5" style="5" customWidth="1"/>
-    <col min="1797" max="1797" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1794" max="1794" width="7.44140625" style="5" customWidth="1"/>
+    <col min="1795" max="1795" width="6.77734375" style="5" customWidth="1"/>
+    <col min="1796" max="1796" width="7.44140625" style="5" customWidth="1"/>
+    <col min="1797" max="1797" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="1798" max="1798" width="19.33203125" style="5" customWidth="1"/>
-    <col min="1799" max="2045" width="8.83203125" style="5"/>
-    <col min="2046" max="2046" width="8.83203125" style="5" customWidth="1"/>
-    <col min="2047" max="2047" width="10.5" style="5" customWidth="1"/>
-    <col min="2048" max="2048" width="22.1640625" style="5" customWidth="1"/>
+    <col min="1799" max="2045" width="8.77734375" style="5"/>
+    <col min="2046" max="2046" width="8.77734375" style="5" customWidth="1"/>
+    <col min="2047" max="2047" width="10.44140625" style="5" customWidth="1"/>
+    <col min="2048" max="2048" width="22.109375" style="5" customWidth="1"/>
     <col min="2049" max="2049" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2050" max="2050" width="7.5" style="5" customWidth="1"/>
-    <col min="2051" max="2051" width="6.83203125" style="5" customWidth="1"/>
-    <col min="2052" max="2052" width="7.5" style="5" customWidth="1"/>
-    <col min="2053" max="2053" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2050" max="2050" width="7.44140625" style="5" customWidth="1"/>
+    <col min="2051" max="2051" width="6.77734375" style="5" customWidth="1"/>
+    <col min="2052" max="2052" width="7.44140625" style="5" customWidth="1"/>
+    <col min="2053" max="2053" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2054" max="2054" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2055" max="2301" width="8.83203125" style="5"/>
-    <col min="2302" max="2302" width="8.83203125" style="5" customWidth="1"/>
-    <col min="2303" max="2303" width="10.5" style="5" customWidth="1"/>
-    <col min="2304" max="2304" width="22.1640625" style="5" customWidth="1"/>
+    <col min="2055" max="2301" width="8.77734375" style="5"/>
+    <col min="2302" max="2302" width="8.77734375" style="5" customWidth="1"/>
+    <col min="2303" max="2303" width="10.44140625" style="5" customWidth="1"/>
+    <col min="2304" max="2304" width="22.109375" style="5" customWidth="1"/>
     <col min="2305" max="2305" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2306" max="2306" width="7.5" style="5" customWidth="1"/>
-    <col min="2307" max="2307" width="6.83203125" style="5" customWidth="1"/>
-    <col min="2308" max="2308" width="7.5" style="5" customWidth="1"/>
-    <col min="2309" max="2309" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2306" max="2306" width="7.44140625" style="5" customWidth="1"/>
+    <col min="2307" max="2307" width="6.77734375" style="5" customWidth="1"/>
+    <col min="2308" max="2308" width="7.44140625" style="5" customWidth="1"/>
+    <col min="2309" max="2309" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2310" max="2310" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2311" max="2557" width="8.83203125" style="5"/>
-    <col min="2558" max="2558" width="8.83203125" style="5" customWidth="1"/>
-    <col min="2559" max="2559" width="10.5" style="5" customWidth="1"/>
-    <col min="2560" max="2560" width="22.1640625" style="5" customWidth="1"/>
+    <col min="2311" max="2557" width="8.77734375" style="5"/>
+    <col min="2558" max="2558" width="8.77734375" style="5" customWidth="1"/>
+    <col min="2559" max="2559" width="10.44140625" style="5" customWidth="1"/>
+    <col min="2560" max="2560" width="22.109375" style="5" customWidth="1"/>
     <col min="2561" max="2561" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2562" max="2562" width="7.5" style="5" customWidth="1"/>
-    <col min="2563" max="2563" width="6.83203125" style="5" customWidth="1"/>
-    <col min="2564" max="2564" width="7.5" style="5" customWidth="1"/>
-    <col min="2565" max="2565" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2562" max="2562" width="7.44140625" style="5" customWidth="1"/>
+    <col min="2563" max="2563" width="6.77734375" style="5" customWidth="1"/>
+    <col min="2564" max="2564" width="7.44140625" style="5" customWidth="1"/>
+    <col min="2565" max="2565" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2566" max="2566" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2567" max="2813" width="8.83203125" style="5"/>
-    <col min="2814" max="2814" width="8.83203125" style="5" customWidth="1"/>
-    <col min="2815" max="2815" width="10.5" style="5" customWidth="1"/>
-    <col min="2816" max="2816" width="22.1640625" style="5" customWidth="1"/>
+    <col min="2567" max="2813" width="8.77734375" style="5"/>
+    <col min="2814" max="2814" width="8.77734375" style="5" customWidth="1"/>
+    <col min="2815" max="2815" width="10.44140625" style="5" customWidth="1"/>
+    <col min="2816" max="2816" width="22.109375" style="5" customWidth="1"/>
     <col min="2817" max="2817" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2818" max="2818" width="7.5" style="5" customWidth="1"/>
-    <col min="2819" max="2819" width="6.83203125" style="5" customWidth="1"/>
-    <col min="2820" max="2820" width="7.5" style="5" customWidth="1"/>
-    <col min="2821" max="2821" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2818" max="2818" width="7.44140625" style="5" customWidth="1"/>
+    <col min="2819" max="2819" width="6.77734375" style="5" customWidth="1"/>
+    <col min="2820" max="2820" width="7.44140625" style="5" customWidth="1"/>
+    <col min="2821" max="2821" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2822" max="2822" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2823" max="3069" width="8.83203125" style="5"/>
-    <col min="3070" max="3070" width="8.83203125" style="5" customWidth="1"/>
-    <col min="3071" max="3071" width="10.5" style="5" customWidth="1"/>
-    <col min="3072" max="3072" width="22.1640625" style="5" customWidth="1"/>
+    <col min="2823" max="3069" width="8.77734375" style="5"/>
+    <col min="3070" max="3070" width="8.77734375" style="5" customWidth="1"/>
+    <col min="3071" max="3071" width="10.44140625" style="5" customWidth="1"/>
+    <col min="3072" max="3072" width="22.109375" style="5" customWidth="1"/>
     <col min="3073" max="3073" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3074" max="3074" width="7.5" style="5" customWidth="1"/>
-    <col min="3075" max="3075" width="6.83203125" style="5" customWidth="1"/>
-    <col min="3076" max="3076" width="7.5" style="5" customWidth="1"/>
-    <col min="3077" max="3077" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3074" max="3074" width="7.44140625" style="5" customWidth="1"/>
+    <col min="3075" max="3075" width="6.77734375" style="5" customWidth="1"/>
+    <col min="3076" max="3076" width="7.44140625" style="5" customWidth="1"/>
+    <col min="3077" max="3077" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3078" max="3078" width="19.33203125" style="5" customWidth="1"/>
-    <col min="3079" max="3325" width="8.83203125" style="5"/>
-    <col min="3326" max="3326" width="8.83203125" style="5" customWidth="1"/>
-    <col min="3327" max="3327" width="10.5" style="5" customWidth="1"/>
-    <col min="3328" max="3328" width="22.1640625" style="5" customWidth="1"/>
+    <col min="3079" max="3325" width="8.77734375" style="5"/>
+    <col min="3326" max="3326" width="8.77734375" style="5" customWidth="1"/>
+    <col min="3327" max="3327" width="10.44140625" style="5" customWidth="1"/>
+    <col min="3328" max="3328" width="22.109375" style="5" customWidth="1"/>
     <col min="3329" max="3329" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3330" max="3330" width="7.5" style="5" customWidth="1"/>
-    <col min="3331" max="3331" width="6.83203125" style="5" customWidth="1"/>
-    <col min="3332" max="3332" width="7.5" style="5" customWidth="1"/>
-    <col min="3333" max="3333" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3330" max="3330" width="7.44140625" style="5" customWidth="1"/>
+    <col min="3331" max="3331" width="6.77734375" style="5" customWidth="1"/>
+    <col min="3332" max="3332" width="7.44140625" style="5" customWidth="1"/>
+    <col min="3333" max="3333" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3334" max="3334" width="19.33203125" style="5" customWidth="1"/>
-    <col min="3335" max="3581" width="8.83203125" style="5"/>
-    <col min="3582" max="3582" width="8.83203125" style="5" customWidth="1"/>
-    <col min="3583" max="3583" width="10.5" style="5" customWidth="1"/>
-    <col min="3584" max="3584" width="22.1640625" style="5" customWidth="1"/>
+    <col min="3335" max="3581" width="8.77734375" style="5"/>
+    <col min="3582" max="3582" width="8.77734375" style="5" customWidth="1"/>
+    <col min="3583" max="3583" width="10.44140625" style="5" customWidth="1"/>
+    <col min="3584" max="3584" width="22.109375" style="5" customWidth="1"/>
     <col min="3585" max="3585" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3586" max="3586" width="7.5" style="5" customWidth="1"/>
-    <col min="3587" max="3587" width="6.83203125" style="5" customWidth="1"/>
-    <col min="3588" max="3588" width="7.5" style="5" customWidth="1"/>
-    <col min="3589" max="3589" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3586" max="3586" width="7.44140625" style="5" customWidth="1"/>
+    <col min="3587" max="3587" width="6.77734375" style="5" customWidth="1"/>
+    <col min="3588" max="3588" width="7.44140625" style="5" customWidth="1"/>
+    <col min="3589" max="3589" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3590" max="3590" width="19.33203125" style="5" customWidth="1"/>
-    <col min="3591" max="3837" width="8.83203125" style="5"/>
-    <col min="3838" max="3838" width="8.83203125" style="5" customWidth="1"/>
-    <col min="3839" max="3839" width="10.5" style="5" customWidth="1"/>
-    <col min="3840" max="3840" width="22.1640625" style="5" customWidth="1"/>
+    <col min="3591" max="3837" width="8.77734375" style="5"/>
+    <col min="3838" max="3838" width="8.77734375" style="5" customWidth="1"/>
+    <col min="3839" max="3839" width="10.44140625" style="5" customWidth="1"/>
+    <col min="3840" max="3840" width="22.109375" style="5" customWidth="1"/>
     <col min="3841" max="3841" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3842" max="3842" width="7.5" style="5" customWidth="1"/>
-    <col min="3843" max="3843" width="6.83203125" style="5" customWidth="1"/>
-    <col min="3844" max="3844" width="7.5" style="5" customWidth="1"/>
-    <col min="3845" max="3845" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3842" max="3842" width="7.44140625" style="5" customWidth="1"/>
+    <col min="3843" max="3843" width="6.77734375" style="5" customWidth="1"/>
+    <col min="3844" max="3844" width="7.44140625" style="5" customWidth="1"/>
+    <col min="3845" max="3845" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3846" max="3846" width="19.33203125" style="5" customWidth="1"/>
-    <col min="3847" max="4093" width="8.83203125" style="5"/>
-    <col min="4094" max="4094" width="8.83203125" style="5" customWidth="1"/>
-    <col min="4095" max="4095" width="10.5" style="5" customWidth="1"/>
-    <col min="4096" max="4096" width="22.1640625" style="5" customWidth="1"/>
+    <col min="3847" max="4093" width="8.77734375" style="5"/>
+    <col min="4094" max="4094" width="8.77734375" style="5" customWidth="1"/>
+    <col min="4095" max="4095" width="10.44140625" style="5" customWidth="1"/>
+    <col min="4096" max="4096" width="22.109375" style="5" customWidth="1"/>
     <col min="4097" max="4097" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4098" max="4098" width="7.5" style="5" customWidth="1"/>
-    <col min="4099" max="4099" width="6.83203125" style="5" customWidth="1"/>
-    <col min="4100" max="4100" width="7.5" style="5" customWidth="1"/>
-    <col min="4101" max="4101" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4098" max="4098" width="7.44140625" style="5" customWidth="1"/>
+    <col min="4099" max="4099" width="6.77734375" style="5" customWidth="1"/>
+    <col min="4100" max="4100" width="7.44140625" style="5" customWidth="1"/>
+    <col min="4101" max="4101" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="4102" max="4102" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4103" max="4349" width="8.83203125" style="5"/>
-    <col min="4350" max="4350" width="8.83203125" style="5" customWidth="1"/>
-    <col min="4351" max="4351" width="10.5" style="5" customWidth="1"/>
-    <col min="4352" max="4352" width="22.1640625" style="5" customWidth="1"/>
+    <col min="4103" max="4349" width="8.77734375" style="5"/>
+    <col min="4350" max="4350" width="8.77734375" style="5" customWidth="1"/>
+    <col min="4351" max="4351" width="10.44140625" style="5" customWidth="1"/>
+    <col min="4352" max="4352" width="22.109375" style="5" customWidth="1"/>
     <col min="4353" max="4353" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4354" max="4354" width="7.5" style="5" customWidth="1"/>
-    <col min="4355" max="4355" width="6.83203125" style="5" customWidth="1"/>
-    <col min="4356" max="4356" width="7.5" style="5" customWidth="1"/>
-    <col min="4357" max="4357" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4354" max="4354" width="7.44140625" style="5" customWidth="1"/>
+    <col min="4355" max="4355" width="6.77734375" style="5" customWidth="1"/>
+    <col min="4356" max="4356" width="7.44140625" style="5" customWidth="1"/>
+    <col min="4357" max="4357" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="4358" max="4358" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4359" max="4605" width="8.83203125" style="5"/>
-    <col min="4606" max="4606" width="8.83203125" style="5" customWidth="1"/>
-    <col min="4607" max="4607" width="10.5" style="5" customWidth="1"/>
-    <col min="4608" max="4608" width="22.1640625" style="5" customWidth="1"/>
+    <col min="4359" max="4605" width="8.77734375" style="5"/>
+    <col min="4606" max="4606" width="8.77734375" style="5" customWidth="1"/>
+    <col min="4607" max="4607" width="10.44140625" style="5" customWidth="1"/>
+    <col min="4608" max="4608" width="22.109375" style="5" customWidth="1"/>
     <col min="4609" max="4609" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4610" max="4610" width="7.5" style="5" customWidth="1"/>
-    <col min="4611" max="4611" width="6.83203125" style="5" customWidth="1"/>
-    <col min="4612" max="4612" width="7.5" style="5" customWidth="1"/>
-    <col min="4613" max="4613" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4610" max="4610" width="7.44140625" style="5" customWidth="1"/>
+    <col min="4611" max="4611" width="6.77734375" style="5" customWidth="1"/>
+    <col min="4612" max="4612" width="7.44140625" style="5" customWidth="1"/>
+    <col min="4613" max="4613" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="4614" max="4614" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4615" max="4861" width="8.83203125" style="5"/>
-    <col min="4862" max="4862" width="8.83203125" style="5" customWidth="1"/>
-    <col min="4863" max="4863" width="10.5" style="5" customWidth="1"/>
-    <col min="4864" max="4864" width="22.1640625" style="5" customWidth="1"/>
+    <col min="4615" max="4861" width="8.77734375" style="5"/>
+    <col min="4862" max="4862" width="8.77734375" style="5" customWidth="1"/>
+    <col min="4863" max="4863" width="10.44140625" style="5" customWidth="1"/>
+    <col min="4864" max="4864" width="22.109375" style="5" customWidth="1"/>
     <col min="4865" max="4865" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4866" max="4866" width="7.5" style="5" customWidth="1"/>
-    <col min="4867" max="4867" width="6.83203125" style="5" customWidth="1"/>
-    <col min="4868" max="4868" width="7.5" style="5" customWidth="1"/>
-    <col min="4869" max="4869" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4866" max="4866" width="7.44140625" style="5" customWidth="1"/>
+    <col min="4867" max="4867" width="6.77734375" style="5" customWidth="1"/>
+    <col min="4868" max="4868" width="7.44140625" style="5" customWidth="1"/>
+    <col min="4869" max="4869" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="4870" max="4870" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4871" max="5117" width="8.83203125" style="5"/>
-    <col min="5118" max="5118" width="8.83203125" style="5" customWidth="1"/>
-    <col min="5119" max="5119" width="10.5" style="5" customWidth="1"/>
-    <col min="5120" max="5120" width="22.1640625" style="5" customWidth="1"/>
+    <col min="4871" max="5117" width="8.77734375" style="5"/>
+    <col min="5118" max="5118" width="8.77734375" style="5" customWidth="1"/>
+    <col min="5119" max="5119" width="10.44140625" style="5" customWidth="1"/>
+    <col min="5120" max="5120" width="22.109375" style="5" customWidth="1"/>
     <col min="5121" max="5121" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5122" max="5122" width="7.5" style="5" customWidth="1"/>
-    <col min="5123" max="5123" width="6.83203125" style="5" customWidth="1"/>
-    <col min="5124" max="5124" width="7.5" style="5" customWidth="1"/>
-    <col min="5125" max="5125" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5122" max="5122" width="7.44140625" style="5" customWidth="1"/>
+    <col min="5123" max="5123" width="6.77734375" style="5" customWidth="1"/>
+    <col min="5124" max="5124" width="7.44140625" style="5" customWidth="1"/>
+    <col min="5125" max="5125" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="5126" max="5126" width="19.33203125" style="5" customWidth="1"/>
-    <col min="5127" max="5373" width="8.83203125" style="5"/>
-    <col min="5374" max="5374" width="8.83203125" style="5" customWidth="1"/>
-    <col min="5375" max="5375" width="10.5" style="5" customWidth="1"/>
-    <col min="5376" max="5376" width="22.1640625" style="5" customWidth="1"/>
+    <col min="5127" max="5373" width="8.77734375" style="5"/>
+    <col min="5374" max="5374" width="8.77734375" style="5" customWidth="1"/>
+    <col min="5375" max="5375" width="10.44140625" style="5" customWidth="1"/>
+    <col min="5376" max="5376" width="22.109375" style="5" customWidth="1"/>
     <col min="5377" max="5377" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5378" max="5378" width="7.5" style="5" customWidth="1"/>
-    <col min="5379" max="5379" width="6.83203125" style="5" customWidth="1"/>
-    <col min="5380" max="5380" width="7.5" style="5" customWidth="1"/>
-    <col min="5381" max="5381" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5378" max="5378" width="7.44140625" style="5" customWidth="1"/>
+    <col min="5379" max="5379" width="6.77734375" style="5" customWidth="1"/>
+    <col min="5380" max="5380" width="7.44140625" style="5" customWidth="1"/>
+    <col min="5381" max="5381" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="5382" max="5382" width="19.33203125" style="5" customWidth="1"/>
-    <col min="5383" max="5629" width="8.83203125" style="5"/>
-    <col min="5630" max="5630" width="8.83203125" style="5" customWidth="1"/>
-    <col min="5631" max="5631" width="10.5" style="5" customWidth="1"/>
-    <col min="5632" max="5632" width="22.1640625" style="5" customWidth="1"/>
+    <col min="5383" max="5629" width="8.77734375" style="5"/>
+    <col min="5630" max="5630" width="8.77734375" style="5" customWidth="1"/>
+    <col min="5631" max="5631" width="10.44140625" style="5" customWidth="1"/>
+    <col min="5632" max="5632" width="22.109375" style="5" customWidth="1"/>
     <col min="5633" max="5633" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5634" max="5634" width="7.5" style="5" customWidth="1"/>
-    <col min="5635" max="5635" width="6.83203125" style="5" customWidth="1"/>
-    <col min="5636" max="5636" width="7.5" style="5" customWidth="1"/>
-    <col min="5637" max="5637" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5634" max="5634" width="7.44140625" style="5" customWidth="1"/>
+    <col min="5635" max="5635" width="6.77734375" style="5" customWidth="1"/>
+    <col min="5636" max="5636" width="7.44140625" style="5" customWidth="1"/>
+    <col min="5637" max="5637" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="5638" max="5638" width="19.33203125" style="5" customWidth="1"/>
-    <col min="5639" max="5885" width="8.83203125" style="5"/>
-    <col min="5886" max="5886" width="8.83203125" style="5" customWidth="1"/>
-    <col min="5887" max="5887" width="10.5" style="5" customWidth="1"/>
-    <col min="5888" max="5888" width="22.1640625" style="5" customWidth="1"/>
+    <col min="5639" max="5885" width="8.77734375" style="5"/>
+    <col min="5886" max="5886" width="8.77734375" style="5" customWidth="1"/>
+    <col min="5887" max="5887" width="10.44140625" style="5" customWidth="1"/>
+    <col min="5888" max="5888" width="22.109375" style="5" customWidth="1"/>
     <col min="5889" max="5889" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5890" max="5890" width="7.5" style="5" customWidth="1"/>
-    <col min="5891" max="5891" width="6.83203125" style="5" customWidth="1"/>
-    <col min="5892" max="5892" width="7.5" style="5" customWidth="1"/>
-    <col min="5893" max="5893" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5890" max="5890" width="7.44140625" style="5" customWidth="1"/>
+    <col min="5891" max="5891" width="6.77734375" style="5" customWidth="1"/>
+    <col min="5892" max="5892" width="7.44140625" style="5" customWidth="1"/>
+    <col min="5893" max="5893" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="5894" max="5894" width="19.33203125" style="5" customWidth="1"/>
-    <col min="5895" max="6141" width="8.83203125" style="5"/>
-    <col min="6142" max="6142" width="8.83203125" style="5" customWidth="1"/>
-    <col min="6143" max="6143" width="10.5" style="5" customWidth="1"/>
-    <col min="6144" max="6144" width="22.1640625" style="5" customWidth="1"/>
+    <col min="5895" max="6141" width="8.77734375" style="5"/>
+    <col min="6142" max="6142" width="8.77734375" style="5" customWidth="1"/>
+    <col min="6143" max="6143" width="10.44140625" style="5" customWidth="1"/>
+    <col min="6144" max="6144" width="22.109375" style="5" customWidth="1"/>
     <col min="6145" max="6145" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6146" max="6146" width="7.5" style="5" customWidth="1"/>
-    <col min="6147" max="6147" width="6.83203125" style="5" customWidth="1"/>
-    <col min="6148" max="6148" width="7.5" style="5" customWidth="1"/>
-    <col min="6149" max="6149" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6146" max="6146" width="7.44140625" style="5" customWidth="1"/>
+    <col min="6147" max="6147" width="6.77734375" style="5" customWidth="1"/>
+    <col min="6148" max="6148" width="7.44140625" style="5" customWidth="1"/>
+    <col min="6149" max="6149" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="6150" max="6150" width="19.33203125" style="5" customWidth="1"/>
-    <col min="6151" max="6397" width="8.83203125" style="5"/>
-    <col min="6398" max="6398" width="8.83203125" style="5" customWidth="1"/>
-    <col min="6399" max="6399" width="10.5" style="5" customWidth="1"/>
-    <col min="6400" max="6400" width="22.1640625" style="5" customWidth="1"/>
+    <col min="6151" max="6397" width="8.77734375" style="5"/>
+    <col min="6398" max="6398" width="8.77734375" style="5" customWidth="1"/>
+    <col min="6399" max="6399" width="10.44140625" style="5" customWidth="1"/>
+    <col min="6400" max="6400" width="22.109375" style="5" customWidth="1"/>
     <col min="6401" max="6401" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6402" max="6402" width="7.5" style="5" customWidth="1"/>
-    <col min="6403" max="6403" width="6.83203125" style="5" customWidth="1"/>
-    <col min="6404" max="6404" width="7.5" style="5" customWidth="1"/>
-    <col min="6405" max="6405" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6402" max="6402" width="7.44140625" style="5" customWidth="1"/>
+    <col min="6403" max="6403" width="6.77734375" style="5" customWidth="1"/>
+    <col min="6404" max="6404" width="7.44140625" style="5" customWidth="1"/>
+    <col min="6405" max="6405" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="6406" max="6406" width="19.33203125" style="5" customWidth="1"/>
-    <col min="6407" max="6653" width="8.83203125" style="5"/>
-    <col min="6654" max="6654" width="8.83203125" style="5" customWidth="1"/>
-    <col min="6655" max="6655" width="10.5" style="5" customWidth="1"/>
-    <col min="6656" max="6656" width="22.1640625" style="5" customWidth="1"/>
+    <col min="6407" max="6653" width="8.77734375" style="5"/>
+    <col min="6654" max="6654" width="8.77734375" style="5" customWidth="1"/>
+    <col min="6655" max="6655" width="10.44140625" style="5" customWidth="1"/>
+    <col min="6656" max="6656" width="22.109375" style="5" customWidth="1"/>
     <col min="6657" max="6657" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6658" max="6658" width="7.5" style="5" customWidth="1"/>
-    <col min="6659" max="6659" width="6.83203125" style="5" customWidth="1"/>
-    <col min="6660" max="6660" width="7.5" style="5" customWidth="1"/>
-    <col min="6661" max="6661" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6658" max="6658" width="7.44140625" style="5" customWidth="1"/>
+    <col min="6659" max="6659" width="6.77734375" style="5" customWidth="1"/>
+    <col min="6660" max="6660" width="7.44140625" style="5" customWidth="1"/>
+    <col min="6661" max="6661" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="6662" max="6662" width="19.33203125" style="5" customWidth="1"/>
-    <col min="6663" max="6909" width="8.83203125" style="5"/>
-    <col min="6910" max="6910" width="8.83203125" style="5" customWidth="1"/>
-    <col min="6911" max="6911" width="10.5" style="5" customWidth="1"/>
-    <col min="6912" max="6912" width="22.1640625" style="5" customWidth="1"/>
+    <col min="6663" max="6909" width="8.77734375" style="5"/>
+    <col min="6910" max="6910" width="8.77734375" style="5" customWidth="1"/>
+    <col min="6911" max="6911" width="10.44140625" style="5" customWidth="1"/>
+    <col min="6912" max="6912" width="22.109375" style="5" customWidth="1"/>
     <col min="6913" max="6913" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6914" max="6914" width="7.5" style="5" customWidth="1"/>
-    <col min="6915" max="6915" width="6.83203125" style="5" customWidth="1"/>
-    <col min="6916" max="6916" width="7.5" style="5" customWidth="1"/>
-    <col min="6917" max="6917" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6914" max="6914" width="7.44140625" style="5" customWidth="1"/>
+    <col min="6915" max="6915" width="6.77734375" style="5" customWidth="1"/>
+    <col min="6916" max="6916" width="7.44140625" style="5" customWidth="1"/>
+    <col min="6917" max="6917" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="6918" max="6918" width="19.33203125" style="5" customWidth="1"/>
-    <col min="6919" max="7165" width="8.83203125" style="5"/>
-    <col min="7166" max="7166" width="8.83203125" style="5" customWidth="1"/>
-    <col min="7167" max="7167" width="10.5" style="5" customWidth="1"/>
-    <col min="7168" max="7168" width="22.1640625" style="5" customWidth="1"/>
+    <col min="6919" max="7165" width="8.77734375" style="5"/>
+    <col min="7166" max="7166" width="8.77734375" style="5" customWidth="1"/>
+    <col min="7167" max="7167" width="10.44140625" style="5" customWidth="1"/>
+    <col min="7168" max="7168" width="22.109375" style="5" customWidth="1"/>
     <col min="7169" max="7169" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7170" max="7170" width="7.5" style="5" customWidth="1"/>
-    <col min="7171" max="7171" width="6.83203125" style="5" customWidth="1"/>
-    <col min="7172" max="7172" width="7.5" style="5" customWidth="1"/>
-    <col min="7173" max="7173" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7170" max="7170" width="7.44140625" style="5" customWidth="1"/>
+    <col min="7171" max="7171" width="6.77734375" style="5" customWidth="1"/>
+    <col min="7172" max="7172" width="7.44140625" style="5" customWidth="1"/>
+    <col min="7173" max="7173" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7174" max="7174" width="19.33203125" style="5" customWidth="1"/>
-    <col min="7175" max="7421" width="8.83203125" style="5"/>
-    <col min="7422" max="7422" width="8.83203125" style="5" customWidth="1"/>
-    <col min="7423" max="7423" width="10.5" style="5" customWidth="1"/>
-    <col min="7424" max="7424" width="22.1640625" style="5" customWidth="1"/>
+    <col min="7175" max="7421" width="8.77734375" style="5"/>
+    <col min="7422" max="7422" width="8.77734375" style="5" customWidth="1"/>
+    <col min="7423" max="7423" width="10.44140625" style="5" customWidth="1"/>
+    <col min="7424" max="7424" width="22.109375" style="5" customWidth="1"/>
     <col min="7425" max="7425" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7426" max="7426" width="7.5" style="5" customWidth="1"/>
-    <col min="7427" max="7427" width="6.83203125" style="5" customWidth="1"/>
-    <col min="7428" max="7428" width="7.5" style="5" customWidth="1"/>
-    <col min="7429" max="7429" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7426" max="7426" width="7.44140625" style="5" customWidth="1"/>
+    <col min="7427" max="7427" width="6.77734375" style="5" customWidth="1"/>
+    <col min="7428" max="7428" width="7.44140625" style="5" customWidth="1"/>
+    <col min="7429" max="7429" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7430" max="7430" width="19.33203125" style="5" customWidth="1"/>
-    <col min="7431" max="7677" width="8.83203125" style="5"/>
-    <col min="7678" max="7678" width="8.83203125" style="5" customWidth="1"/>
-    <col min="7679" max="7679" width="10.5" style="5" customWidth="1"/>
-    <col min="7680" max="7680" width="22.1640625" style="5" customWidth="1"/>
+    <col min="7431" max="7677" width="8.77734375" style="5"/>
+    <col min="7678" max="7678" width="8.77734375" style="5" customWidth="1"/>
+    <col min="7679" max="7679" width="10.44140625" style="5" customWidth="1"/>
+    <col min="7680" max="7680" width="22.109375" style="5" customWidth="1"/>
     <col min="7681" max="7681" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7682" max="7682" width="7.5" style="5" customWidth="1"/>
-    <col min="7683" max="7683" width="6.83203125" style="5" customWidth="1"/>
-    <col min="7684" max="7684" width="7.5" style="5" customWidth="1"/>
-    <col min="7685" max="7685" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7682" max="7682" width="7.44140625" style="5" customWidth="1"/>
+    <col min="7683" max="7683" width="6.77734375" style="5" customWidth="1"/>
+    <col min="7684" max="7684" width="7.44140625" style="5" customWidth="1"/>
+    <col min="7685" max="7685" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7686" max="7686" width="19.33203125" style="5" customWidth="1"/>
-    <col min="7687" max="7933" width="8.83203125" style="5"/>
-    <col min="7934" max="7934" width="8.83203125" style="5" customWidth="1"/>
-    <col min="7935" max="7935" width="10.5" style="5" customWidth="1"/>
-    <col min="7936" max="7936" width="22.1640625" style="5" customWidth="1"/>
+    <col min="7687" max="7933" width="8.77734375" style="5"/>
+    <col min="7934" max="7934" width="8.77734375" style="5" customWidth="1"/>
+    <col min="7935" max="7935" width="10.44140625" style="5" customWidth="1"/>
+    <col min="7936" max="7936" width="22.109375" style="5" customWidth="1"/>
     <col min="7937" max="7937" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7938" max="7938" width="7.5" style="5" customWidth="1"/>
-    <col min="7939" max="7939" width="6.83203125" style="5" customWidth="1"/>
-    <col min="7940" max="7940" width="7.5" style="5" customWidth="1"/>
-    <col min="7941" max="7941" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7938" max="7938" width="7.44140625" style="5" customWidth="1"/>
+    <col min="7939" max="7939" width="6.77734375" style="5" customWidth="1"/>
+    <col min="7940" max="7940" width="7.44140625" style="5" customWidth="1"/>
+    <col min="7941" max="7941" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7942" max="7942" width="19.33203125" style="5" customWidth="1"/>
-    <col min="7943" max="8189" width="8.83203125" style="5"/>
-    <col min="8190" max="8190" width="8.83203125" style="5" customWidth="1"/>
-    <col min="8191" max="8191" width="10.5" style="5" customWidth="1"/>
-    <col min="8192" max="8192" width="22.1640625" style="5" customWidth="1"/>
+    <col min="7943" max="8189" width="8.77734375" style="5"/>
+    <col min="8190" max="8190" width="8.77734375" style="5" customWidth="1"/>
+    <col min="8191" max="8191" width="10.44140625" style="5" customWidth="1"/>
+    <col min="8192" max="8192" width="22.109375" style="5" customWidth="1"/>
     <col min="8193" max="8193" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8194" max="8194" width="7.5" style="5" customWidth="1"/>
-    <col min="8195" max="8195" width="6.83203125" style="5" customWidth="1"/>
-    <col min="8196" max="8196" width="7.5" style="5" customWidth="1"/>
-    <col min="8197" max="8197" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8194" max="8194" width="7.44140625" style="5" customWidth="1"/>
+    <col min="8195" max="8195" width="6.77734375" style="5" customWidth="1"/>
+    <col min="8196" max="8196" width="7.44140625" style="5" customWidth="1"/>
+    <col min="8197" max="8197" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="8198" max="8198" width="19.33203125" style="5" customWidth="1"/>
-    <col min="8199" max="8445" width="8.83203125" style="5"/>
-    <col min="8446" max="8446" width="8.83203125" style="5" customWidth="1"/>
-    <col min="8447" max="8447" width="10.5" style="5" customWidth="1"/>
-    <col min="8448" max="8448" width="22.1640625" style="5" customWidth="1"/>
+    <col min="8199" max="8445" width="8.77734375" style="5"/>
+    <col min="8446" max="8446" width="8.77734375" style="5" customWidth="1"/>
+    <col min="8447" max="8447" width="10.44140625" style="5" customWidth="1"/>
+    <col min="8448" max="8448" width="22.109375" style="5" customWidth="1"/>
     <col min="8449" max="8449" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8450" max="8450" width="7.5" style="5" customWidth="1"/>
-    <col min="8451" max="8451" width="6.83203125" style="5" customWidth="1"/>
-    <col min="8452" max="8452" width="7.5" style="5" customWidth="1"/>
-    <col min="8453" max="8453" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8450" max="8450" width="7.44140625" style="5" customWidth="1"/>
+    <col min="8451" max="8451" width="6.77734375" style="5" customWidth="1"/>
+    <col min="8452" max="8452" width="7.44140625" style="5" customWidth="1"/>
+    <col min="8453" max="8453" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="8454" max="8454" width="19.33203125" style="5" customWidth="1"/>
-    <col min="8455" max="8701" width="8.83203125" style="5"/>
-    <col min="8702" max="8702" width="8.83203125" style="5" customWidth="1"/>
-    <col min="8703" max="8703" width="10.5" style="5" customWidth="1"/>
-    <col min="8704" max="8704" width="22.1640625" style="5" customWidth="1"/>
+    <col min="8455" max="8701" width="8.77734375" style="5"/>
+    <col min="8702" max="8702" width="8.77734375" style="5" customWidth="1"/>
+    <col min="8703" max="8703" width="10.44140625" style="5" customWidth="1"/>
+    <col min="8704" max="8704" width="22.109375" style="5" customWidth="1"/>
     <col min="8705" max="8705" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8706" max="8706" width="7.5" style="5" customWidth="1"/>
-    <col min="8707" max="8707" width="6.83203125" style="5" customWidth="1"/>
-    <col min="8708" max="8708" width="7.5" style="5" customWidth="1"/>
-    <col min="8709" max="8709" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8706" max="8706" width="7.44140625" style="5" customWidth="1"/>
+    <col min="8707" max="8707" width="6.77734375" style="5" customWidth="1"/>
+    <col min="8708" max="8708" width="7.44140625" style="5" customWidth="1"/>
+    <col min="8709" max="8709" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="8710" max="8710" width="19.33203125" style="5" customWidth="1"/>
-    <col min="8711" max="8957" width="8.83203125" style="5"/>
-    <col min="8958" max="8958" width="8.83203125" style="5" customWidth="1"/>
-    <col min="8959" max="8959" width="10.5" style="5" customWidth="1"/>
-    <col min="8960" max="8960" width="22.1640625" style="5" customWidth="1"/>
+    <col min="8711" max="8957" width="8.77734375" style="5"/>
+    <col min="8958" max="8958" width="8.77734375" style="5" customWidth="1"/>
+    <col min="8959" max="8959" width="10.44140625" style="5" customWidth="1"/>
+    <col min="8960" max="8960" width="22.109375" style="5" customWidth="1"/>
     <col min="8961" max="8961" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8962" max="8962" width="7.5" style="5" customWidth="1"/>
-    <col min="8963" max="8963" width="6.83203125" style="5" customWidth="1"/>
-    <col min="8964" max="8964" width="7.5" style="5" customWidth="1"/>
-    <col min="8965" max="8965" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8962" max="8962" width="7.44140625" style="5" customWidth="1"/>
+    <col min="8963" max="8963" width="6.77734375" style="5" customWidth="1"/>
+    <col min="8964" max="8964" width="7.44140625" style="5" customWidth="1"/>
+    <col min="8965" max="8965" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="8966" max="8966" width="19.33203125" style="5" customWidth="1"/>
-    <col min="8967" max="9213" width="8.83203125" style="5"/>
-    <col min="9214" max="9214" width="8.83203125" style="5" customWidth="1"/>
-    <col min="9215" max="9215" width="10.5" style="5" customWidth="1"/>
-    <col min="9216" max="9216" width="22.1640625" style="5" customWidth="1"/>
+    <col min="8967" max="9213" width="8.77734375" style="5"/>
+    <col min="9214" max="9214" width="8.77734375" style="5" customWidth="1"/>
+    <col min="9215" max="9215" width="10.44140625" style="5" customWidth="1"/>
+    <col min="9216" max="9216" width="22.109375" style="5" customWidth="1"/>
     <col min="9217" max="9217" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9218" max="9218" width="7.5" style="5" customWidth="1"/>
-    <col min="9219" max="9219" width="6.83203125" style="5" customWidth="1"/>
-    <col min="9220" max="9220" width="7.5" style="5" customWidth="1"/>
-    <col min="9221" max="9221" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9218" max="9218" width="7.44140625" style="5" customWidth="1"/>
+    <col min="9219" max="9219" width="6.77734375" style="5" customWidth="1"/>
+    <col min="9220" max="9220" width="7.44140625" style="5" customWidth="1"/>
+    <col min="9221" max="9221" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="9222" max="9222" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9223" max="9469" width="8.83203125" style="5"/>
-    <col min="9470" max="9470" width="8.83203125" style="5" customWidth="1"/>
-    <col min="9471" max="9471" width="10.5" style="5" customWidth="1"/>
-    <col min="9472" max="9472" width="22.1640625" style="5" customWidth="1"/>
+    <col min="9223" max="9469" width="8.77734375" style="5"/>
+    <col min="9470" max="9470" width="8.77734375" style="5" customWidth="1"/>
+    <col min="9471" max="9471" width="10.44140625" style="5" customWidth="1"/>
+    <col min="9472" max="9472" width="22.109375" style="5" customWidth="1"/>
     <col min="9473" max="9473" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9474" max="9474" width="7.5" style="5" customWidth="1"/>
-    <col min="9475" max="9475" width="6.83203125" style="5" customWidth="1"/>
-    <col min="9476" max="9476" width="7.5" style="5" customWidth="1"/>
-    <col min="9477" max="9477" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9474" max="9474" width="7.44140625" style="5" customWidth="1"/>
+    <col min="9475" max="9475" width="6.77734375" style="5" customWidth="1"/>
+    <col min="9476" max="9476" width="7.44140625" style="5" customWidth="1"/>
+    <col min="9477" max="9477" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="9478" max="9478" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9479" max="9725" width="8.83203125" style="5"/>
-    <col min="9726" max="9726" width="8.83203125" style="5" customWidth="1"/>
-    <col min="9727" max="9727" width="10.5" style="5" customWidth="1"/>
-    <col min="9728" max="9728" width="22.1640625" style="5" customWidth="1"/>
+    <col min="9479" max="9725" width="8.77734375" style="5"/>
+    <col min="9726" max="9726" width="8.77734375" style="5" customWidth="1"/>
+    <col min="9727" max="9727" width="10.44140625" style="5" customWidth="1"/>
+    <col min="9728" max="9728" width="22.109375" style="5" customWidth="1"/>
     <col min="9729" max="9729" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9730" max="9730" width="7.5" style="5" customWidth="1"/>
-    <col min="9731" max="9731" width="6.83203125" style="5" customWidth="1"/>
-    <col min="9732" max="9732" width="7.5" style="5" customWidth="1"/>
-    <col min="9733" max="9733" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9730" max="9730" width="7.44140625" style="5" customWidth="1"/>
+    <col min="9731" max="9731" width="6.77734375" style="5" customWidth="1"/>
+    <col min="9732" max="9732" width="7.44140625" style="5" customWidth="1"/>
+    <col min="9733" max="9733" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="9734" max="9734" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9735" max="9981" width="8.83203125" style="5"/>
-    <col min="9982" max="9982" width="8.83203125" style="5" customWidth="1"/>
-    <col min="9983" max="9983" width="10.5" style="5" customWidth="1"/>
-    <col min="9984" max="9984" width="22.1640625" style="5" customWidth="1"/>
+    <col min="9735" max="9981" width="8.77734375" style="5"/>
+    <col min="9982" max="9982" width="8.77734375" style="5" customWidth="1"/>
+    <col min="9983" max="9983" width="10.44140625" style="5" customWidth="1"/>
+    <col min="9984" max="9984" width="22.109375" style="5" customWidth="1"/>
     <col min="9985" max="9985" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9986" max="9986" width="7.5" style="5" customWidth="1"/>
-    <col min="9987" max="9987" width="6.83203125" style="5" customWidth="1"/>
-    <col min="9988" max="9988" width="7.5" style="5" customWidth="1"/>
-    <col min="9989" max="9989" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9986" max="9986" width="7.44140625" style="5" customWidth="1"/>
+    <col min="9987" max="9987" width="6.77734375" style="5" customWidth="1"/>
+    <col min="9988" max="9988" width="7.44140625" style="5" customWidth="1"/>
+    <col min="9989" max="9989" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="9990" max="9990" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9991" max="10237" width="8.83203125" style="5"/>
-    <col min="10238" max="10238" width="8.83203125" style="5" customWidth="1"/>
-    <col min="10239" max="10239" width="10.5" style="5" customWidth="1"/>
-    <col min="10240" max="10240" width="22.1640625" style="5" customWidth="1"/>
+    <col min="9991" max="10237" width="8.77734375" style="5"/>
+    <col min="10238" max="10238" width="8.77734375" style="5" customWidth="1"/>
+    <col min="10239" max="10239" width="10.44140625" style="5" customWidth="1"/>
+    <col min="10240" max="10240" width="22.109375" style="5" customWidth="1"/>
     <col min="10241" max="10241" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10242" max="10242" width="7.5" style="5" customWidth="1"/>
-    <col min="10243" max="10243" width="6.83203125" style="5" customWidth="1"/>
-    <col min="10244" max="10244" width="7.5" style="5" customWidth="1"/>
-    <col min="10245" max="10245" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10242" max="10242" width="7.44140625" style="5" customWidth="1"/>
+    <col min="10243" max="10243" width="6.77734375" style="5" customWidth="1"/>
+    <col min="10244" max="10244" width="7.44140625" style="5" customWidth="1"/>
+    <col min="10245" max="10245" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="10246" max="10246" width="19.33203125" style="5" customWidth="1"/>
-    <col min="10247" max="10493" width="8.83203125" style="5"/>
-    <col min="10494" max="10494" width="8.83203125" style="5" customWidth="1"/>
-    <col min="10495" max="10495" width="10.5" style="5" customWidth="1"/>
-    <col min="10496" max="10496" width="22.1640625" style="5" customWidth="1"/>
+    <col min="10247" max="10493" width="8.77734375" style="5"/>
+    <col min="10494" max="10494" width="8.77734375" style="5" customWidth="1"/>
+    <col min="10495" max="10495" width="10.44140625" style="5" customWidth="1"/>
+    <col min="10496" max="10496" width="22.109375" style="5" customWidth="1"/>
     <col min="10497" max="10497" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10498" max="10498" width="7.5" style="5" customWidth="1"/>
-    <col min="10499" max="10499" width="6.83203125" style="5" customWidth="1"/>
-    <col min="10500" max="10500" width="7.5" style="5" customWidth="1"/>
-    <col min="10501" max="10501" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10498" max="10498" width="7.44140625" style="5" customWidth="1"/>
+    <col min="10499" max="10499" width="6.77734375" style="5" customWidth="1"/>
+    <col min="10500" max="10500" width="7.44140625" style="5" customWidth="1"/>
+    <col min="10501" max="10501" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="10502" max="10502" width="19.33203125" style="5" customWidth="1"/>
-    <col min="10503" max="10749" width="8.83203125" style="5"/>
-    <col min="10750" max="10750" width="8.83203125" style="5" customWidth="1"/>
-    <col min="10751" max="10751" width="10.5" style="5" customWidth="1"/>
-    <col min="10752" max="10752" width="22.1640625" style="5" customWidth="1"/>
+    <col min="10503" max="10749" width="8.77734375" style="5"/>
+    <col min="10750" max="10750" width="8.77734375" style="5" customWidth="1"/>
+    <col min="10751" max="10751" width="10.44140625" style="5" customWidth="1"/>
+    <col min="10752" max="10752" width="22.109375" style="5" customWidth="1"/>
     <col min="10753" max="10753" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10754" max="10754" width="7.5" style="5" customWidth="1"/>
-    <col min="10755" max="10755" width="6.83203125" style="5" customWidth="1"/>
-    <col min="10756" max="10756" width="7.5" style="5" customWidth="1"/>
-    <col min="10757" max="10757" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10754" max="10754" width="7.44140625" style="5" customWidth="1"/>
+    <col min="10755" max="10755" width="6.77734375" style="5" customWidth="1"/>
+    <col min="10756" max="10756" width="7.44140625" style="5" customWidth="1"/>
+    <col min="10757" max="10757" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="10758" max="10758" width="19.33203125" style="5" customWidth="1"/>
-    <col min="10759" max="11005" width="8.83203125" style="5"/>
-    <col min="11006" max="11006" width="8.83203125" style="5" customWidth="1"/>
-    <col min="11007" max="11007" width="10.5" style="5" customWidth="1"/>
-    <col min="11008" max="11008" width="22.1640625" style="5" customWidth="1"/>
+    <col min="10759" max="11005" width="8.77734375" style="5"/>
+    <col min="11006" max="11006" width="8.77734375" style="5" customWidth="1"/>
+    <col min="11007" max="11007" width="10.44140625" style="5" customWidth="1"/>
+    <col min="11008" max="11008" width="22.109375" style="5" customWidth="1"/>
     <col min="11009" max="11009" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11010" max="11010" width="7.5" style="5" customWidth="1"/>
-    <col min="11011" max="11011" width="6.83203125" style="5" customWidth="1"/>
-    <col min="11012" max="11012" width="7.5" style="5" customWidth="1"/>
-    <col min="11013" max="11013" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11010" max="11010" width="7.44140625" style="5" customWidth="1"/>
+    <col min="11011" max="11011" width="6.77734375" style="5" customWidth="1"/>
+    <col min="11012" max="11012" width="7.44140625" style="5" customWidth="1"/>
+    <col min="11013" max="11013" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="11014" max="11014" width="19.33203125" style="5" customWidth="1"/>
-    <col min="11015" max="11261" width="8.83203125" style="5"/>
-    <col min="11262" max="11262" width="8.83203125" style="5" customWidth="1"/>
-    <col min="11263" max="11263" width="10.5" style="5" customWidth="1"/>
-    <col min="11264" max="11264" width="22.1640625" style="5" customWidth="1"/>
+    <col min="11015" max="11261" width="8.77734375" style="5"/>
+    <col min="11262" max="11262" width="8.77734375" style="5" customWidth="1"/>
+    <col min="11263" max="11263" width="10.44140625" style="5" customWidth="1"/>
+    <col min="11264" max="11264" width="22.109375" style="5" customWidth="1"/>
     <col min="11265" max="11265" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11266" max="11266" width="7.5" style="5" customWidth="1"/>
-    <col min="11267" max="11267" width="6.83203125" style="5" customWidth="1"/>
-    <col min="11268" max="11268" width="7.5" style="5" customWidth="1"/>
-    <col min="11269" max="11269" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11266" max="11266" width="7.44140625" style="5" customWidth="1"/>
+    <col min="11267" max="11267" width="6.77734375" style="5" customWidth="1"/>
+    <col min="11268" max="11268" width="7.44140625" style="5" customWidth="1"/>
+    <col min="11269" max="11269" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="11270" max="11270" width="19.33203125" style="5" customWidth="1"/>
-    <col min="11271" max="11517" width="8.83203125" style="5"/>
-    <col min="11518" max="11518" width="8.83203125" style="5" customWidth="1"/>
-    <col min="11519" max="11519" width="10.5" style="5" customWidth="1"/>
-    <col min="11520" max="11520" width="22.1640625" style="5" customWidth="1"/>
+    <col min="11271" max="11517" width="8.77734375" style="5"/>
+    <col min="11518" max="11518" width="8.77734375" style="5" customWidth="1"/>
+    <col min="11519" max="11519" width="10.44140625" style="5" customWidth="1"/>
+    <col min="11520" max="11520" width="22.109375" style="5" customWidth="1"/>
     <col min="11521" max="11521" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11522" max="11522" width="7.5" style="5" customWidth="1"/>
-    <col min="11523" max="11523" width="6.83203125" style="5" customWidth="1"/>
-    <col min="11524" max="11524" width="7.5" style="5" customWidth="1"/>
-    <col min="11525" max="11525" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11522" max="11522" width="7.44140625" style="5" customWidth="1"/>
+    <col min="11523" max="11523" width="6.77734375" style="5" customWidth="1"/>
+    <col min="11524" max="11524" width="7.44140625" style="5" customWidth="1"/>
+    <col min="11525" max="11525" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="11526" max="11526" width="19.33203125" style="5" customWidth="1"/>
-    <col min="11527" max="11773" width="8.83203125" style="5"/>
-    <col min="11774" max="11774" width="8.83203125" style="5" customWidth="1"/>
-    <col min="11775" max="11775" width="10.5" style="5" customWidth="1"/>
-    <col min="11776" max="11776" width="22.1640625" style="5" customWidth="1"/>
+    <col min="11527" max="11773" width="8.77734375" style="5"/>
+    <col min="11774" max="11774" width="8.77734375" style="5" customWidth="1"/>
+    <col min="11775" max="11775" width="10.44140625" style="5" customWidth="1"/>
+    <col min="11776" max="11776" width="22.109375" style="5" customWidth="1"/>
     <col min="11777" max="11777" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11778" max="11778" width="7.5" style="5" customWidth="1"/>
-    <col min="11779" max="11779" width="6.83203125" style="5" customWidth="1"/>
-    <col min="11780" max="11780" width="7.5" style="5" customWidth="1"/>
-    <col min="11781" max="11781" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11778" max="11778" width="7.44140625" style="5" customWidth="1"/>
+    <col min="11779" max="11779" width="6.77734375" style="5" customWidth="1"/>
+    <col min="11780" max="11780" width="7.44140625" style="5" customWidth="1"/>
+    <col min="11781" max="11781" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="11782" max="11782" width="19.33203125" style="5" customWidth="1"/>
-    <col min="11783" max="12029" width="8.83203125" style="5"/>
-    <col min="12030" max="12030" width="8.83203125" style="5" customWidth="1"/>
-    <col min="12031" max="12031" width="10.5" style="5" customWidth="1"/>
-    <col min="12032" max="12032" width="22.1640625" style="5" customWidth="1"/>
+    <col min="11783" max="12029" width="8.77734375" style="5"/>
+    <col min="12030" max="12030" width="8.77734375" style="5" customWidth="1"/>
+    <col min="12031" max="12031" width="10.44140625" style="5" customWidth="1"/>
+    <col min="12032" max="12032" width="22.109375" style="5" customWidth="1"/>
     <col min="12033" max="12033" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12034" max="12034" width="7.5" style="5" customWidth="1"/>
-    <col min="12035" max="12035" width="6.83203125" style="5" customWidth="1"/>
-    <col min="12036" max="12036" width="7.5" style="5" customWidth="1"/>
-    <col min="12037" max="12037" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12034" max="12034" width="7.44140625" style="5" customWidth="1"/>
+    <col min="12035" max="12035" width="6.77734375" style="5" customWidth="1"/>
+    <col min="12036" max="12036" width="7.44140625" style="5" customWidth="1"/>
+    <col min="12037" max="12037" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="12038" max="12038" width="19.33203125" style="5" customWidth="1"/>
-    <col min="12039" max="12285" width="8.83203125" style="5"/>
-    <col min="12286" max="12286" width="8.83203125" style="5" customWidth="1"/>
-    <col min="12287" max="12287" width="10.5" style="5" customWidth="1"/>
-    <col min="12288" max="12288" width="22.1640625" style="5" customWidth="1"/>
+    <col min="12039" max="12285" width="8.77734375" style="5"/>
+    <col min="12286" max="12286" width="8.77734375" style="5" customWidth="1"/>
+    <col min="12287" max="12287" width="10.44140625" style="5" customWidth="1"/>
+    <col min="12288" max="12288" width="22.109375" style="5" customWidth="1"/>
     <col min="12289" max="12289" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12290" max="12290" width="7.5" style="5" customWidth="1"/>
-    <col min="12291" max="12291" width="6.83203125" style="5" customWidth="1"/>
-    <col min="12292" max="12292" width="7.5" style="5" customWidth="1"/>
-    <col min="12293" max="12293" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12290" max="12290" width="7.44140625" style="5" customWidth="1"/>
+    <col min="12291" max="12291" width="6.77734375" style="5" customWidth="1"/>
+    <col min="12292" max="12292" width="7.44140625" style="5" customWidth="1"/>
+    <col min="12293" max="12293" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="12294" max="12294" width="19.33203125" style="5" customWidth="1"/>
-    <col min="12295" max="12541" width="8.83203125" style="5"/>
-    <col min="12542" max="12542" width="8.83203125" style="5" customWidth="1"/>
-    <col min="12543" max="12543" width="10.5" style="5" customWidth="1"/>
-    <col min="12544" max="12544" width="22.1640625" style="5" customWidth="1"/>
+    <col min="12295" max="12541" width="8.77734375" style="5"/>
+    <col min="12542" max="12542" width="8.77734375" style="5" customWidth="1"/>
+    <col min="12543" max="12543" width="10.44140625" style="5" customWidth="1"/>
+    <col min="12544" max="12544" width="22.109375" style="5" customWidth="1"/>
     <col min="12545" max="12545" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12546" max="12546" width="7.5" style="5" customWidth="1"/>
-    <col min="12547" max="12547" width="6.83203125" style="5" customWidth="1"/>
-    <col min="12548" max="12548" width="7.5" style="5" customWidth="1"/>
-    <col min="12549" max="12549" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12546" max="12546" width="7.44140625" style="5" customWidth="1"/>
+    <col min="12547" max="12547" width="6.77734375" style="5" customWidth="1"/>
+    <col min="12548" max="12548" width="7.44140625" style="5" customWidth="1"/>
+    <col min="12549" max="12549" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="12550" max="12550" width="19.33203125" style="5" customWidth="1"/>
-    <col min="12551" max="12797" width="8.83203125" style="5"/>
-    <col min="12798" max="12798" width="8.83203125" style="5" customWidth="1"/>
-    <col min="12799" max="12799" width="10.5" style="5" customWidth="1"/>
-    <col min="12800" max="12800" width="22.1640625" style="5" customWidth="1"/>
+    <col min="12551" max="12797" width="8.77734375" style="5"/>
+    <col min="12798" max="12798" width="8.77734375" style="5" customWidth="1"/>
+    <col min="12799" max="12799" width="10.44140625" style="5" customWidth="1"/>
+    <col min="12800" max="12800" width="22.109375" style="5" customWidth="1"/>
     <col min="12801" max="12801" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12802" max="12802" width="7.5" style="5" customWidth="1"/>
-    <col min="12803" max="12803" width="6.83203125" style="5" customWidth="1"/>
-    <col min="12804" max="12804" width="7.5" style="5" customWidth="1"/>
-    <col min="12805" max="12805" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12802" max="12802" width="7.44140625" style="5" customWidth="1"/>
+    <col min="12803" max="12803" width="6.77734375" style="5" customWidth="1"/>
+    <col min="12804" max="12804" width="7.44140625" style="5" customWidth="1"/>
+    <col min="12805" max="12805" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="12806" max="12806" width="19.33203125" style="5" customWidth="1"/>
-    <col min="12807" max="13053" width="8.83203125" style="5"/>
-    <col min="13054" max="13054" width="8.83203125" style="5" customWidth="1"/>
-    <col min="13055" max="13055" width="10.5" style="5" customWidth="1"/>
-    <col min="13056" max="13056" width="22.1640625" style="5" customWidth="1"/>
+    <col min="12807" max="13053" width="8.77734375" style="5"/>
+    <col min="13054" max="13054" width="8.77734375" style="5" customWidth="1"/>
+    <col min="13055" max="13055" width="10.44140625" style="5" customWidth="1"/>
+    <col min="13056" max="13056" width="22.109375" style="5" customWidth="1"/>
     <col min="13057" max="13057" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13058" max="13058" width="7.5" style="5" customWidth="1"/>
-    <col min="13059" max="13059" width="6.83203125" style="5" customWidth="1"/>
-    <col min="13060" max="13060" width="7.5" style="5" customWidth="1"/>
-    <col min="13061" max="13061" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13058" max="13058" width="7.44140625" style="5" customWidth="1"/>
+    <col min="13059" max="13059" width="6.77734375" style="5" customWidth="1"/>
+    <col min="13060" max="13060" width="7.44140625" style="5" customWidth="1"/>
+    <col min="13061" max="13061" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="13062" max="13062" width="19.33203125" style="5" customWidth="1"/>
-    <col min="13063" max="13309" width="8.83203125" style="5"/>
-    <col min="13310" max="13310" width="8.83203125" style="5" customWidth="1"/>
-    <col min="13311" max="13311" width="10.5" style="5" customWidth="1"/>
-    <col min="13312" max="13312" width="22.1640625" style="5" customWidth="1"/>
+    <col min="13063" max="13309" width="8.77734375" style="5"/>
+    <col min="13310" max="13310" width="8.77734375" style="5" customWidth="1"/>
+    <col min="13311" max="13311" width="10.44140625" style="5" customWidth="1"/>
+    <col min="13312" max="13312" width="22.109375" style="5" customWidth="1"/>
     <col min="13313" max="13313" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13314" max="13314" width="7.5" style="5" customWidth="1"/>
-    <col min="13315" max="13315" width="6.83203125" style="5" customWidth="1"/>
-    <col min="13316" max="13316" width="7.5" style="5" customWidth="1"/>
-    <col min="13317" max="13317" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13314" max="13314" width="7.44140625" style="5" customWidth="1"/>
+    <col min="13315" max="13315" width="6.77734375" style="5" customWidth="1"/>
+    <col min="13316" max="13316" width="7.44140625" style="5" customWidth="1"/>
+    <col min="13317" max="13317" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="13318" max="13318" width="19.33203125" style="5" customWidth="1"/>
-    <col min="13319" max="13565" width="8.83203125" style="5"/>
-    <col min="13566" max="13566" width="8.83203125" style="5" customWidth="1"/>
-    <col min="13567" max="13567" width="10.5" style="5" customWidth="1"/>
-    <col min="13568" max="13568" width="22.1640625" style="5" customWidth="1"/>
+    <col min="13319" max="13565" width="8.77734375" style="5"/>
+    <col min="13566" max="13566" width="8.77734375" style="5" customWidth="1"/>
+    <col min="13567" max="13567" width="10.44140625" style="5" customWidth="1"/>
+    <col min="13568" max="13568" width="22.109375" style="5" customWidth="1"/>
     <col min="13569" max="13569" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13570" max="13570" width="7.5" style="5" customWidth="1"/>
-    <col min="13571" max="13571" width="6.83203125" style="5" customWidth="1"/>
-    <col min="13572" max="13572" width="7.5" style="5" customWidth="1"/>
-    <col min="13573" max="13573" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13570" max="13570" width="7.44140625" style="5" customWidth="1"/>
+    <col min="13571" max="13571" width="6.77734375" style="5" customWidth="1"/>
+    <col min="13572" max="13572" width="7.44140625" style="5" customWidth="1"/>
+    <col min="13573" max="13573" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="13574" max="13574" width="19.33203125" style="5" customWidth="1"/>
-    <col min="13575" max="13821" width="8.83203125" style="5"/>
-    <col min="13822" max="13822" width="8.83203125" style="5" customWidth="1"/>
-    <col min="13823" max="13823" width="10.5" style="5" customWidth="1"/>
-    <col min="13824" max="13824" width="22.1640625" style="5" customWidth="1"/>
+    <col min="13575" max="13821" width="8.77734375" style="5"/>
+    <col min="13822" max="13822" width="8.77734375" style="5" customWidth="1"/>
+    <col min="13823" max="13823" width="10.44140625" style="5" customWidth="1"/>
+    <col min="13824" max="13824" width="22.109375" style="5" customWidth="1"/>
     <col min="13825" max="13825" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13826" max="13826" width="7.5" style="5" customWidth="1"/>
-    <col min="13827" max="13827" width="6.83203125" style="5" customWidth="1"/>
-    <col min="13828" max="13828" width="7.5" style="5" customWidth="1"/>
-    <col min="13829" max="13829" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13826" max="13826" width="7.44140625" style="5" customWidth="1"/>
+    <col min="13827" max="13827" width="6.77734375" style="5" customWidth="1"/>
+    <col min="13828" max="13828" width="7.44140625" style="5" customWidth="1"/>
+    <col min="13829" max="13829" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="13830" max="13830" width="19.33203125" style="5" customWidth="1"/>
-    <col min="13831" max="14077" width="8.83203125" style="5"/>
-    <col min="14078" max="14078" width="8.83203125" style="5" customWidth="1"/>
-    <col min="14079" max="14079" width="10.5" style="5" customWidth="1"/>
-    <col min="14080" max="14080" width="22.1640625" style="5" customWidth="1"/>
+    <col min="13831" max="14077" width="8.77734375" style="5"/>
+    <col min="14078" max="14078" width="8.77734375" style="5" customWidth="1"/>
+    <col min="14079" max="14079" width="10.44140625" style="5" customWidth="1"/>
+    <col min="14080" max="14080" width="22.109375" style="5" customWidth="1"/>
     <col min="14081" max="14081" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14082" max="14082" width="7.5" style="5" customWidth="1"/>
-    <col min="14083" max="14083" width="6.83203125" style="5" customWidth="1"/>
-    <col min="14084" max="14084" width="7.5" style="5" customWidth="1"/>
-    <col min="14085" max="14085" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14082" max="14082" width="7.44140625" style="5" customWidth="1"/>
+    <col min="14083" max="14083" width="6.77734375" style="5" customWidth="1"/>
+    <col min="14084" max="14084" width="7.44140625" style="5" customWidth="1"/>
+    <col min="14085" max="14085" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="14086" max="14086" width="19.33203125" style="5" customWidth="1"/>
-    <col min="14087" max="14333" width="8.83203125" style="5"/>
-    <col min="14334" max="14334" width="8.83203125" style="5" customWidth="1"/>
-    <col min="14335" max="14335" width="10.5" style="5" customWidth="1"/>
-    <col min="14336" max="14336" width="22.1640625" style="5" customWidth="1"/>
+    <col min="14087" max="14333" width="8.77734375" style="5"/>
+    <col min="14334" max="14334" width="8.77734375" style="5" customWidth="1"/>
+    <col min="14335" max="14335" width="10.44140625" style="5" customWidth="1"/>
+    <col min="14336" max="14336" width="22.109375" style="5" customWidth="1"/>
     <col min="14337" max="14337" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14338" max="14338" width="7.5" style="5" customWidth="1"/>
-    <col min="14339" max="14339" width="6.83203125" style="5" customWidth="1"/>
-    <col min="14340" max="14340" width="7.5" style="5" customWidth="1"/>
-    <col min="14341" max="14341" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14338" max="14338" width="7.44140625" style="5" customWidth="1"/>
+    <col min="14339" max="14339" width="6.77734375" style="5" customWidth="1"/>
+    <col min="14340" max="14340" width="7.44140625" style="5" customWidth="1"/>
+    <col min="14341" max="14341" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="14342" max="14342" width="19.33203125" style="5" customWidth="1"/>
-    <col min="14343" max="14589" width="8.83203125" style="5"/>
-    <col min="14590" max="14590" width="8.83203125" style="5" customWidth="1"/>
-    <col min="14591" max="14591" width="10.5" style="5" customWidth="1"/>
-    <col min="14592" max="14592" width="22.1640625" style="5" customWidth="1"/>
+    <col min="14343" max="14589" width="8.77734375" style="5"/>
+    <col min="14590" max="14590" width="8.77734375" style="5" customWidth="1"/>
+    <col min="14591" max="14591" width="10.44140625" style="5" customWidth="1"/>
+    <col min="14592" max="14592" width="22.109375" style="5" customWidth="1"/>
     <col min="14593" max="14593" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14594" max="14594" width="7.5" style="5" customWidth="1"/>
-    <col min="14595" max="14595" width="6.83203125" style="5" customWidth="1"/>
-    <col min="14596" max="14596" width="7.5" style="5" customWidth="1"/>
-    <col min="14597" max="14597" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14594" max="14594" width="7.44140625" style="5" customWidth="1"/>
+    <col min="14595" max="14595" width="6.77734375" style="5" customWidth="1"/>
+    <col min="14596" max="14596" width="7.44140625" style="5" customWidth="1"/>
+    <col min="14597" max="14597" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="14598" max="14598" width="19.33203125" style="5" customWidth="1"/>
-    <col min="14599" max="14845" width="8.83203125" style="5"/>
-    <col min="14846" max="14846" width="8.83203125" style="5" customWidth="1"/>
-    <col min="14847" max="14847" width="10.5" style="5" customWidth="1"/>
-    <col min="14848" max="14848" width="22.1640625" style="5" customWidth="1"/>
+    <col min="14599" max="14845" width="8.77734375" style="5"/>
+    <col min="14846" max="14846" width="8.77734375" style="5" customWidth="1"/>
+    <col min="14847" max="14847" width="10.44140625" style="5" customWidth="1"/>
+    <col min="14848" max="14848" width="22.109375" style="5" customWidth="1"/>
     <col min="14849" max="14849" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14850" max="14850" width="7.5" style="5" customWidth="1"/>
-    <col min="14851" max="14851" width="6.83203125" style="5" customWidth="1"/>
-    <col min="14852" max="14852" width="7.5" style="5" customWidth="1"/>
-    <col min="14853" max="14853" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14850" max="14850" width="7.44140625" style="5" customWidth="1"/>
+    <col min="14851" max="14851" width="6.77734375" style="5" customWidth="1"/>
+    <col min="14852" max="14852" width="7.44140625" style="5" customWidth="1"/>
+    <col min="14853" max="14853" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="14854" max="14854" width="19.33203125" style="5" customWidth="1"/>
-    <col min="14855" max="15101" width="8.83203125" style="5"/>
-    <col min="15102" max="15102" width="8.83203125" style="5" customWidth="1"/>
-    <col min="15103" max="15103" width="10.5" style="5" customWidth="1"/>
-    <col min="15104" max="15104" width="22.1640625" style="5" customWidth="1"/>
+    <col min="14855" max="15101" width="8.77734375" style="5"/>
+    <col min="15102" max="15102" width="8.77734375" style="5" customWidth="1"/>
+    <col min="15103" max="15103" width="10.44140625" style="5" customWidth="1"/>
+    <col min="15104" max="15104" width="22.109375" style="5" customWidth="1"/>
     <col min="15105" max="15105" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15106" max="15106" width="7.5" style="5" customWidth="1"/>
-    <col min="15107" max="15107" width="6.83203125" style="5" customWidth="1"/>
-    <col min="15108" max="15108" width="7.5" style="5" customWidth="1"/>
-    <col min="15109" max="15109" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15106" max="15106" width="7.44140625" style="5" customWidth="1"/>
+    <col min="15107" max="15107" width="6.77734375" style="5" customWidth="1"/>
+    <col min="15108" max="15108" width="7.44140625" style="5" customWidth="1"/>
+    <col min="15109" max="15109" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="15110" max="15110" width="19.33203125" style="5" customWidth="1"/>
-    <col min="15111" max="15357" width="8.83203125" style="5"/>
-    <col min="15358" max="15358" width="8.83203125" style="5" customWidth="1"/>
-    <col min="15359" max="15359" width="10.5" style="5" customWidth="1"/>
-    <col min="15360" max="15360" width="22.1640625" style="5" customWidth="1"/>
+    <col min="15111" max="15357" width="8.77734375" style="5"/>
+    <col min="15358" max="15358" width="8.77734375" style="5" customWidth="1"/>
+    <col min="15359" max="15359" width="10.44140625" style="5" customWidth="1"/>
+    <col min="15360" max="15360" width="22.109375" style="5" customWidth="1"/>
     <col min="15361" max="15361" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15362" max="15362" width="7.5" style="5" customWidth="1"/>
-    <col min="15363" max="15363" width="6.83203125" style="5" customWidth="1"/>
-    <col min="15364" max="15364" width="7.5" style="5" customWidth="1"/>
-    <col min="15365" max="15365" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15362" max="15362" width="7.44140625" style="5" customWidth="1"/>
+    <col min="15363" max="15363" width="6.77734375" style="5" customWidth="1"/>
+    <col min="15364" max="15364" width="7.44140625" style="5" customWidth="1"/>
+    <col min="15365" max="15365" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="15366" max="15366" width="19.33203125" style="5" customWidth="1"/>
-    <col min="15367" max="15613" width="8.83203125" style="5"/>
-    <col min="15614" max="15614" width="8.83203125" style="5" customWidth="1"/>
-    <col min="15615" max="15615" width="10.5" style="5" customWidth="1"/>
-    <col min="15616" max="15616" width="22.1640625" style="5" customWidth="1"/>
+    <col min="15367" max="15613" width="8.77734375" style="5"/>
+    <col min="15614" max="15614" width="8.77734375" style="5" customWidth="1"/>
+    <col min="15615" max="15615" width="10.44140625" style="5" customWidth="1"/>
+    <col min="15616" max="15616" width="22.109375" style="5" customWidth="1"/>
     <col min="15617" max="15617" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15618" max="15618" width="7.5" style="5" customWidth="1"/>
-    <col min="15619" max="15619" width="6.83203125" style="5" customWidth="1"/>
-    <col min="15620" max="15620" width="7.5" style="5" customWidth="1"/>
-    <col min="15621" max="15621" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15618" max="15618" width="7.44140625" style="5" customWidth="1"/>
+    <col min="15619" max="15619" width="6.77734375" style="5" customWidth="1"/>
+    <col min="15620" max="15620" width="7.44140625" style="5" customWidth="1"/>
+    <col min="15621" max="15621" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="15622" max="15622" width="19.33203125" style="5" customWidth="1"/>
-    <col min="15623" max="15869" width="8.83203125" style="5"/>
-    <col min="15870" max="15870" width="8.83203125" style="5" customWidth="1"/>
-    <col min="15871" max="15871" width="10.5" style="5" customWidth="1"/>
-    <col min="15872" max="15872" width="22.1640625" style="5" customWidth="1"/>
+    <col min="15623" max="15869" width="8.77734375" style="5"/>
+    <col min="15870" max="15870" width="8.77734375" style="5" customWidth="1"/>
+    <col min="15871" max="15871" width="10.44140625" style="5" customWidth="1"/>
+    <col min="15872" max="15872" width="22.109375" style="5" customWidth="1"/>
     <col min="15873" max="15873" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15874" max="15874" width="7.5" style="5" customWidth="1"/>
-    <col min="15875" max="15875" width="6.83203125" style="5" customWidth="1"/>
-    <col min="15876" max="15876" width="7.5" style="5" customWidth="1"/>
-    <col min="15877" max="15877" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15874" max="15874" width="7.44140625" style="5" customWidth="1"/>
+    <col min="15875" max="15875" width="6.77734375" style="5" customWidth="1"/>
+    <col min="15876" max="15876" width="7.44140625" style="5" customWidth="1"/>
+    <col min="15877" max="15877" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="15878" max="15878" width="19.33203125" style="5" customWidth="1"/>
-    <col min="15879" max="16125" width="8.83203125" style="5"/>
-    <col min="16126" max="16126" width="8.83203125" style="5" customWidth="1"/>
-    <col min="16127" max="16127" width="10.5" style="5" customWidth="1"/>
-    <col min="16128" max="16128" width="22.1640625" style="5" customWidth="1"/>
+    <col min="15879" max="16125" width="8.77734375" style="5"/>
+    <col min="16126" max="16126" width="8.77734375" style="5" customWidth="1"/>
+    <col min="16127" max="16127" width="10.44140625" style="5" customWidth="1"/>
+    <col min="16128" max="16128" width="22.109375" style="5" customWidth="1"/>
     <col min="16129" max="16129" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="16130" max="16130" width="7.5" style="5" customWidth="1"/>
-    <col min="16131" max="16131" width="6.83203125" style="5" customWidth="1"/>
-    <col min="16132" max="16132" width="7.5" style="5" customWidth="1"/>
-    <col min="16133" max="16133" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="16130" max="16130" width="7.44140625" style="5" customWidth="1"/>
+    <col min="16131" max="16131" width="6.77734375" style="5" customWidth="1"/>
+    <col min="16132" max="16132" width="7.44140625" style="5" customWidth="1"/>
+    <col min="16133" max="16133" width="19.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="16134" max="16134" width="19.33203125" style="5" customWidth="1"/>
-    <col min="16135" max="16384" width="8.83203125" style="5"/>
+    <col min="16135" max="16384" width="8.77734375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="26.25" customHeight="1" thickBot="1">
@@ -42543,7 +42491,7 @@
     <row r="19" spans="1:17">
       <c r="E19" s="21"/>
     </row>
-    <row r="20" spans="1:17" ht="16">
+    <row r="20" spans="1:17">
       <c r="A20" s="33" t="s">
         <v>55</v>
       </c>
@@ -42626,7 +42574,7 @@
       <c r="K25" s="66"/>
       <c r="L25" s="66"/>
     </row>
-    <row r="26" spans="1:17" ht="32">
+    <row r="26" spans="1:17" ht="27">
       <c r="D26" s="59" t="s">
         <v>91</v>
       </c>
@@ -42649,7 +42597,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="32">
+    <row r="27" spans="1:17" ht="27">
       <c r="D27" s="59" t="s">
         <v>92</v>
       </c>
@@ -42672,7 +42620,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="32">
+    <row r="28" spans="1:17" ht="27">
       <c r="D28" s="59" t="s">
         <v>93</v>
       </c>
@@ -42693,7 +42641,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="32">
+    <row r="29" spans="1:17" ht="27">
       <c r="D29" s="59" t="s">
         <v>94</v>
       </c>
@@ -42714,7 +42662,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="32">
+    <row r="30" spans="1:17" ht="27">
       <c r="D30" s="65" t="s">
         <v>95</v>
       </c>
@@ -42735,7 +42683,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="32">
+    <row r="31" spans="1:17" ht="27">
       <c r="D31" s="59" t="s">
         <v>96</v>
       </c>
